--- a/Versão5/ABNT/Ontologia_15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2N.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68FD8845-9ABA-4534-97FD-2FFCC6ECC059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DC0F1E-9936-47ED-A1FE-C6923602FA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3617" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3617" uniqueCount="430">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1375,6 +1375,12 @@
   </si>
   <si>
     <t>Código.ABNT</t>
+  </si>
+  <si>
+    <t>2N.14.08.aa</t>
+  </si>
+  <si>
+    <t>2N.92.14.06</t>
   </si>
 </sst>
 </file>
@@ -1897,7 +1903,25 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A0D90F96-026A-4EEB-BDCF-93327D239D7A}"/>
   </cellStyles>
-  <dxfs count="55">
+  <dxfs count="57">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3516,31 +3540,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:W157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="54" dataDxfId="52" headerRowBorderDxfId="53" tableBorderDxfId="51" totalsRowBorderDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:W157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55" tableBorderDxfId="53" totalsRowBorderDxfId="52">
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{F705C4B4-26FC-4C67-A385-0B420ADBB875}" name="Coluna1" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{992338D4-59FD-409D-8597-5B1757FD3C48}" name="Coluna2" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="17" dataDxfId="16"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="15" dataDxfId="14"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="13" dataDxfId="12"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="11" dataDxfId="10"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="9" dataDxfId="8"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="7" dataDxfId="6"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="5" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{F705C4B4-26FC-4C67-A385-0B420ADBB875}" name="Coluna1" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{992338D4-59FD-409D-8597-5B1757FD3C48}" name="Coluna2" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="13" dataDxfId="12"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="11" dataDxfId="10"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="9" dataDxfId="8"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="7" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4068,7 +4092,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46139.327135763888</v>
+        <v>46146.342987037038</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>412</v>
@@ -4369,7 +4393,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="AA1:AA2">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4522,7 +4546,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4567,7 +4591,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4588,7 +4612,7 @@
     <col min="5" max="5" width="10" style="56" customWidth="1"/>
     <col min="6" max="7" width="7.296875" style="56" customWidth="1"/>
     <col min="8" max="8" width="4.296875" style="56" customWidth="1"/>
-    <col min="9" max="9" width="21" style="56" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.296875" style="56" customWidth="1"/>
     <col min="10" max="10" width="7" style="56" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="43.796875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.5" style="56" bestFit="1" customWidth="1"/>
@@ -7090,7 +7114,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>218</v>
+        <v>428</v>
       </c>
       <c r="C36" s="14" t="s">
         <v>427</v>
@@ -14758,7 +14782,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>325</v>
+        <v>429</v>
       </c>
       <c r="C144" s="14" t="s">
         <v>427</v>
@@ -15750,9 +15774,12 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="R1:W1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Versão5/ABNT/Ontologia_15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2N.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EF0BA2-C0F9-4026-8B8D-55836DB871AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F72AA2-393B-48D7-BFB4-DB595A7E3BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -1344,9 +1344,6 @@
     <t>subtema</t>
   </si>
   <si>
-    <t>"Classificação de objetos da construção"</t>
-  </si>
-  <si>
     <t>"Norma Brasileira para a classificação de objetos da construção"</t>
   </si>
   <si>
@@ -1605,9 +1602,6 @@
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I.</t>
   </si>
   <si>
-    <t>"Classificação de objetos da construção - 2N"</t>
-  </si>
-  <si>
     <t>"Empreendedores"</t>
   </si>
   <si>
@@ -1633,6 +1627,12 @@
   </si>
   <si>
     <t>"Empresas e grupos"</t>
+  </si>
+  <si>
+    <t>"Normas"</t>
+  </si>
+  <si>
+    <t>"Classificação de Projeto e Construção"</t>
   </si>
 </sst>
 </file>
@@ -1970,7 +1970,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2147,6 +2147,9 @@
     <xf numFmtId="0" fontId="6" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2242,162 +2245,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond Light"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond Light"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -3074,6 +2921,162 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3900,20 +3903,20 @@
     <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="43" dataDxfId="42"/>
     <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="41" dataDxfId="40"/>
     <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="12" dataDxfId="11"/>
-    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="13" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="17" dataDxfId="16"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="13" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="11" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4441,7 +4444,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46148.398003587965</v>
+        <v>46148.57189097222</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>408</v>
@@ -4449,7 +4452,7 @@
     </row>
     <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>414</v>
@@ -4472,7 +4475,7 @@
     </row>
     <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B21" s="5" t="str">
         <f>_xlfn.TRANSLATE(B20,"pt","en")</f>
@@ -4653,19 +4656,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="52" t="s">
+        <v>423</v>
+      </c>
+      <c r="C2" s="53" t="s">
         <v>424</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="D2" s="52" t="s">
         <v>425</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="E2" s="52" t="s">
         <v>426</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="F2" s="53" t="s">
         <v>427</v>
-      </c>
-      <c r="F2" s="53" t="s">
-        <v>428</v>
       </c>
       <c r="G2" s="54" t="s">
         <v>181</v>
@@ -4699,10 +4702,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="40" t="s">
+        <v>428</v>
+      </c>
+      <c r="Q2" s="40" t="s">
         <v>429</v>
-      </c>
-      <c r="Q2" s="40" t="s">
-        <v>430</v>
       </c>
       <c r="R2" s="56" t="s">
         <v>181</v>
@@ -4720,7 +4723,7 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="40" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="W2" s="58" t="str">
         <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key.ABNT.",A2)</f>
@@ -4736,7 +4739,7 @@
         <v>181</v>
       </c>
       <c r="AA2" s="40" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4744,19 +4747,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="52" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="53" t="s">
         <v>424</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="D3" s="52" t="s">
         <v>425</v>
       </c>
-      <c r="D3" s="52" t="s">
-        <v>426</v>
-      </c>
       <c r="E3" s="52" t="s">
+        <v>432</v>
+      </c>
+      <c r="F3" s="53" t="s">
         <v>433</v>
-      </c>
-      <c r="F3" s="53" t="s">
-        <v>434</v>
       </c>
       <c r="G3" s="54" t="s">
         <v>181</v>
@@ -4790,10 +4793,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="40" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q3" s="40" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="R3" s="56" t="s">
         <v>181</v>
@@ -4811,7 +4814,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="40" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="W3" s="58" t="str">
         <f t="shared" si="3"/>
@@ -4827,7 +4830,7 @@
         <v>181</v>
       </c>
       <c r="AA3" s="40" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4835,19 +4838,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="52" t="s">
+        <v>423</v>
+      </c>
+      <c r="C4" s="53" t="s">
         <v>424</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="D4" s="52" t="s">
         <v>425</v>
       </c>
-      <c r="D4" s="52" t="s">
-        <v>426</v>
-      </c>
       <c r="E4" s="52" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F4" s="53" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G4" s="54" t="s">
         <v>181</v>
@@ -4881,10 +4884,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q4" s="40" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="R4" s="56" t="s">
         <v>181</v>
@@ -4902,7 +4905,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="40" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="W4" s="58" t="str">
         <f t="shared" si="3"/>
@@ -4918,7 +4921,7 @@
         <v>181</v>
       </c>
       <c r="AA4" s="40" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4926,19 +4929,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="52" t="s">
+        <v>423</v>
+      </c>
+      <c r="C5" s="53" t="s">
         <v>424</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="D5" s="52" t="s">
         <v>425</v>
       </c>
-      <c r="D5" s="52" t="s">
-        <v>426</v>
-      </c>
       <c r="E5" s="52" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G5" s="54" t="s">
         <v>181</v>
@@ -4972,10 +4975,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="40" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q5" s="40" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="R5" s="56" t="s">
         <v>181</v>
@@ -4993,7 +4996,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="40" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="W5" s="58" t="str">
         <f t="shared" si="3"/>
@@ -5009,7 +5012,7 @@
         <v>181</v>
       </c>
       <c r="AA5" s="40" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5017,19 +5020,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="52" t="s">
+        <v>423</v>
+      </c>
+      <c r="C6" s="53" t="s">
         <v>424</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="D6" s="52" t="s">
         <v>425</v>
       </c>
-      <c r="D6" s="52" t="s">
-        <v>426</v>
-      </c>
       <c r="E6" s="52" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G6" s="54" t="s">
         <v>181</v>
@@ -5063,10 +5066,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="40" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Q6" s="40" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="R6" s="56" t="s">
         <v>181</v>
@@ -5084,7 +5087,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="40" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="W6" s="58" t="str">
         <f t="shared" si="3"/>
@@ -5100,7 +5103,7 @@
         <v>181</v>
       </c>
       <c r="AA6" s="40" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5120,7 +5123,7 @@
         <v>393</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G7" s="38" t="s">
         <v>181</v>
@@ -5154,10 +5157,10 @@
         <v>ABNT.0M</v>
       </c>
       <c r="P7" s="55" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q7" s="55" t="s">
         <v>447</v>
-      </c>
-      <c r="Q7" s="55" t="s">
-        <v>448</v>
       </c>
       <c r="R7" s="56" t="s">
         <v>181</v>
@@ -5188,10 +5191,10 @@
         <v>181</v>
       </c>
       <c r="Z7" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="AA7" s="59" t="s">
         <v>449</v>
-      </c>
-      <c r="AA7" s="59" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5211,7 +5214,7 @@
         <v>393</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G8" s="38" t="s">
         <v>181</v>
@@ -5245,10 +5248,10 @@
         <v>ABNT.0P</v>
       </c>
       <c r="P8" s="55" t="s">
+        <v>451</v>
+      </c>
+      <c r="Q8" s="55" t="s">
         <v>452</v>
-      </c>
-      <c r="Q8" s="55" t="s">
-        <v>453</v>
       </c>
       <c r="R8" s="56" t="s">
         <v>181</v>
@@ -5279,10 +5282,10 @@
         <v>181</v>
       </c>
       <c r="Z8" s="40" t="s">
+        <v>453</v>
+      </c>
+      <c r="AA8" s="59" t="s">
         <v>454</v>
-      </c>
-      <c r="AA8" s="59" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5302,7 +5305,7 @@
         <v>393</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G9" s="38" t="s">
         <v>181</v>
@@ -5336,10 +5339,10 @@
         <v>ABNT.1D</v>
       </c>
       <c r="P9" s="55" t="s">
+        <v>456</v>
+      </c>
+      <c r="Q9" s="55" t="s">
         <v>457</v>
-      </c>
-      <c r="Q9" s="55" t="s">
-        <v>458</v>
       </c>
       <c r="R9" s="56" t="s">
         <v>181</v>
@@ -5370,10 +5373,10 @@
         <v>181</v>
       </c>
       <c r="Z9" s="40" t="s">
+        <v>458</v>
+      </c>
+      <c r="AA9" s="59" t="s">
         <v>459</v>
-      </c>
-      <c r="AA9" s="59" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5393,7 +5396,7 @@
         <v>393</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G10" s="38" t="s">
         <v>181</v>
@@ -5427,10 +5430,10 @@
         <v>ABNT.1F</v>
       </c>
       <c r="P10" s="55" t="s">
+        <v>461</v>
+      </c>
+      <c r="Q10" s="55" t="s">
         <v>462</v>
-      </c>
-      <c r="Q10" s="55" t="s">
-        <v>463</v>
       </c>
       <c r="R10" s="56" t="s">
         <v>181</v>
@@ -5461,10 +5464,10 @@
         <v>181</v>
       </c>
       <c r="Z10" s="40" t="s">
+        <v>463</v>
+      </c>
+      <c r="AA10" s="59" t="s">
         <v>464</v>
-      </c>
-      <c r="AA10" s="59" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5484,7 +5487,7 @@
         <v>393</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G11" s="38" t="s">
         <v>181</v>
@@ -5518,10 +5521,10 @@
         <v>ABNT.1S</v>
       </c>
       <c r="P11" s="55" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q11" s="55" t="s">
         <v>467</v>
-      </c>
-      <c r="Q11" s="55" t="s">
-        <v>468</v>
       </c>
       <c r="R11" s="56" t="s">
         <v>181</v>
@@ -5552,10 +5555,10 @@
         <v>181</v>
       </c>
       <c r="Z11" s="40" t="s">
+        <v>468</v>
+      </c>
+      <c r="AA11" s="59" t="s">
         <v>469</v>
-      </c>
-      <c r="AA11" s="59" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5575,7 +5578,7 @@
         <v>393</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>181</v>
@@ -5609,10 +5612,10 @@
         <v>ABNT.2C</v>
       </c>
       <c r="P12" s="55" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q12" s="55" t="s">
         <v>472</v>
-      </c>
-      <c r="Q12" s="55" t="s">
-        <v>473</v>
       </c>
       <c r="R12" s="56" t="s">
         <v>181</v>
@@ -5643,10 +5646,10 @@
         <v>181</v>
       </c>
       <c r="Z12" s="40" t="s">
+        <v>473</v>
+      </c>
+      <c r="AA12" s="59" t="s">
         <v>474</v>
-      </c>
-      <c r="AA12" s="59" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5666,7 +5669,7 @@
         <v>393</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G13" s="38" t="s">
         <v>181</v>
@@ -5700,10 +5703,10 @@
         <v>ABNT.2N</v>
       </c>
       <c r="P13" s="55" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q13" s="55" t="s">
         <v>472</v>
-      </c>
-      <c r="Q13" s="55" t="s">
-        <v>473</v>
       </c>
       <c r="R13" s="56" t="s">
         <v>181</v>
@@ -5737,7 +5740,7 @@
         <v>342</v>
       </c>
       <c r="AA13" s="59" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5757,7 +5760,7 @@
         <v>393</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G14" s="38" t="s">
         <v>181</v>
@@ -5791,10 +5794,10 @@
         <v>ABNT.2Q</v>
       </c>
       <c r="P14" s="55" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q14" s="55" t="s">
         <v>472</v>
-      </c>
-      <c r="Q14" s="55" t="s">
-        <v>473</v>
       </c>
       <c r="R14" s="56" t="s">
         <v>181</v>
@@ -5825,10 +5828,10 @@
         <v>181</v>
       </c>
       <c r="Z14" s="40" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AA14" s="59" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5848,7 +5851,7 @@
         <v>393</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G15" s="38" t="s">
         <v>181</v>
@@ -5882,10 +5885,10 @@
         <v>ABNT.3E</v>
       </c>
       <c r="P15" s="55" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q15" s="55" t="s">
         <v>480</v>
-      </c>
-      <c r="Q15" s="55" t="s">
-        <v>481</v>
       </c>
       <c r="R15" s="56" t="s">
         <v>181</v>
@@ -5916,10 +5919,10 @@
         <v>181</v>
       </c>
       <c r="Z15" s="40" t="s">
+        <v>481</v>
+      </c>
+      <c r="AA15" s="59" t="s">
         <v>482</v>
-      </c>
-      <c r="AA15" s="59" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5939,7 +5942,7 @@
         <v>393</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>181</v>
@@ -5973,10 +5976,10 @@
         <v>ABNT.3R</v>
       </c>
       <c r="P16" s="55" t="s">
+        <v>484</v>
+      </c>
+      <c r="Q16" s="55" t="s">
         <v>485</v>
-      </c>
-      <c r="Q16" s="55" t="s">
-        <v>486</v>
       </c>
       <c r="R16" s="56" t="s">
         <v>181</v>
@@ -6007,10 +6010,10 @@
         <v>181</v>
       </c>
       <c r="Z16" s="40" t="s">
+        <v>486</v>
+      </c>
+      <c r="AA16" s="59" t="s">
         <v>487</v>
-      </c>
-      <c r="AA16" s="59" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6030,7 +6033,7 @@
         <v>393</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G17" s="38" t="s">
         <v>181</v>
@@ -6064,10 +6067,10 @@
         <v>ABNT.4A</v>
       </c>
       <c r="P17" s="55" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q17" s="55" t="s">
         <v>490</v>
-      </c>
-      <c r="Q17" s="55" t="s">
-        <v>491</v>
       </c>
       <c r="R17" s="56" t="s">
         <v>181</v>
@@ -6098,10 +6101,10 @@
         <v>181</v>
       </c>
       <c r="Z17" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="AA17" s="59" t="s">
         <v>492</v>
-      </c>
-      <c r="AA17" s="59" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6121,7 +6124,7 @@
         <v>393</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G18" s="38" t="s">
         <v>181</v>
@@ -6155,10 +6158,10 @@
         <v>ABNT.4U</v>
       </c>
       <c r="P18" s="55" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q18" s="55" t="s">
         <v>495</v>
-      </c>
-      <c r="Q18" s="55" t="s">
-        <v>496</v>
       </c>
       <c r="R18" s="56" t="s">
         <v>181</v>
@@ -6189,10 +6192,10 @@
         <v>181</v>
       </c>
       <c r="Z18" s="40" t="s">
+        <v>496</v>
+      </c>
+      <c r="AA18" s="59" t="s">
         <v>497</v>
-      </c>
-      <c r="AA18" s="59" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6212,7 +6215,7 @@
         <v>393</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G19" s="38" t="s">
         <v>181</v>
@@ -6246,10 +6249,10 @@
         <v>ABNT.5I</v>
       </c>
       <c r="P19" s="55" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q19" s="55" t="s">
         <v>500</v>
-      </c>
-      <c r="Q19" s="55" t="s">
-        <v>501</v>
       </c>
       <c r="R19" s="56" t="s">
         <v>181</v>
@@ -6280,10 +6283,10 @@
         <v>181</v>
       </c>
       <c r="Z19" s="40" t="s">
+        <v>501</v>
+      </c>
+      <c r="AA19" s="59" t="s">
         <v>502</v>
-      </c>
-      <c r="AA19" s="59" t="s">
-        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -6518,9 +6521,9 @@
     <col min="5" max="5" width="10" style="50" customWidth="1"/>
     <col min="6" max="7" width="7.33203125" style="50" customWidth="1"/>
     <col min="8" max="8" width="4.33203125" style="50" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" style="50" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="50" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.5" style="50" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" style="50" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.1640625" style="50" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" style="50" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="43.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.6640625" style="50" customWidth="1"/>
@@ -6618,28 +6621,28 @@
         <v>347</v>
       </c>
       <c r="F2" s="47" t="s">
-        <v>339</v>
+        <v>181</v>
       </c>
       <c r="G2" s="48" t="s">
-        <v>413</v>
+        <v>181</v>
       </c>
       <c r="H2" s="47" t="s">
         <v>340</v>
       </c>
       <c r="I2" s="48" t="s">
-        <v>417</v>
+        <v>512</v>
       </c>
       <c r="J2" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K2" s="48" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="L2" s="49" t="s">
         <v>1</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N2" s="47" t="s">
         <v>411</v>
@@ -6688,23 +6691,23 @@
       <c r="E3" s="48" t="s">
         <v>347</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="49" t="s">
         <v>339</v>
       </c>
-      <c r="G3" s="48" t="s">
+      <c r="G3" s="60" t="s">
         <v>341</v>
       </c>
       <c r="H3" s="47" t="s">
         <v>340</v>
       </c>
       <c r="I3" s="48" t="s">
-        <v>417</v>
+        <v>512</v>
       </c>
       <c r="J3" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K3" s="48" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="L3" s="49" t="s">
         <v>1</v>
@@ -6751,7 +6754,7 @@
         <v>342</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>346</v>
@@ -6759,23 +6762,23 @@
       <c r="E4" s="48" t="s">
         <v>347</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="49" t="s">
         <v>339</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="60" t="s">
         <v>341</v>
       </c>
       <c r="H4" s="47" t="s">
         <v>340</v>
       </c>
       <c r="I4" s="48" t="s">
-        <v>417</v>
+        <v>512</v>
       </c>
       <c r="J4" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K4" s="48" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="L4" s="49" t="s">
         <v>1</v>
@@ -6822,7 +6825,7 @@
         <v>188</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>346</v>
@@ -6840,13 +6843,13 @@
         <v>340</v>
       </c>
       <c r="I5" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J5" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K5" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L5" s="49" t="s">
         <v>1</v>
@@ -6893,7 +6896,7 @@
         <v>189</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>346</v>
@@ -6911,13 +6914,13 @@
         <v>340</v>
       </c>
       <c r="I6" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J6" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K6" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L6" s="49" t="s">
         <v>1</v>
@@ -6964,7 +6967,7 @@
         <v>190</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>346</v>
@@ -6982,13 +6985,13 @@
         <v>340</v>
       </c>
       <c r="I7" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J7" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K7" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L7" s="49" t="s">
         <v>1</v>
@@ -7035,7 +7038,7 @@
         <v>191</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>346</v>
@@ -7053,13 +7056,13 @@
         <v>340</v>
       </c>
       <c r="I8" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J8" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K8" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L8" s="49" t="s">
         <v>1</v>
@@ -7106,7 +7109,7 @@
         <v>192</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D9" s="47" t="s">
         <v>346</v>
@@ -7124,13 +7127,13 @@
         <v>340</v>
       </c>
       <c r="I9" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J9" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K9" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L9" s="49" t="s">
         <v>1</v>
@@ -7177,7 +7180,7 @@
         <v>193</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D10" s="47" t="s">
         <v>346</v>
@@ -7195,13 +7198,13 @@
         <v>340</v>
       </c>
       <c r="I10" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J10" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K10" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L10" s="49" t="s">
         <v>1</v>
@@ -7248,7 +7251,7 @@
         <v>194</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D11" s="47" t="s">
         <v>346</v>
@@ -7266,13 +7269,13 @@
         <v>340</v>
       </c>
       <c r="I11" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J11" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K11" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L11" s="49" t="s">
         <v>1</v>
@@ -7319,7 +7322,7 @@
         <v>195</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D12" s="47" t="s">
         <v>346</v>
@@ -7337,13 +7340,13 @@
         <v>340</v>
       </c>
       <c r="I12" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J12" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K12" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L12" s="49" t="s">
         <v>1</v>
@@ -7390,7 +7393,7 @@
         <v>196</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D13" s="47" t="s">
         <v>346</v>
@@ -7408,13 +7411,13 @@
         <v>340</v>
       </c>
       <c r="I13" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J13" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K13" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L13" s="49" t="s">
         <v>1</v>
@@ -7461,7 +7464,7 @@
         <v>197</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D14" s="47" t="s">
         <v>346</v>
@@ -7479,13 +7482,13 @@
         <v>340</v>
       </c>
       <c r="I14" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J14" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K14" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L14" s="49" t="s">
         <v>1</v>
@@ -7532,7 +7535,7 @@
         <v>198</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D15" s="47" t="s">
         <v>346</v>
@@ -7550,13 +7553,13 @@
         <v>340</v>
       </c>
       <c r="I15" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J15" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K15" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L15" s="49" t="s">
         <v>1</v>
@@ -7603,7 +7606,7 @@
         <v>199</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D16" s="47" t="s">
         <v>346</v>
@@ -7621,13 +7624,13 @@
         <v>340</v>
       </c>
       <c r="I16" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J16" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K16" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L16" s="49" t="s">
         <v>1</v>
@@ -7674,7 +7677,7 @@
         <v>200</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D17" s="47" t="s">
         <v>346</v>
@@ -7692,13 +7695,13 @@
         <v>340</v>
       </c>
       <c r="I17" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J17" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K17" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L17" s="49" t="s">
         <v>1</v>
@@ -7745,7 +7748,7 @@
         <v>201</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D18" s="47" t="s">
         <v>346</v>
@@ -7763,13 +7766,13 @@
         <v>340</v>
       </c>
       <c r="I18" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J18" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K18" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L18" s="49" t="s">
         <v>1</v>
@@ -7816,7 +7819,7 @@
         <v>202</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D19" s="47" t="s">
         <v>346</v>
@@ -7834,13 +7837,13 @@
         <v>340</v>
       </c>
       <c r="I19" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J19" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K19" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L19" s="49" t="s">
         <v>1</v>
@@ -7887,7 +7890,7 @@
         <v>203</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D20" s="47" t="s">
         <v>346</v>
@@ -7905,13 +7908,13 @@
         <v>340</v>
       </c>
       <c r="I20" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J20" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K20" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L20" s="49" t="s">
         <v>1</v>
@@ -7958,7 +7961,7 @@
         <v>204</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D21" s="47" t="s">
         <v>346</v>
@@ -7976,13 +7979,13 @@
         <v>340</v>
       </c>
       <c r="I21" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J21" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K21" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L21" s="49" t="s">
         <v>1</v>
@@ -8029,7 +8032,7 @@
         <v>205</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D22" s="47" t="s">
         <v>346</v>
@@ -8047,13 +8050,13 @@
         <v>340</v>
       </c>
       <c r="I22" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J22" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K22" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L22" s="49" t="s">
         <v>1</v>
@@ -8100,7 +8103,7 @@
         <v>206</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D23" s="47" t="s">
         <v>346</v>
@@ -8118,13 +8121,13 @@
         <v>340</v>
       </c>
       <c r="I23" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J23" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K23" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L23" s="49" t="s">
         <v>1</v>
@@ -8171,7 +8174,7 @@
         <v>207</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D24" s="47" t="s">
         <v>346</v>
@@ -8189,13 +8192,13 @@
         <v>340</v>
       </c>
       <c r="I24" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J24" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K24" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L24" s="49" t="s">
         <v>1</v>
@@ -8242,7 +8245,7 @@
         <v>208</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D25" s="47" t="s">
         <v>346</v>
@@ -8260,13 +8263,13 @@
         <v>340</v>
       </c>
       <c r="I25" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J25" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K25" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L25" s="49" t="s">
         <v>1</v>
@@ -8313,7 +8316,7 @@
         <v>209</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D26" s="47" t="s">
         <v>346</v>
@@ -8331,13 +8334,13 @@
         <v>340</v>
       </c>
       <c r="I26" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J26" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K26" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L26" s="49" t="s">
         <v>1</v>
@@ -8384,7 +8387,7 @@
         <v>210</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D27" s="47" t="s">
         <v>346</v>
@@ -8402,13 +8405,13 @@
         <v>340</v>
       </c>
       <c r="I27" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J27" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K27" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L27" s="49" t="s">
         <v>1</v>
@@ -8455,7 +8458,7 @@
         <v>211</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D28" s="47" t="s">
         <v>346</v>
@@ -8473,13 +8476,13 @@
         <v>340</v>
       </c>
       <c r="I28" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J28" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K28" s="48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L28" s="49" t="s">
         <v>1</v>
@@ -8526,7 +8529,7 @@
         <v>212</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D29" s="47" t="s">
         <v>346</v>
@@ -8544,13 +8547,13 @@
         <v>340</v>
       </c>
       <c r="I29" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J29" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K29" s="48" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L29" s="49" t="s">
         <v>1</v>
@@ -8597,7 +8600,7 @@
         <v>213</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D30" s="47" t="s">
         <v>346</v>
@@ -8615,13 +8618,13 @@
         <v>340</v>
       </c>
       <c r="I30" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J30" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K30" s="48" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L30" s="49" t="s">
         <v>1</v>
@@ -8668,7 +8671,7 @@
         <v>214</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D31" s="47" t="s">
         <v>346</v>
@@ -8686,13 +8689,13 @@
         <v>340</v>
       </c>
       <c r="I31" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J31" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K31" s="48" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L31" s="49" t="s">
         <v>1</v>
@@ -8739,7 +8742,7 @@
         <v>215</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D32" s="47" t="s">
         <v>346</v>
@@ -8757,13 +8760,13 @@
         <v>340</v>
       </c>
       <c r="I32" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J32" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K32" s="48" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L32" s="49" t="s">
         <v>1</v>
@@ -8810,7 +8813,7 @@
         <v>216</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D33" s="47" t="s">
         <v>346</v>
@@ -8828,13 +8831,13 @@
         <v>340</v>
       </c>
       <c r="I33" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J33" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K33" s="48" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L33" s="49" t="s">
         <v>1</v>
@@ -8881,7 +8884,7 @@
         <v>217</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D34" s="47" t="s">
         <v>346</v>
@@ -8899,13 +8902,13 @@
         <v>340</v>
       </c>
       <c r="I34" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J34" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K34" s="48" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L34" s="49" t="s">
         <v>1</v>
@@ -8952,7 +8955,7 @@
         <v>218</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D35" s="47" t="s">
         <v>346</v>
@@ -8970,13 +8973,13 @@
         <v>340</v>
       </c>
       <c r="I35" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J35" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K35" s="48" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L35" s="49" t="s">
         <v>1</v>
@@ -9020,10 +9023,10 @@
         <v>36</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D36" s="47" t="s">
         <v>346</v>
@@ -9041,13 +9044,13 @@
         <v>340</v>
       </c>
       <c r="I36" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J36" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K36" s="48" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L36" s="49" t="s">
         <v>1</v>
@@ -9094,7 +9097,7 @@
         <v>219</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D37" s="47" t="s">
         <v>346</v>
@@ -9112,13 +9115,13 @@
         <v>340</v>
       </c>
       <c r="I37" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J37" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K37" s="48" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L37" s="49" t="s">
         <v>1</v>
@@ -9165,7 +9168,7 @@
         <v>220</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D38" s="47" t="s">
         <v>346</v>
@@ -9183,13 +9186,13 @@
         <v>340</v>
       </c>
       <c r="I38" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J38" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K38" s="48" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L38" s="49" t="s">
         <v>1</v>
@@ -9236,7 +9239,7 @@
         <v>221</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D39" s="47" t="s">
         <v>346</v>
@@ -9254,13 +9257,13 @@
         <v>340</v>
       </c>
       <c r="I39" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J39" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K39" s="48" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L39" s="49" t="s">
         <v>1</v>
@@ -9307,7 +9310,7 @@
         <v>222</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D40" s="47" t="s">
         <v>346</v>
@@ -9325,13 +9328,13 @@
         <v>340</v>
       </c>
       <c r="I40" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J40" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K40" s="48" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L40" s="49" t="s">
         <v>1</v>
@@ -9378,7 +9381,7 @@
         <v>223</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D41" s="47" t="s">
         <v>346</v>
@@ -9396,13 +9399,13 @@
         <v>340</v>
       </c>
       <c r="I41" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J41" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K41" s="48" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L41" s="49" t="s">
         <v>1</v>
@@ -9449,7 +9452,7 @@
         <v>224</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D42" s="47" t="s">
         <v>346</v>
@@ -9467,13 +9470,13 @@
         <v>340</v>
       </c>
       <c r="I42" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J42" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K42" s="48" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L42" s="49" t="s">
         <v>1</v>
@@ -9520,7 +9523,7 @@
         <v>225</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D43" s="47" t="s">
         <v>346</v>
@@ -9538,13 +9541,13 @@
         <v>340</v>
       </c>
       <c r="I43" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J43" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K43" s="48" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L43" s="49" t="s">
         <v>1</v>
@@ -9591,7 +9594,7 @@
         <v>226</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D44" s="47" t="s">
         <v>346</v>
@@ -9609,13 +9612,13 @@
         <v>340</v>
       </c>
       <c r="I44" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J44" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K44" s="48" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L44" s="49" t="s">
         <v>1</v>
@@ -9662,7 +9665,7 @@
         <v>227</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D45" s="47" t="s">
         <v>346</v>
@@ -9680,13 +9683,13 @@
         <v>340</v>
       </c>
       <c r="I45" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J45" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K45" s="48" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L45" s="49" t="s">
         <v>1</v>
@@ -9733,7 +9736,7 @@
         <v>228</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D46" s="47" t="s">
         <v>346</v>
@@ -9751,13 +9754,13 @@
         <v>340</v>
       </c>
       <c r="I46" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J46" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K46" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L46" s="49" t="s">
         <v>1</v>
@@ -9804,7 +9807,7 @@
         <v>229</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D47" s="47" t="s">
         <v>346</v>
@@ -9822,13 +9825,13 @@
         <v>340</v>
       </c>
       <c r="I47" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J47" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K47" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L47" s="49" t="s">
         <v>1</v>
@@ -9875,7 +9878,7 @@
         <v>230</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D48" s="47" t="s">
         <v>346</v>
@@ -9893,13 +9896,13 @@
         <v>340</v>
       </c>
       <c r="I48" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J48" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K48" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L48" s="49" t="s">
         <v>1</v>
@@ -9946,7 +9949,7 @@
         <v>231</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D49" s="47" t="s">
         <v>346</v>
@@ -9964,13 +9967,13 @@
         <v>340</v>
       </c>
       <c r="I49" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J49" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K49" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L49" s="49" t="s">
         <v>1</v>
@@ -10017,7 +10020,7 @@
         <v>232</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D50" s="47" t="s">
         <v>346</v>
@@ -10035,13 +10038,13 @@
         <v>340</v>
       </c>
       <c r="I50" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J50" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K50" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L50" s="49" t="s">
         <v>1</v>
@@ -10088,7 +10091,7 @@
         <v>233</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D51" s="47" t="s">
         <v>346</v>
@@ -10106,13 +10109,13 @@
         <v>340</v>
       </c>
       <c r="I51" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J51" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K51" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L51" s="49" t="s">
         <v>1</v>
@@ -10159,7 +10162,7 @@
         <v>234</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D52" s="47" t="s">
         <v>346</v>
@@ -10177,13 +10180,13 @@
         <v>340</v>
       </c>
       <c r="I52" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J52" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K52" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L52" s="49" t="s">
         <v>1</v>
@@ -10230,7 +10233,7 @@
         <v>235</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D53" s="47" t="s">
         <v>346</v>
@@ -10248,13 +10251,13 @@
         <v>340</v>
       </c>
       <c r="I53" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J53" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K53" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L53" s="49" t="s">
         <v>1</v>
@@ -10301,7 +10304,7 @@
         <v>236</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D54" s="47" t="s">
         <v>346</v>
@@ -10319,13 +10322,13 @@
         <v>340</v>
       </c>
       <c r="I54" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J54" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K54" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L54" s="49" t="s">
         <v>1</v>
@@ -10372,7 +10375,7 @@
         <v>237</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D55" s="47" t="s">
         <v>346</v>
@@ -10390,13 +10393,13 @@
         <v>340</v>
       </c>
       <c r="I55" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J55" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K55" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L55" s="49" t="s">
         <v>1</v>
@@ -10443,7 +10446,7 @@
         <v>238</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D56" s="47" t="s">
         <v>346</v>
@@ -10461,13 +10464,13 @@
         <v>340</v>
       </c>
       <c r="I56" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J56" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K56" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L56" s="49" t="s">
         <v>1</v>
@@ -10514,7 +10517,7 @@
         <v>239</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D57" s="47" t="s">
         <v>346</v>
@@ -10532,13 +10535,13 @@
         <v>340</v>
       </c>
       <c r="I57" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J57" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K57" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L57" s="49" t="s">
         <v>1</v>
@@ -10585,7 +10588,7 @@
         <v>240</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D58" s="47" t="s">
         <v>346</v>
@@ -10603,13 +10606,13 @@
         <v>340</v>
       </c>
       <c r="I58" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J58" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K58" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L58" s="49" t="s">
         <v>1</v>
@@ -10656,7 +10659,7 @@
         <v>241</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D59" s="47" t="s">
         <v>346</v>
@@ -10674,13 +10677,13 @@
         <v>340</v>
       </c>
       <c r="I59" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J59" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K59" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L59" s="49" t="s">
         <v>1</v>
@@ -10727,7 +10730,7 @@
         <v>242</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D60" s="47" t="s">
         <v>346</v>
@@ -10745,13 +10748,13 @@
         <v>340</v>
       </c>
       <c r="I60" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J60" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K60" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L60" s="49" t="s">
         <v>1</v>
@@ -10798,7 +10801,7 @@
         <v>243</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D61" s="47" t="s">
         <v>346</v>
@@ -10816,13 +10819,13 @@
         <v>340</v>
       </c>
       <c r="I61" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J61" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K61" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L61" s="49" t="s">
         <v>1</v>
@@ -10869,7 +10872,7 @@
         <v>244</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D62" s="47" t="s">
         <v>346</v>
@@ -10887,13 +10890,13 @@
         <v>340</v>
       </c>
       <c r="I62" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J62" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K62" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L62" s="49" t="s">
         <v>1</v>
@@ -10940,7 +10943,7 @@
         <v>245</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D63" s="47" t="s">
         <v>346</v>
@@ -10958,13 +10961,13 @@
         <v>340</v>
       </c>
       <c r="I63" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J63" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K63" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L63" s="49" t="s">
         <v>1</v>
@@ -11011,7 +11014,7 @@
         <v>246</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D64" s="47" t="s">
         <v>346</v>
@@ -11029,13 +11032,13 @@
         <v>340</v>
       </c>
       <c r="I64" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J64" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K64" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L64" s="49" t="s">
         <v>1</v>
@@ -11082,7 +11085,7 @@
         <v>247</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D65" s="47" t="s">
         <v>346</v>
@@ -11100,13 +11103,13 @@
         <v>340</v>
       </c>
       <c r="I65" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J65" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K65" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L65" s="49" t="s">
         <v>1</v>
@@ -11153,7 +11156,7 @@
         <v>248</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D66" s="47" t="s">
         <v>346</v>
@@ -11171,13 +11174,13 @@
         <v>340</v>
       </c>
       <c r="I66" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J66" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K66" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L66" s="49" t="s">
         <v>1</v>
@@ -11224,7 +11227,7 @@
         <v>249</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D67" s="47" t="s">
         <v>346</v>
@@ -11242,13 +11245,13 @@
         <v>340</v>
       </c>
       <c r="I67" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J67" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K67" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L67" s="49" t="s">
         <v>1</v>
@@ -11295,7 +11298,7 @@
         <v>250</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D68" s="47" t="s">
         <v>346</v>
@@ -11313,13 +11316,13 @@
         <v>340</v>
       </c>
       <c r="I68" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J68" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K68" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L68" s="49" t="s">
         <v>1</v>
@@ -11366,7 +11369,7 @@
         <v>251</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D69" s="47" t="s">
         <v>346</v>
@@ -11384,13 +11387,13 @@
         <v>340</v>
       </c>
       <c r="I69" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J69" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K69" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L69" s="49" t="s">
         <v>1</v>
@@ -11437,7 +11440,7 @@
         <v>252</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D70" s="47" t="s">
         <v>346</v>
@@ -11455,13 +11458,13 @@
         <v>340</v>
       </c>
       <c r="I70" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J70" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K70" s="48" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L70" s="49" t="s">
         <v>1</v>
@@ -11508,7 +11511,7 @@
         <v>253</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D71" s="47" t="s">
         <v>346</v>
@@ -11526,13 +11529,13 @@
         <v>340</v>
       </c>
       <c r="I71" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J71" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K71" s="48" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L71" s="49" t="s">
         <v>1</v>
@@ -11579,7 +11582,7 @@
         <v>254</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D72" s="47" t="s">
         <v>346</v>
@@ -11597,13 +11600,13 @@
         <v>340</v>
       </c>
       <c r="I72" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J72" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K72" s="48" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L72" s="49" t="s">
         <v>1</v>
@@ -11650,7 +11653,7 @@
         <v>255</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D73" s="47" t="s">
         <v>346</v>
@@ -11668,13 +11671,13 @@
         <v>340</v>
       </c>
       <c r="I73" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J73" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K73" s="48" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L73" s="49" t="s">
         <v>1</v>
@@ -11721,7 +11724,7 @@
         <v>256</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D74" s="47" t="s">
         <v>346</v>
@@ -11739,13 +11742,13 @@
         <v>340</v>
       </c>
       <c r="I74" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J74" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K74" s="48" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L74" s="49" t="s">
         <v>1</v>
@@ -11792,7 +11795,7 @@
         <v>257</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D75" s="47" t="s">
         <v>346</v>
@@ -11810,13 +11813,13 @@
         <v>340</v>
       </c>
       <c r="I75" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J75" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K75" s="48" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L75" s="49" t="s">
         <v>1</v>
@@ -11863,7 +11866,7 @@
         <v>258</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D76" s="47" t="s">
         <v>346</v>
@@ -11881,13 +11884,13 @@
         <v>340</v>
       </c>
       <c r="I76" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J76" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K76" s="48" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L76" s="49" t="s">
         <v>1</v>
@@ -11934,7 +11937,7 @@
         <v>259</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D77" s="47" t="s">
         <v>346</v>
@@ -11952,13 +11955,13 @@
         <v>340</v>
       </c>
       <c r="I77" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J77" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K77" s="48" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L77" s="49" t="s">
         <v>1</v>
@@ -12005,7 +12008,7 @@
         <v>260</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D78" s="47" t="s">
         <v>346</v>
@@ -12023,13 +12026,13 @@
         <v>340</v>
       </c>
       <c r="I78" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J78" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K78" s="48" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L78" s="49" t="s">
         <v>1</v>
@@ -12076,7 +12079,7 @@
         <v>261</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D79" s="47" t="s">
         <v>346</v>
@@ -12094,13 +12097,13 @@
         <v>340</v>
       </c>
       <c r="I79" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J79" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K79" s="48" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L79" s="49" t="s">
         <v>1</v>
@@ -12147,7 +12150,7 @@
         <v>262</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D80" s="47" t="s">
         <v>346</v>
@@ -12165,13 +12168,13 @@
         <v>340</v>
       </c>
       <c r="I80" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J80" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K80" s="48" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L80" s="49" t="s">
         <v>1</v>
@@ -12218,7 +12221,7 @@
         <v>263</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D81" s="47" t="s">
         <v>346</v>
@@ -12236,13 +12239,13 @@
         <v>340</v>
       </c>
       <c r="I81" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J81" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K81" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L81" s="49" t="s">
         <v>1</v>
@@ -12289,7 +12292,7 @@
         <v>264</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D82" s="47" t="s">
         <v>346</v>
@@ -12307,13 +12310,13 @@
         <v>340</v>
       </c>
       <c r="I82" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J82" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K82" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L82" s="49" t="s">
         <v>1</v>
@@ -12360,7 +12363,7 @@
         <v>265</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D83" s="47" t="s">
         <v>346</v>
@@ -12378,13 +12381,13 @@
         <v>340</v>
       </c>
       <c r="I83" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J83" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K83" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L83" s="49" t="s">
         <v>1</v>
@@ -12431,7 +12434,7 @@
         <v>266</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D84" s="47" t="s">
         <v>346</v>
@@ -12449,13 +12452,13 @@
         <v>340</v>
       </c>
       <c r="I84" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J84" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K84" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L84" s="49" t="s">
         <v>1</v>
@@ -12502,7 +12505,7 @@
         <v>267</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D85" s="47" t="s">
         <v>346</v>
@@ -12520,13 +12523,13 @@
         <v>340</v>
       </c>
       <c r="I85" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J85" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K85" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L85" s="49" t="s">
         <v>1</v>
@@ -12573,7 +12576,7 @@
         <v>268</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D86" s="47" t="s">
         <v>346</v>
@@ -12591,13 +12594,13 @@
         <v>340</v>
       </c>
       <c r="I86" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J86" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K86" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L86" s="49" t="s">
         <v>1</v>
@@ -12644,7 +12647,7 @@
         <v>269</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D87" s="47" t="s">
         <v>346</v>
@@ -12662,13 +12665,13 @@
         <v>340</v>
       </c>
       <c r="I87" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J87" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K87" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L87" s="49" t="s">
         <v>1</v>
@@ -12715,7 +12718,7 @@
         <v>270</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D88" s="47" t="s">
         <v>346</v>
@@ -12733,13 +12736,13 @@
         <v>340</v>
       </c>
       <c r="I88" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J88" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K88" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L88" s="49" t="s">
         <v>1</v>
@@ -12786,7 +12789,7 @@
         <v>271</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D89" s="47" t="s">
         <v>346</v>
@@ -12804,13 +12807,13 @@
         <v>340</v>
       </c>
       <c r="I89" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J89" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K89" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L89" s="49" t="s">
         <v>1</v>
@@ -12857,7 +12860,7 @@
         <v>272</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D90" s="47" t="s">
         <v>346</v>
@@ -12875,13 +12878,13 @@
         <v>340</v>
       </c>
       <c r="I90" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J90" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K90" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L90" s="49" t="s">
         <v>1</v>
@@ -12928,7 +12931,7 @@
         <v>273</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D91" s="47" t="s">
         <v>346</v>
@@ -12946,13 +12949,13 @@
         <v>340</v>
       </c>
       <c r="I91" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J91" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K91" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L91" s="49" t="s">
         <v>1</v>
@@ -12999,7 +13002,7 @@
         <v>274</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D92" s="47" t="s">
         <v>346</v>
@@ -13017,13 +13020,13 @@
         <v>340</v>
       </c>
       <c r="I92" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J92" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K92" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L92" s="49" t="s">
         <v>1</v>
@@ -13070,7 +13073,7 @@
         <v>275</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D93" s="47" t="s">
         <v>346</v>
@@ -13088,13 +13091,13 @@
         <v>340</v>
       </c>
       <c r="I93" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J93" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K93" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L93" s="49" t="s">
         <v>1</v>
@@ -13141,7 +13144,7 @@
         <v>276</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D94" s="47" t="s">
         <v>346</v>
@@ -13159,13 +13162,13 @@
         <v>340</v>
       </c>
       <c r="I94" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J94" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K94" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L94" s="49" t="s">
         <v>1</v>
@@ -13212,7 +13215,7 @@
         <v>277</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D95" s="47" t="s">
         <v>346</v>
@@ -13230,13 +13233,13 @@
         <v>340</v>
       </c>
       <c r="I95" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J95" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K95" s="48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L95" s="49" t="s">
         <v>1</v>
@@ -13283,7 +13286,7 @@
         <v>278</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D96" s="47" t="s">
         <v>346</v>
@@ -13301,13 +13304,13 @@
         <v>340</v>
       </c>
       <c r="I96" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J96" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K96" s="48" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L96" s="49" t="s">
         <v>1</v>
@@ -13354,7 +13357,7 @@
         <v>279</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D97" s="47" t="s">
         <v>346</v>
@@ -13372,13 +13375,13 @@
         <v>340</v>
       </c>
       <c r="I97" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J97" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K97" s="48" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L97" s="49" t="s">
         <v>1</v>
@@ -13425,7 +13428,7 @@
         <v>280</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D98" s="47" t="s">
         <v>346</v>
@@ -13443,13 +13446,13 @@
         <v>340</v>
       </c>
       <c r="I98" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J98" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K98" s="48" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L98" s="49" t="s">
         <v>1</v>
@@ -13496,7 +13499,7 @@
         <v>281</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D99" s="47" t="s">
         <v>346</v>
@@ -13514,13 +13517,13 @@
         <v>340</v>
       </c>
       <c r="I99" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J99" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K99" s="48" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L99" s="49" t="s">
         <v>1</v>
@@ -13567,7 +13570,7 @@
         <v>282</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D100" s="47" t="s">
         <v>346</v>
@@ -13585,13 +13588,13 @@
         <v>340</v>
       </c>
       <c r="I100" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J100" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K100" s="48" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L100" s="49" t="s">
         <v>1</v>
@@ -13638,7 +13641,7 @@
         <v>283</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D101" s="47" t="s">
         <v>346</v>
@@ -13656,13 +13659,13 @@
         <v>340</v>
       </c>
       <c r="I101" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J101" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K101" s="48" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L101" s="49" t="s">
         <v>1</v>
@@ -13709,7 +13712,7 @@
         <v>284</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D102" s="47" t="s">
         <v>346</v>
@@ -13727,13 +13730,13 @@
         <v>340</v>
       </c>
       <c r="I102" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J102" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K102" s="48" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L102" s="49" t="s">
         <v>1</v>
@@ -13780,7 +13783,7 @@
         <v>285</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D103" s="47" t="s">
         <v>346</v>
@@ -13798,13 +13801,13 @@
         <v>340</v>
       </c>
       <c r="I103" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J103" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K103" s="48" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L103" s="49" t="s">
         <v>1</v>
@@ -13851,7 +13854,7 @@
         <v>286</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D104" s="47" t="s">
         <v>346</v>
@@ -13869,13 +13872,13 @@
         <v>340</v>
       </c>
       <c r="I104" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J104" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K104" s="48" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L104" s="49" t="s">
         <v>1</v>
@@ -13922,7 +13925,7 @@
         <v>287</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D105" s="47" t="s">
         <v>346</v>
@@ -13940,13 +13943,13 @@
         <v>340</v>
       </c>
       <c r="I105" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J105" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K105" s="48" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L105" s="49" t="s">
         <v>1</v>
@@ -13993,7 +13996,7 @@
         <v>288</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D106" s="47" t="s">
         <v>346</v>
@@ -14011,13 +14014,13 @@
         <v>340</v>
       </c>
       <c r="I106" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J106" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K106" s="48" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L106" s="49" t="s">
         <v>1</v>
@@ -14064,7 +14067,7 @@
         <v>289</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D107" s="47" t="s">
         <v>346</v>
@@ -14082,13 +14085,13 @@
         <v>340</v>
       </c>
       <c r="I107" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J107" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K107" s="48" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L107" s="49" t="s">
         <v>1</v>
@@ -14135,7 +14138,7 @@
         <v>290</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D108" s="47" t="s">
         <v>346</v>
@@ -14153,13 +14156,13 @@
         <v>340</v>
       </c>
       <c r="I108" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J108" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K108" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L108" s="49" t="s">
         <v>1</v>
@@ -14206,7 +14209,7 @@
         <v>291</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D109" s="47" t="s">
         <v>346</v>
@@ -14224,13 +14227,13 @@
         <v>340</v>
       </c>
       <c r="I109" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J109" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K109" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L109" s="49" t="s">
         <v>1</v>
@@ -14277,7 +14280,7 @@
         <v>292</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D110" s="47" t="s">
         <v>346</v>
@@ -14295,13 +14298,13 @@
         <v>340</v>
       </c>
       <c r="I110" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J110" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K110" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L110" s="49" t="s">
         <v>1</v>
@@ -14348,7 +14351,7 @@
         <v>293</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D111" s="47" t="s">
         <v>346</v>
@@ -14366,13 +14369,13 @@
         <v>340</v>
       </c>
       <c r="I111" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J111" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K111" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L111" s="49" t="s">
         <v>1</v>
@@ -14419,7 +14422,7 @@
         <v>294</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D112" s="47" t="s">
         <v>346</v>
@@ -14437,13 +14440,13 @@
         <v>340</v>
       </c>
       <c r="I112" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J112" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K112" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L112" s="49" t="s">
         <v>1</v>
@@ -14490,7 +14493,7 @@
         <v>295</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D113" s="47" t="s">
         <v>346</v>
@@ -14508,13 +14511,13 @@
         <v>340</v>
       </c>
       <c r="I113" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J113" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K113" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L113" s="49" t="s">
         <v>1</v>
@@ -14561,7 +14564,7 @@
         <v>296</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D114" s="47" t="s">
         <v>346</v>
@@ -14579,13 +14582,13 @@
         <v>340</v>
       </c>
       <c r="I114" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J114" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K114" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L114" s="49" t="s">
         <v>1</v>
@@ -14632,7 +14635,7 @@
         <v>297</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D115" s="47" t="s">
         <v>346</v>
@@ -14650,13 +14653,13 @@
         <v>340</v>
       </c>
       <c r="I115" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J115" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K115" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L115" s="49" t="s">
         <v>1</v>
@@ -14703,7 +14706,7 @@
         <v>298</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D116" s="47" t="s">
         <v>346</v>
@@ -14721,13 +14724,13 @@
         <v>340</v>
       </c>
       <c r="I116" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J116" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K116" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L116" s="49" t="s">
         <v>1</v>
@@ -14774,7 +14777,7 @@
         <v>299</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D117" s="47" t="s">
         <v>346</v>
@@ -14792,13 +14795,13 @@
         <v>340</v>
       </c>
       <c r="I117" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J117" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K117" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L117" s="49" t="s">
         <v>1</v>
@@ -14845,7 +14848,7 @@
         <v>300</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D118" s="47" t="s">
         <v>346</v>
@@ -14863,13 +14866,13 @@
         <v>340</v>
       </c>
       <c r="I118" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J118" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K118" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L118" s="49" t="s">
         <v>1</v>
@@ -14916,7 +14919,7 @@
         <v>301</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D119" s="47" t="s">
         <v>346</v>
@@ -14934,13 +14937,13 @@
         <v>340</v>
       </c>
       <c r="I119" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J119" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K119" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L119" s="49" t="s">
         <v>1</v>
@@ -14987,7 +14990,7 @@
         <v>302</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D120" s="47" t="s">
         <v>346</v>
@@ -15005,13 +15008,13 @@
         <v>340</v>
       </c>
       <c r="I120" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J120" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K120" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L120" s="49" t="s">
         <v>1</v>
@@ -15058,7 +15061,7 @@
         <v>303</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D121" s="47" t="s">
         <v>346</v>
@@ -15076,13 +15079,13 @@
         <v>340</v>
       </c>
       <c r="I121" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J121" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K121" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L121" s="49" t="s">
         <v>1</v>
@@ -15129,7 +15132,7 @@
         <v>304</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D122" s="47" t="s">
         <v>346</v>
@@ -15147,13 +15150,13 @@
         <v>340</v>
       </c>
       <c r="I122" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J122" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K122" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L122" s="49" t="s">
         <v>1</v>
@@ -15200,7 +15203,7 @@
         <v>305</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D123" s="47" t="s">
         <v>346</v>
@@ -15218,13 +15221,13 @@
         <v>340</v>
       </c>
       <c r="I123" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J123" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K123" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L123" s="49" t="s">
         <v>1</v>
@@ -15271,7 +15274,7 @@
         <v>306</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D124" s="47" t="s">
         <v>346</v>
@@ -15289,13 +15292,13 @@
         <v>340</v>
       </c>
       <c r="I124" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J124" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K124" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L124" s="49" t="s">
         <v>1</v>
@@ -15342,7 +15345,7 @@
         <v>307</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D125" s="47" t="s">
         <v>346</v>
@@ -15360,13 +15363,13 @@
         <v>340</v>
       </c>
       <c r="I125" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J125" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K125" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L125" s="49" t="s">
         <v>1</v>
@@ -15413,7 +15416,7 @@
         <v>308</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D126" s="47" t="s">
         <v>346</v>
@@ -15431,13 +15434,13 @@
         <v>340</v>
       </c>
       <c r="I126" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J126" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K126" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L126" s="49" t="s">
         <v>1</v>
@@ -15484,7 +15487,7 @@
         <v>309</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D127" s="47" t="s">
         <v>346</v>
@@ -15502,13 +15505,13 @@
         <v>340</v>
       </c>
       <c r="I127" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J127" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K127" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L127" s="49" t="s">
         <v>1</v>
@@ -15555,7 +15558,7 @@
         <v>310</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D128" s="47" t="s">
         <v>346</v>
@@ -15573,13 +15576,13 @@
         <v>340</v>
       </c>
       <c r="I128" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J128" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K128" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L128" s="49" t="s">
         <v>1</v>
@@ -15626,7 +15629,7 @@
         <v>311</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D129" s="47" t="s">
         <v>346</v>
@@ -15644,13 +15647,13 @@
         <v>340</v>
       </c>
       <c r="I129" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J129" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K129" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L129" s="49" t="s">
         <v>1</v>
@@ -15697,7 +15700,7 @@
         <v>312</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D130" s="47" t="s">
         <v>346</v>
@@ -15715,13 +15718,13 @@
         <v>340</v>
       </c>
       <c r="I130" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J130" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K130" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L130" s="49" t="s">
         <v>1</v>
@@ -15768,7 +15771,7 @@
         <v>313</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D131" s="47" t="s">
         <v>346</v>
@@ -15786,13 +15789,13 @@
         <v>340</v>
       </c>
       <c r="I131" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J131" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K131" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L131" s="49" t="s">
         <v>1</v>
@@ -15839,7 +15842,7 @@
         <v>314</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D132" s="47" t="s">
         <v>346</v>
@@ -15857,13 +15860,13 @@
         <v>340</v>
       </c>
       <c r="I132" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J132" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K132" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L132" s="49" t="s">
         <v>1</v>
@@ -15910,7 +15913,7 @@
         <v>315</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D133" s="47" t="s">
         <v>346</v>
@@ -15928,13 +15931,13 @@
         <v>340</v>
       </c>
       <c r="I133" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J133" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K133" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L133" s="49" t="s">
         <v>1</v>
@@ -15981,7 +15984,7 @@
         <v>316</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D134" s="47" t="s">
         <v>346</v>
@@ -15999,13 +16002,13 @@
         <v>340</v>
       </c>
       <c r="I134" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J134" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K134" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L134" s="49" t="s">
         <v>1</v>
@@ -16052,7 +16055,7 @@
         <v>317</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D135" s="47" t="s">
         <v>346</v>
@@ -16070,13 +16073,13 @@
         <v>340</v>
       </c>
       <c r="I135" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J135" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K135" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L135" s="49" t="s">
         <v>1</v>
@@ -16123,7 +16126,7 @@
         <v>318</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D136" s="47" t="s">
         <v>346</v>
@@ -16141,13 +16144,13 @@
         <v>340</v>
       </c>
       <c r="I136" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J136" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K136" s="48" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L136" s="49" t="s">
         <v>1</v>
@@ -16194,7 +16197,7 @@
         <v>319</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D137" s="47" t="s">
         <v>346</v>
@@ -16212,13 +16215,13 @@
         <v>340</v>
       </c>
       <c r="I137" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J137" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K137" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L137" s="49" t="s">
         <v>1</v>
@@ -16265,7 +16268,7 @@
         <v>320</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D138" s="47" t="s">
         <v>346</v>
@@ -16283,13 +16286,13 @@
         <v>340</v>
       </c>
       <c r="I138" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J138" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K138" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L138" s="49" t="s">
         <v>1</v>
@@ -16336,7 +16339,7 @@
         <v>321</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D139" s="47" t="s">
         <v>346</v>
@@ -16354,13 +16357,13 @@
         <v>340</v>
       </c>
       <c r="I139" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J139" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K139" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L139" s="49" t="s">
         <v>1</v>
@@ -16407,7 +16410,7 @@
         <v>322</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D140" s="47" t="s">
         <v>346</v>
@@ -16425,13 +16428,13 @@
         <v>340</v>
       </c>
       <c r="I140" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J140" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K140" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L140" s="49" t="s">
         <v>1</v>
@@ -16478,7 +16481,7 @@
         <v>323</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D141" s="47" t="s">
         <v>346</v>
@@ -16496,13 +16499,13 @@
         <v>340</v>
       </c>
       <c r="I141" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J141" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K141" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L141" s="49" t="s">
         <v>1</v>
@@ -16549,7 +16552,7 @@
         <v>324</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D142" s="47" t="s">
         <v>346</v>
@@ -16567,13 +16570,13 @@
         <v>340</v>
       </c>
       <c r="I142" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J142" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K142" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L142" s="49" t="s">
         <v>1</v>
@@ -16620,7 +16623,7 @@
         <v>325</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D143" s="47" t="s">
         <v>346</v>
@@ -16638,13 +16641,13 @@
         <v>340</v>
       </c>
       <c r="I143" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J143" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K143" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L143" s="49" t="s">
         <v>1</v>
@@ -16688,10 +16691,10 @@
         <v>144</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D144" s="47" t="s">
         <v>346</v>
@@ -16709,13 +16712,13 @@
         <v>340</v>
       </c>
       <c r="I144" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J144" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K144" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L144" s="49" t="s">
         <v>1</v>
@@ -16762,7 +16765,7 @@
         <v>326</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D145" s="47" t="s">
         <v>346</v>
@@ -16780,13 +16783,13 @@
         <v>340</v>
       </c>
       <c r="I145" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J145" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K145" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L145" s="49" t="s">
         <v>1</v>
@@ -16833,7 +16836,7 @@
         <v>327</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D146" s="47" t="s">
         <v>346</v>
@@ -16851,13 +16854,13 @@
         <v>340</v>
       </c>
       <c r="I146" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J146" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K146" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L146" s="49" t="s">
         <v>1</v>
@@ -16904,7 +16907,7 @@
         <v>328</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D147" s="47" t="s">
         <v>346</v>
@@ -16922,13 +16925,13 @@
         <v>340</v>
       </c>
       <c r="I147" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J147" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K147" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L147" s="49" t="s">
         <v>1</v>
@@ -16975,7 +16978,7 @@
         <v>329</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D148" s="47" t="s">
         <v>346</v>
@@ -16993,13 +16996,13 @@
         <v>340</v>
       </c>
       <c r="I148" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J148" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K148" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L148" s="49" t="s">
         <v>1</v>
@@ -17046,7 +17049,7 @@
         <v>330</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D149" s="47" t="s">
         <v>346</v>
@@ -17064,13 +17067,13 @@
         <v>340</v>
       </c>
       <c r="I149" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J149" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K149" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L149" s="49" t="s">
         <v>1</v>
@@ -17117,7 +17120,7 @@
         <v>331</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D150" s="47" t="s">
         <v>346</v>
@@ -17135,13 +17138,13 @@
         <v>340</v>
       </c>
       <c r="I150" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J150" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K150" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L150" s="49" t="s">
         <v>1</v>
@@ -17188,7 +17191,7 @@
         <v>332</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D151" s="47" t="s">
         <v>346</v>
@@ -17206,13 +17209,13 @@
         <v>340</v>
       </c>
       <c r="I151" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J151" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K151" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L151" s="49" t="s">
         <v>1</v>
@@ -17259,7 +17262,7 @@
         <v>333</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D152" s="47" t="s">
         <v>346</v>
@@ -17277,13 +17280,13 @@
         <v>340</v>
       </c>
       <c r="I152" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J152" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K152" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L152" s="49" t="s">
         <v>1</v>
@@ -17330,7 +17333,7 @@
         <v>334</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D153" s="47" t="s">
         <v>346</v>
@@ -17348,13 +17351,13 @@
         <v>340</v>
       </c>
       <c r="I153" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J153" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K153" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L153" s="49" t="s">
         <v>1</v>
@@ -17401,7 +17404,7 @@
         <v>335</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D154" s="47" t="s">
         <v>346</v>
@@ -17419,13 +17422,13 @@
         <v>340</v>
       </c>
       <c r="I154" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J154" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K154" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L154" s="49" t="s">
         <v>1</v>
@@ -17472,7 +17475,7 @@
         <v>336</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D155" s="47" t="s">
         <v>346</v>
@@ -17490,13 +17493,13 @@
         <v>340</v>
       </c>
       <c r="I155" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J155" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K155" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L155" s="49" t="s">
         <v>1</v>
@@ -17543,7 +17546,7 @@
         <v>337</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D156" s="47" t="s">
         <v>346</v>
@@ -17561,13 +17564,13 @@
         <v>340</v>
       </c>
       <c r="I156" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J156" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K156" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L156" s="49" t="s">
         <v>1</v>
@@ -17614,7 +17617,7 @@
         <v>338</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D157" s="47" t="s">
         <v>346</v>
@@ -17632,13 +17635,13 @@
         <v>340</v>
       </c>
       <c r="I157" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J157" s="47" t="s">
         <v>416</v>
       </c>
       <c r="K157" s="48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L157" s="49" t="s">
         <v>1</v>

--- a/Versão5/ABNT/Ontologia_15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2N.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C63CCEB-578F-4629-8A32-D5CB61F54FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -2180,84 +2180,6 @@
     <dxf>
       <font>
         <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond Light"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor rgb="FFFFDE75"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
@@ -2344,84 +2266,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond Light"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor rgb="FFFFDE75"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -3773,6 +3617,162 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF2CB"/>
+          <bgColor rgb="FFFFDE75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF2CB"/>
+          <bgColor rgb="FFFFDE75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -4074,28 +4074,28 @@
     <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="59" dataDxfId="58"/>
     <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="57" dataDxfId="56"/>
     <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="1" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="13" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="17" dataDxfId="16"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="13" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="11" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4420,15 +4420,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03763A90-6A45-4DA0-A35B-2601294A84FF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" style="45" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.6640625" style="45" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" style="45" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.69921875" style="45" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" style="45" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="11" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>168</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>169</v>
       </c>
@@ -4461,7 +4461,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -4472,7 +4472,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>9</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>170</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>172</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>173</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -4562,7 +4562,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>174</v>
       </c>
@@ -4573,7 +4573,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>175</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>176</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>177</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -4617,19 +4617,19 @@
         <v>408</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>178</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46148.624876273148</v>
+        <v>46157.683343518518</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>419</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>415</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="41" t="s">
         <v>420</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>167</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>179</v>
       </c>
@@ -4686,7 +4686,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>184</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>186</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41" t="s">
         <v>404</v>
       </c>
@@ -4728,26 +4728,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958751C2-A34E-4345-8D6A-082603A025F9}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA19"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="6.83203125" style="36" customWidth="1"/>
+    <col min="1" max="1" width="2.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="6.796875" style="36" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="36" customWidth="1"/>
-    <col min="7" max="11" width="8.6640625" style="36" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.69921875" style="36" bestFit="1" customWidth="1"/>
     <col min="12" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="42.6640625" customWidth="1"/>
-    <col min="17" max="17" width="44.33203125" customWidth="1"/>
-    <col min="18" max="18" width="5.83203125" customWidth="1"/>
+    <col min="16" max="16" width="42.69921875" customWidth="1"/>
+    <col min="17" max="17" width="44.296875" customWidth="1"/>
+    <col min="18" max="18" width="5.796875" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="6.6640625" customWidth="1"/>
-    <col min="21" max="21" width="5.83203125" customWidth="1"/>
-    <col min="22" max="22" width="8.1640625" customWidth="1"/>
-    <col min="23" max="23" width="8.6640625" customWidth="1"/>
+    <col min="20" max="20" width="6.69921875" customWidth="1"/>
+    <col min="21" max="21" width="5.796875" customWidth="1"/>
+    <col min="22" max="22" width="8.19921875" customWidth="1"/>
+    <col min="23" max="23" width="8.69921875" customWidth="1"/>
     <col min="26" max="26" width="6" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="37.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="37.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="57.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="30.9" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>349</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="51">
         <v>2</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="51">
         <v>3</v>
       </c>
@@ -5012,7 +5012,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="51">
         <v>4</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="51">
         <v>5</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="51">
         <v>6</v>
       </c>
@@ -5285,7 +5285,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="51">
         <v>7</v>
       </c>
@@ -5376,7 +5376,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="51">
         <v>8</v>
       </c>
@@ -5467,7 +5467,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="51">
         <v>9</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="51">
         <v>10</v>
       </c>
@@ -5649,7 +5649,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="51">
         <v>11</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="51">
         <v>12</v>
       </c>
@@ -5831,7 +5831,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="51">
         <v>13</v>
       </c>
@@ -5922,7 +5922,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="51">
         <v>14</v>
       </c>
@@ -6013,7 +6013,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="51">
         <v>15</v>
       </c>
@@ -6104,7 +6104,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="51">
         <v>16</v>
       </c>
@@ -6195,7 +6195,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="51">
         <v>17</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="51">
         <v>18</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="51">
         <v>19</v>
       </c>
@@ -6470,18 +6470,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A19">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA19">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6496,13 +6496,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B4A051-97A0-4486-9B30-1861C9F77522}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.296875" defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="21" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="24.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="23.15" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>350</v>
       </c>
@@ -6567,7 +6567,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="29">
         <v>2</v>
       </c>
@@ -6634,7 +6634,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6649,13 +6649,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78CA1C4B-37EB-4980-B878-E43323BA46B5}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="32">
         <v>1</v>
       </c>
@@ -6666,7 +6666,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -6679,7 +6679,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6691,30 +6691,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y157"/>
-  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.296875" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="50" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.19921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.296875" style="50" customWidth="1"/>
     <col min="7" max="7" width="10" style="50" customWidth="1"/>
-    <col min="8" max="9" width="7.33203125" style="50" customWidth="1"/>
-    <col min="10" max="10" width="4.33203125" style="50" customWidth="1"/>
+    <col min="8" max="9" width="7.296875" style="50" customWidth="1"/>
+    <col min="10" max="10" width="4.296875" style="50" customWidth="1"/>
     <col min="11" max="11" width="14" style="50" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.5" style="50" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.1640625" style="50" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.19921875" style="50" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7" style="50" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.6640625" style="50" customWidth="1"/>
+    <col min="15" max="15" width="43.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.69921875" style="50" customWidth="1"/>
     <col min="17" max="17" width="5" style="50" customWidth="1"/>
     <col min="18" max="18" width="5.5" style="50" customWidth="1"/>
     <col min="19" max="25" width="5" style="50" customWidth="1"/>
-    <col min="26" max="16384" width="11.33203125" style="2"/>
+    <col min="26" max="16384" width="11.296875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>180</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>2</v>
       </c>
@@ -6864,7 +6864,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>3</v>
       </c>
@@ -6941,7 +6941,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>4</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>5</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>6</v>
       </c>
@@ -7172,7 +7172,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>7</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>8</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>9</v>
       </c>
@@ -7403,7 +7403,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>10</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>11</v>
       </c>
@@ -7557,7 +7557,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>12</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>13</v>
       </c>
@@ -7711,7 +7711,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>14</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>15</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>16</v>
       </c>
@@ -7942,7 +7942,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>17</v>
       </c>
@@ -8019,7 +8019,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>18</v>
       </c>
@@ -8096,7 +8096,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>19</v>
       </c>
@@ -8173,7 +8173,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>20</v>
       </c>
@@ -8250,7 +8250,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>21</v>
       </c>
@@ -8327,7 +8327,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>22</v>
       </c>
@@ -8404,7 +8404,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>23</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>24</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>25</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>26</v>
       </c>
@@ -8712,7 +8712,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>27</v>
       </c>
@@ -8789,7 +8789,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>28</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>29</v>
       </c>
@@ -8943,7 +8943,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>30</v>
       </c>
@@ -9020,7 +9020,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>31</v>
       </c>
@@ -9097,7 +9097,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>32</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>33</v>
       </c>
@@ -9251,7 +9251,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>34</v>
       </c>
@@ -9328,7 +9328,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>35</v>
       </c>
@@ -9405,7 +9405,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>36</v>
       </c>
@@ -9482,7 +9482,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>37</v>
       </c>
@@ -9559,7 +9559,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>38</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>39</v>
       </c>
@@ -9713,7 +9713,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>40</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>41</v>
       </c>
@@ -9867,7 +9867,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>42</v>
       </c>
@@ -9944,7 +9944,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>43</v>
       </c>
@@ -10021,7 +10021,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>44</v>
       </c>
@@ -10098,7 +10098,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <v>45</v>
       </c>
@@ -10175,7 +10175,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
         <v>46</v>
       </c>
@@ -10252,7 +10252,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>47</v>
       </c>
@@ -10329,7 +10329,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>48</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>49</v>
       </c>
@@ -10483,7 +10483,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <v>50</v>
       </c>
@@ -10560,7 +10560,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>51</v>
       </c>
@@ -10637,7 +10637,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>52</v>
       </c>
@@ -10714,7 +10714,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>53</v>
       </c>
@@ -10791,7 +10791,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>54</v>
       </c>
@@ -10868,7 +10868,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>55</v>
       </c>
@@ -10945,7 +10945,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>56</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>57</v>
       </c>
@@ -11099,7 +11099,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <v>58</v>
       </c>
@@ -11176,7 +11176,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>59</v>
       </c>
@@ -11253,7 +11253,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>60</v>
       </c>
@@ -11330,7 +11330,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>61</v>
       </c>
@@ -11407,7 +11407,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>62</v>
       </c>
@@ -11484,7 +11484,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>63</v>
       </c>
@@ -11561,7 +11561,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>64</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>65</v>
       </c>
@@ -11715,7 +11715,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>66</v>
       </c>
@@ -11792,7 +11792,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>67</v>
       </c>
@@ -11869,7 +11869,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>68</v>
       </c>
@@ -11946,7 +11946,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <v>69</v>
       </c>
@@ -12023,7 +12023,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <v>70</v>
       </c>
@@ -12100,7 +12100,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>71</v>
       </c>
@@ -12177,7 +12177,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>72</v>
       </c>
@@ -12254,7 +12254,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>73</v>
       </c>
@@ -12331,7 +12331,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>74</v>
       </c>
@@ -12408,7 +12408,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <v>75</v>
       </c>
@@ -12485,7 +12485,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <v>76</v>
       </c>
@@ -12562,7 +12562,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>77</v>
       </c>
@@ -12639,7 +12639,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>78</v>
       </c>
@@ -12716,7 +12716,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>79</v>
       </c>
@@ -12793,7 +12793,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>80</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <v>81</v>
       </c>
@@ -12947,7 +12947,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <v>82</v>
       </c>
@@ -13024,7 +13024,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>83</v>
       </c>
@@ -13101,7 +13101,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>84</v>
       </c>
@@ -13178,7 +13178,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>85</v>
       </c>
@@ -13255,7 +13255,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>86</v>
       </c>
@@ -13332,7 +13332,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>87</v>
       </c>
@@ -13409,7 +13409,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>88</v>
       </c>
@@ -13486,7 +13486,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="9">
         <v>89</v>
       </c>
@@ -13563,7 +13563,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="9">
         <v>90</v>
       </c>
@@ -13640,7 +13640,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
         <v>91</v>
       </c>
@@ -13717,7 +13717,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9">
         <v>92</v>
       </c>
@@ -13794,7 +13794,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="9">
         <v>93</v>
       </c>
@@ -13871,7 +13871,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
         <v>94</v>
       </c>
@@ -13948,7 +13948,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
         <v>95</v>
       </c>
@@ -14025,7 +14025,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
         <v>96</v>
       </c>
@@ -14102,7 +14102,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="9">
         <v>97</v>
       </c>
@@ -14179,7 +14179,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="9">
         <v>98</v>
       </c>
@@ -14256,7 +14256,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="9">
         <v>99</v>
       </c>
@@ -14333,7 +14333,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
         <v>100</v>
       </c>
@@ -14410,7 +14410,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="9">
         <v>101</v>
       </c>
@@ -14487,7 +14487,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="9">
         <v>102</v>
       </c>
@@ -14564,7 +14564,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9">
         <v>103</v>
       </c>
@@ -14641,7 +14641,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
         <v>104</v>
       </c>
@@ -14718,7 +14718,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="9">
         <v>105</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="9">
         <v>106</v>
       </c>
@@ -14872,7 +14872,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
         <v>107</v>
       </c>
@@ -14949,7 +14949,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="9">
         <v>108</v>
       </c>
@@ -15026,7 +15026,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>109</v>
       </c>
@@ -15103,7 +15103,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="9">
         <v>110</v>
       </c>
@@ -15180,7 +15180,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="9">
         <v>111</v>
       </c>
@@ -15257,7 +15257,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="9">
         <v>112</v>
       </c>
@@ -15334,7 +15334,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="9">
         <v>113</v>
       </c>
@@ -15411,7 +15411,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="9">
         <v>114</v>
       </c>
@@ -15488,7 +15488,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="9">
         <v>115</v>
       </c>
@@ -15565,7 +15565,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="9">
         <v>116</v>
       </c>
@@ -15642,7 +15642,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="9">
         <v>117</v>
       </c>
@@ -15719,7 +15719,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="9">
         <v>118</v>
       </c>
@@ -15796,7 +15796,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="9">
         <v>119</v>
       </c>
@@ -15873,7 +15873,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="9">
         <v>120</v>
       </c>
@@ -15950,7 +15950,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="9">
         <v>121</v>
       </c>
@@ -16027,7 +16027,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="9">
         <v>122</v>
       </c>
@@ -16104,7 +16104,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="9">
         <v>123</v>
       </c>
@@ -16181,7 +16181,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="9">
         <v>124</v>
       </c>
@@ -16258,7 +16258,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9">
         <v>125</v>
       </c>
@@ -16335,7 +16335,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="9">
         <v>126</v>
       </c>
@@ -16412,7 +16412,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="9">
         <v>127</v>
       </c>
@@ -16489,7 +16489,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="9">
         <v>128</v>
       </c>
@@ -16566,7 +16566,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="9">
         <v>129</v>
       </c>
@@ -16643,7 +16643,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="9">
         <v>130</v>
       </c>
@@ -16720,7 +16720,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="9">
         <v>131</v>
       </c>
@@ -16797,7 +16797,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="9">
         <v>132</v>
       </c>
@@ -16874,7 +16874,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="9">
         <v>133</v>
       </c>
@@ -16951,7 +16951,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="9">
         <v>134</v>
       </c>
@@ -17028,7 +17028,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="9">
         <v>135</v>
       </c>
@@ -17105,7 +17105,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="9">
         <v>136</v>
       </c>
@@ -17182,7 +17182,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9">
         <v>137</v>
       </c>
@@ -17259,7 +17259,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="9">
         <v>138</v>
       </c>
@@ -17336,7 +17336,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="9">
         <v>139</v>
       </c>
@@ -17413,7 +17413,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="9">
         <v>140</v>
       </c>
@@ -17490,7 +17490,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="9">
         <v>141</v>
       </c>
@@ -17567,7 +17567,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="9">
         <v>142</v>
       </c>
@@ -17644,7 +17644,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="9">
         <v>143</v>
       </c>
@@ -17721,7 +17721,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="9">
         <v>144</v>
       </c>
@@ -17798,7 +17798,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="9">
         <v>145</v>
       </c>
@@ -17875,7 +17875,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="9">
         <v>146</v>
       </c>
@@ -17952,7 +17952,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="9">
         <v>147</v>
       </c>
@@ -18029,7 +18029,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9">
         <v>148</v>
       </c>
@@ -18106,7 +18106,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="9">
         <v>149</v>
       </c>
@@ -18183,7 +18183,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="9">
         <v>150</v>
       </c>
@@ -18260,7 +18260,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="9">
         <v>151</v>
       </c>
@@ -18337,7 +18337,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="9">
         <v>152</v>
       </c>
@@ -18414,7 +18414,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="9">
         <v>153</v>
       </c>
@@ -18491,7 +18491,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="9">
         <v>154</v>
       </c>
@@ -18568,7 +18568,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="9">
         <v>155</v>
       </c>
@@ -18645,7 +18645,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="9">
         <v>156</v>
       </c>
@@ -18722,7 +18722,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="9">
         <v>157</v>
       </c>
@@ -18802,10 +18802,10 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2N.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFD6335-9F70-4FC7-AD5E-7BD257D63FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57AB93C-BC62-496D-8A8E-F83CB451B8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -2272,17 +2272,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A0D90F96-026A-4EEB-BDCF-93327D239D7A}"/>
   </cellStyles>
-  <dxfs count="68">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="65">
     <dxf>
       <font>
         <b val="0"/>
@@ -2315,22 +2305,6 @@
         <i/>
         <strike val="0"/>
         <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -2388,45 +2362,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond Light"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor rgb="FFFFDE75"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -3912,6 +3847,45 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF2CB"/>
+          <bgColor rgb="FFFFDE75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -4191,33 +4165,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="67" dataDxfId="65" headerRowBorderDxfId="66" tableBorderDxfId="64" totalsRowBorderDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="64" dataDxfId="62" headerRowBorderDxfId="63" tableBorderDxfId="61" totalsRowBorderDxfId="60">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="62" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="60" dataDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="58" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="17" dataDxfId="16"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="13" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="11" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4745,7 +4719,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46165.78152326389</v>
+        <v>46165.895527430555</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>406</v>
@@ -7433,29 +7407,19 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A19">
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="equal">
+  <conditionalFormatting sqref="A2:A28">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA19">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A20:A28">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA20:AA28">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+  <conditionalFormatting sqref="AA1:AA28">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7608,7 +7572,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7653,7 +7617,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19776,10 +19740,10 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2N.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57AB93C-BC62-496D-8A8E-F83CB451B8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47B14F7-2B68-41A0-8387-3A70D10B0E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4380" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4380" uniqueCount="550">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1371,18 +1371,9 @@
     <t>No.Projeto</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
-  </si>
-  <si>
-    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
     <t>Interdisciplinar</t>
   </si>
   <si>
-    <t>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</t>
-  </si>
-  <si>
     <t>Requerida</t>
   </si>
   <si>
@@ -1719,10 +1710,37 @@
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requisitos Mobiliários do Projeto.</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requisitos de Equipamentos do Projeto.</t>
-  </si>
-  <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requisitos de Sistemas Prediais do Projeto.</t>
+  </si>
+  <si>
+    <t>"Parte 4 da NBR 15.965"</t>
+  </si>
+  <si>
+    <t>"Recursos Humanos relacionados com a Construção"</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definições do Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Definiciones del Proyecto.</t>
+  </si>
+  <si>
+    <t>Defines an information container in accordance with the NBR 19650-1 standard. Project Definitions.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos Espaciales del Proyecto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de Mobiliarios del Proyecto.</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requisitos Equipamentos do Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de Equipamiento del Proyecto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de Instalaciones del Proyecto.</t>
   </si>
 </sst>
 </file>
@@ -2272,7 +2290,63 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A0D90F96-026A-4EEB-BDCF-93327D239D7A}"/>
   </cellStyles>
-  <dxfs count="65">
+  <dxfs count="71">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4165,33 +4239,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="64" dataDxfId="62" headerRowBorderDxfId="63" tableBorderDxfId="61" totalsRowBorderDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" tableBorderDxfId="67" totalsRowBorderDxfId="66">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="17" dataDxfId="16"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="15" dataDxfId="14"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="13" dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="11" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="17" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4719,7 +4793,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46165.895527430555</v>
+        <v>46167.41566712963</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>406</v>
@@ -4824,7 +4898,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958751C2-A34E-4345-8D6A-082603A025F9}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA28"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="5.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.296875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="6.796875" style="36" customWidth="1"/>
@@ -4837,7 +4911,7 @@
     <col min="14" max="14" width="7" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="62" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="45.59765625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="60.69921875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5.796875" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
     <col min="20" max="20" width="9.19921875" customWidth="1"/>
@@ -4848,7 +4922,7 @@
     <col min="27" max="27" width="64.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="30.9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="31.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>349</v>
       </c>
@@ -4931,7 +5005,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="51">
         <v>2</v>
       </c>
@@ -4966,7 +5040,7 @@
         <v>181</v>
       </c>
       <c r="L2" s="55" t="str">
-        <f t="shared" ref="L2:N17" si="0">CONCATENATE("", C2)</f>
+        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
         <v>Contêiner</v>
       </c>
       <c r="M2" s="55" t="str">
@@ -4982,10 +5056,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="40" t="s">
-        <v>426</v>
+        <v>542</v>
       </c>
       <c r="Q2" s="40" t="s">
-        <v>427</v>
+        <v>543</v>
       </c>
       <c r="R2" s="56" t="s">
         <v>181</v>
@@ -5003,10 +5077,10 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="40" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="W2" s="58" t="str">
-        <f t="shared" ref="W2:W28" si="3">CONCATENATE("Key.ABNT.",A2)</f>
+        <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key.ABNT.",A2)</f>
         <v>Key.ABNT.2</v>
       </c>
       <c r="X2" s="40" t="s">
@@ -5019,10 +5093,10 @@
         <v>181</v>
       </c>
       <c r="AA2" s="40" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="51">
         <v>3</v>
       </c>
@@ -5036,10 +5110,10 @@
         <v>423</v>
       </c>
       <c r="E3" s="52" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F3" s="53" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="G3" s="54" t="s">
         <v>181</v>
@@ -5073,10 +5147,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="40" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="Q3" s="40" t="s">
-        <v>427</v>
+        <v>545</v>
       </c>
       <c r="R3" s="56" t="s">
         <v>181</v>
@@ -5094,7 +5168,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="40" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="W3" s="58" t="str">
         <f t="shared" si="3"/>
@@ -5110,10 +5184,10 @@
         <v>181</v>
       </c>
       <c r="AA3" s="40" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="51">
         <v>4</v>
       </c>
@@ -5127,10 +5201,10 @@
         <v>423</v>
       </c>
       <c r="E4" s="52" t="s">
+        <v>427</v>
+      </c>
+      <c r="F4" s="53" t="s">
         <v>430</v>
-      </c>
-      <c r="F4" s="53" t="s">
-        <v>433</v>
       </c>
       <c r="G4" s="54" t="s">
         <v>181</v>
@@ -5164,10 +5238,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="Q4" s="40" t="s">
-        <v>427</v>
+        <v>546</v>
       </c>
       <c r="R4" s="56" t="s">
         <v>181</v>
@@ -5185,7 +5259,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="40" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="W4" s="58" t="str">
         <f t="shared" si="3"/>
@@ -5201,10 +5275,10 @@
         <v>181</v>
       </c>
       <c r="AA4" s="40" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="51">
         <v>5</v>
       </c>
@@ -5218,10 +5292,10 @@
         <v>423</v>
       </c>
       <c r="E5" s="52" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="G5" s="54" t="s">
         <v>181</v>
@@ -5255,10 +5329,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="40" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="Q5" s="40" t="s">
-        <v>427</v>
+        <v>548</v>
       </c>
       <c r="R5" s="56" t="s">
         <v>181</v>
@@ -5276,7 +5350,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="40" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="W5" s="58" t="str">
         <f t="shared" si="3"/>
@@ -5292,10 +5366,10 @@
         <v>181</v>
       </c>
       <c r="AA5" s="40" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="51">
         <v>6</v>
       </c>
@@ -5309,10 +5383,10 @@
         <v>423</v>
       </c>
       <c r="E6" s="52" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="G6" s="54" t="s">
         <v>181</v>
@@ -5346,10 +5420,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="40" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="Q6" s="40" t="s">
-        <v>427</v>
+        <v>549</v>
       </c>
       <c r="R6" s="56" t="s">
         <v>181</v>
@@ -5367,7 +5441,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="40" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="W6" s="58" t="str">
         <f t="shared" si="3"/>
@@ -5383,10 +5457,10 @@
         <v>181</v>
       </c>
       <c r="AA6" s="40" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="51">
         <v>7</v>
       </c>
@@ -5400,10 +5474,10 @@
         <v>372</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="G7" s="38" t="s">
         <v>181</v>
@@ -5421,63 +5495,63 @@
         <v>181</v>
       </c>
       <c r="L7" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L2:N17" si="4">CONCATENATE("", C7)</f>
         <v>Norma</v>
       </c>
       <c r="M7" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N7" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O7" s="55" t="str">
-        <f t="shared" ref="O7:O28" si="4">F7</f>
+        <f t="shared" ref="O7:O28" si="5">F7</f>
         <v>NBR.0M</v>
       </c>
       <c r="P7" s="55" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q7" s="55" t="s">
+        <v>437</v>
+      </c>
+      <c r="R7" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S7" s="57" t="str">
+        <f t="shared" ref="S7:U22" si="6">SUBSTITUTE(C7, "_", " ")</f>
+        <v>Norma</v>
+      </c>
+      <c r="T7" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U7" s="55" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="V7" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W7" s="58" t="str">
+        <f t="shared" ref="W2:W28" si="7">CONCATENATE("Key.ABNT.",A7)</f>
+        <v>Key.ABNT.7</v>
+      </c>
+      <c r="X7" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y7" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z7" s="40" t="s">
+        <v>438</v>
+      </c>
+      <c r="AA7" s="59" t="s">
         <v>439</v>
       </c>
-      <c r="Q7" s="55" t="s">
-        <v>440</v>
-      </c>
-      <c r="R7" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S7" s="57" t="str">
-        <f t="shared" ref="S7:U22" si="5">SUBSTITUTE(C7, "_", " ")</f>
-        <v>Norma</v>
-      </c>
-      <c r="T7" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U7" s="55" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="V7" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W7" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key.ABNT.7</v>
-      </c>
-      <c r="X7" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y7" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z7" s="40" t="s">
-        <v>441</v>
-      </c>
-      <c r="AA7" s="59" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="51">
         <v>8</v>
       </c>
@@ -5491,10 +5565,10 @@
         <v>372</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="G8" s="38" t="s">
         <v>181</v>
@@ -5512,63 +5586,63 @@
         <v>181</v>
       </c>
       <c r="L8" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M8" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N8" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O8" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.0P</v>
       </c>
       <c r="P8" s="55" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q8" s="55" t="s">
+        <v>441</v>
+      </c>
+      <c r="R8" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S8" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>Norma</v>
+      </c>
+      <c r="T8" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U8" s="55" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="V8" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W8" s="58" t="str">
+        <f t="shared" si="7"/>
+        <v>Key.ABNT.8</v>
+      </c>
+      <c r="X8" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y8" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z8" s="40" t="s">
+        <v>442</v>
+      </c>
+      <c r="AA8" s="59" t="s">
         <v>443</v>
       </c>
-      <c r="Q8" s="55" t="s">
-        <v>444</v>
-      </c>
-      <c r="R8" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S8" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T8" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U8" s="55" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="V8" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W8" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key.ABNT.8</v>
-      </c>
-      <c r="X8" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y8" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z8" s="40" t="s">
-        <v>445</v>
-      </c>
-      <c r="AA8" s="59" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="51">
         <v>9</v>
       </c>
@@ -5582,11 +5656,11 @@
         <v>372</v>
       </c>
       <c r="E9" s="35" t="s">
+        <v>495</v>
+      </c>
+      <c r="F9" s="28" t="s">
         <v>498</v>
       </c>
-      <c r="F9" s="28" t="s">
-        <v>501</v>
-      </c>
       <c r="G9" s="38" t="s">
         <v>181</v>
       </c>
@@ -5603,63 +5677,63 @@
         <v>181</v>
       </c>
       <c r="L9" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M9" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N9" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O9" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.1D</v>
       </c>
       <c r="P9" s="55" t="s">
+        <v>444</v>
+      </c>
+      <c r="Q9" s="55" t="s">
+        <v>445</v>
+      </c>
+      <c r="R9" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S9" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>Norma</v>
+      </c>
+      <c r="T9" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U9" s="55" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="V9" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W9" s="58" t="str">
+        <f t="shared" si="7"/>
+        <v>Key.ABNT.9</v>
+      </c>
+      <c r="X9" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y9" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z9" s="40" t="s">
+        <v>446</v>
+      </c>
+      <c r="AA9" s="59" t="s">
         <v>447</v>
       </c>
-      <c r="Q9" s="55" t="s">
-        <v>448</v>
-      </c>
-      <c r="R9" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S9" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T9" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U9" s="55" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="V9" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W9" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key.ABNT.9</v>
-      </c>
-      <c r="X9" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y9" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z9" s="40" t="s">
-        <v>449</v>
-      </c>
-      <c r="AA9" s="59" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="51">
         <v>10</v>
       </c>
@@ -5673,10 +5747,10 @@
         <v>372</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G10" s="38" t="s">
         <v>181</v>
@@ -5694,63 +5768,63 @@
         <v>181</v>
       </c>
       <c r="L10" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M10" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N10" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O10" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.1F</v>
       </c>
       <c r="P10" s="55" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q10" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="R10" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S10" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>Norma</v>
+      </c>
+      <c r="T10" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U10" s="55" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="V10" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W10" s="58" t="str">
+        <f t="shared" si="7"/>
+        <v>Key.ABNT.10</v>
+      </c>
+      <c r="X10" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y10" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z10" s="40" t="s">
+        <v>450</v>
+      </c>
+      <c r="AA10" s="59" t="s">
         <v>451</v>
       </c>
-      <c r="Q10" s="55" t="s">
-        <v>452</v>
-      </c>
-      <c r="R10" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S10" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T10" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U10" s="55" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="V10" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W10" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key.ABNT.10</v>
-      </c>
-      <c r="X10" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y10" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z10" s="40" t="s">
-        <v>453</v>
-      </c>
-      <c r="AA10" s="59" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="51">
         <v>11</v>
       </c>
@@ -5764,10 +5838,10 @@
         <v>372</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G11" s="38" t="s">
         <v>181</v>
@@ -5785,63 +5859,63 @@
         <v>181</v>
       </c>
       <c r="L11" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M11" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N11" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O11" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.1S</v>
       </c>
       <c r="P11" s="55" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q11" s="55" t="s">
+        <v>453</v>
+      </c>
+      <c r="R11" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S11" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>Norma</v>
+      </c>
+      <c r="T11" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U11" s="55" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="V11" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W11" s="58" t="str">
+        <f t="shared" si="7"/>
+        <v>Key.ABNT.11</v>
+      </c>
+      <c r="X11" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y11" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z11" s="40" t="s">
+        <v>454</v>
+      </c>
+      <c r="AA11" s="59" t="s">
         <v>455</v>
       </c>
-      <c r="Q11" s="55" t="s">
-        <v>456</v>
-      </c>
-      <c r="R11" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S11" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T11" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U11" s="55" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="V11" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W11" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key.ABNT.11</v>
-      </c>
-      <c r="X11" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y11" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z11" s="40" t="s">
-        <v>457</v>
-      </c>
-      <c r="AA11" s="59" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="51">
         <v>12</v>
       </c>
@@ -5855,10 +5929,10 @@
         <v>372</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>181</v>
@@ -5876,63 +5950,63 @@
         <v>181</v>
       </c>
       <c r="L12" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M12" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N12" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O12" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.2C</v>
       </c>
       <c r="P12" s="55" t="s">
+        <v>456</v>
+      </c>
+      <c r="Q12" s="55" t="s">
+        <v>457</v>
+      </c>
+      <c r="R12" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S12" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>Norma</v>
+      </c>
+      <c r="T12" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U12" s="55" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="V12" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W12" s="58" t="str">
+        <f t="shared" si="7"/>
+        <v>Key.ABNT.12</v>
+      </c>
+      <c r="X12" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y12" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z12" s="40" t="s">
+        <v>458</v>
+      </c>
+      <c r="AA12" s="59" t="s">
         <v>459</v>
       </c>
-      <c r="Q12" s="55" t="s">
-        <v>460</v>
-      </c>
-      <c r="R12" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S12" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T12" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U12" s="55" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="V12" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W12" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key.ABNT.12</v>
-      </c>
-      <c r="X12" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y12" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z12" s="40" t="s">
-        <v>461</v>
-      </c>
-      <c r="AA12" s="59" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="51">
         <v>13</v>
       </c>
@@ -5946,10 +6020,10 @@
         <v>372</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="G13" s="38" t="s">
         <v>181</v>
@@ -5967,47 +6041,47 @@
         <v>181</v>
       </c>
       <c r="L13" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M13" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N13" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O13" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.2N</v>
       </c>
       <c r="P13" s="55" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="Q13" s="55" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="R13" s="56" t="s">
         <v>181</v>
       </c>
       <c r="S13" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T13" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U13" s="55" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V13" s="40" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="W13" s="58" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.13</v>
       </c>
       <c r="X13" s="40" t="s">
@@ -6020,10 +6094,10 @@
         <v>342</v>
       </c>
       <c r="AA13" s="59" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="51">
         <v>14</v>
       </c>
@@ -6037,10 +6111,10 @@
         <v>372</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="G14" s="38" t="s">
         <v>181</v>
@@ -6058,63 +6132,63 @@
         <v>181</v>
       </c>
       <c r="L14" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M14" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N14" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O14" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.2Q</v>
       </c>
       <c r="P14" s="55" t="s">
+        <v>456</v>
+      </c>
+      <c r="Q14" s="55" t="s">
+        <v>457</v>
+      </c>
+      <c r="R14" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S14" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>Norma</v>
+      </c>
+      <c r="T14" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U14" s="55" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="V14" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W14" s="58" t="str">
+        <f t="shared" si="7"/>
+        <v>Key.ABNT.14</v>
+      </c>
+      <c r="X14" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y14" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z14" s="40" t="s">
+        <v>460</v>
+      </c>
+      <c r="AA14" s="59" t="s">
         <v>459</v>
       </c>
-      <c r="Q14" s="55" t="s">
-        <v>460</v>
-      </c>
-      <c r="R14" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S14" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T14" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U14" s="55" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="V14" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W14" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key.ABNT.14</v>
-      </c>
-      <c r="X14" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y14" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z14" s="40" t="s">
-        <v>463</v>
-      </c>
-      <c r="AA14" s="59" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="51">
         <v>15</v>
       </c>
@@ -6128,10 +6202,10 @@
         <v>372</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="G15" s="38" t="s">
         <v>181</v>
@@ -6149,63 +6223,63 @@
         <v>181</v>
       </c>
       <c r="L15" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M15" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N15" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O15" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.3E</v>
       </c>
       <c r="P15" s="55" t="s">
+        <v>461</v>
+      </c>
+      <c r="Q15" s="55" t="s">
+        <v>462</v>
+      </c>
+      <c r="R15" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S15" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>Norma</v>
+      </c>
+      <c r="T15" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U15" s="55" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="V15" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W15" s="58" t="str">
+        <f t="shared" si="7"/>
+        <v>Key.ABNT.15</v>
+      </c>
+      <c r="X15" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y15" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z15" s="40" t="s">
+        <v>463</v>
+      </c>
+      <c r="AA15" s="59" t="s">
         <v>464</v>
       </c>
-      <c r="Q15" s="55" t="s">
-        <v>465</v>
-      </c>
-      <c r="R15" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S15" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T15" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U15" s="55" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="V15" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W15" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key.ABNT.15</v>
-      </c>
-      <c r="X15" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y15" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z15" s="40" t="s">
-        <v>466</v>
-      </c>
-      <c r="AA15" s="59" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="51">
         <v>16</v>
       </c>
@@ -6219,10 +6293,10 @@
         <v>372</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>181</v>
@@ -6240,63 +6314,63 @@
         <v>181</v>
       </c>
       <c r="L16" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M16" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N16" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O16" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.3R</v>
       </c>
       <c r="P16" s="55" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q16" s="55" t="s">
+        <v>466</v>
+      </c>
+      <c r="R16" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S16" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>Norma</v>
+      </c>
+      <c r="T16" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U16" s="55" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="V16" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W16" s="58" t="str">
+        <f t="shared" si="7"/>
+        <v>Key.ABNT.16</v>
+      </c>
+      <c r="X16" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y16" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z16" s="40" t="s">
+        <v>467</v>
+      </c>
+      <c r="AA16" s="59" t="s">
         <v>468</v>
       </c>
-      <c r="Q16" s="55" t="s">
-        <v>469</v>
-      </c>
-      <c r="R16" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S16" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T16" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U16" s="55" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="V16" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W16" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key.ABNT.16</v>
-      </c>
-      <c r="X16" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y16" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z16" s="40" t="s">
-        <v>470</v>
-      </c>
-      <c r="AA16" s="59" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="51">
         <v>17</v>
       </c>
@@ -6310,10 +6384,10 @@
         <v>372</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="G17" s="38" t="s">
         <v>181</v>
@@ -6331,63 +6405,63 @@
         <v>181</v>
       </c>
       <c r="L17" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M17" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N17" s="55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O17" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.4A</v>
       </c>
       <c r="P17" s="55" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q17" s="55" t="s">
+        <v>470</v>
+      </c>
+      <c r="R17" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S17" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>Norma</v>
+      </c>
+      <c r="T17" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U17" s="55" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="V17" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W17" s="58" t="str">
+        <f t="shared" si="7"/>
+        <v>Key.ABNT.17</v>
+      </c>
+      <c r="X17" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y17" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z17" s="40" t="s">
+        <v>471</v>
+      </c>
+      <c r="AA17" s="59" t="s">
         <v>472</v>
       </c>
-      <c r="Q17" s="55" t="s">
-        <v>473</v>
-      </c>
-      <c r="R17" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S17" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T17" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U17" s="55" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="V17" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W17" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key.ABNT.17</v>
-      </c>
-      <c r="X17" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y17" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z17" s="40" t="s">
-        <v>474</v>
-      </c>
-      <c r="AA17" s="59" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="51">
         <v>18</v>
       </c>
@@ -6401,10 +6475,10 @@
         <v>372</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="G18" s="38" t="s">
         <v>181</v>
@@ -6422,63 +6496,63 @@
         <v>181</v>
       </c>
       <c r="L18" s="55" t="str">
-        <f t="shared" ref="L18:N28" si="6">CONCATENATE("", C18)</f>
+        <f t="shared" ref="L18:N28" si="8">CONCATENATE("", C18)</f>
         <v>Norma</v>
       </c>
       <c r="M18" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N18" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O18" s="55" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.4U</v>
+      </c>
+      <c r="P18" s="55" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q18" s="55" t="s">
+        <v>474</v>
+      </c>
+      <c r="R18" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S18" s="57" t="str">
+        <f t="shared" si="6"/>
+        <v>Norma</v>
+      </c>
+      <c r="T18" s="57" t="str">
         <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N18" s="55" t="str">
+      <c r="U18" s="55" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O18" s="55" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.4U</v>
-      </c>
-      <c r="P18" s="55" t="s">
+      <c r="V18" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W18" s="58" t="str">
+        <f t="shared" si="7"/>
+        <v>Key.ABNT.18</v>
+      </c>
+      <c r="X18" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y18" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z18" s="40" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA18" s="59" t="s">
         <v>476</v>
       </c>
-      <c r="Q18" s="55" t="s">
-        <v>477</v>
-      </c>
-      <c r="R18" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S18" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T18" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U18" s="55" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="V18" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W18" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key.ABNT.18</v>
-      </c>
-      <c r="X18" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y18" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z18" s="40" t="s">
-        <v>478</v>
-      </c>
-      <c r="AA18" s="59" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="51">
         <v>19</v>
       </c>
@@ -6492,10 +6566,10 @@
         <v>372</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="G19" s="38" t="s">
         <v>181</v>
@@ -6513,63 +6587,63 @@
         <v>181</v>
       </c>
       <c r="L19" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>Norma</v>
+      </c>
+      <c r="M19" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N19" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O19" s="55" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.5I</v>
+      </c>
+      <c r="P19" s="55" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q19" s="55" t="s">
+        <v>478</v>
+      </c>
+      <c r="R19" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S19" s="57" t="str">
         <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
-      <c r="M19" s="55" t="str">
+      <c r="T19" s="57" t="str">
         <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N19" s="55" t="str">
+      <c r="U19" s="55" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O19" s="55" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.5I</v>
-      </c>
-      <c r="P19" s="55" t="s">
+      <c r="V19" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W19" s="58" t="str">
+        <f t="shared" si="7"/>
+        <v>Key.ABNT.19</v>
+      </c>
+      <c r="X19" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y19" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z19" s="40" t="s">
+        <v>479</v>
+      </c>
+      <c r="AA19" s="59" t="s">
         <v>480</v>
       </c>
-      <c r="Q19" s="55" t="s">
-        <v>481</v>
-      </c>
-      <c r="R19" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S19" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T19" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U19" s="55" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="V19" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W19" s="58" t="str">
-        <f t="shared" si="3"/>
-        <v>Key.ABNT.19</v>
-      </c>
-      <c r="X19" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y19" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z19" s="40" t="s">
-        <v>482</v>
-      </c>
-      <c r="AA19" s="59" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="51">
         <v>20</v>
       </c>
@@ -6577,16 +6651,16 @@
         <v>395</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="G20" s="38" t="s">
         <v>181</v>
@@ -6604,23 +6678,23 @@
         <v>181</v>
       </c>
       <c r="L20" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M20" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N20" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="O20" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.N.Empreendedor</v>
       </c>
       <c r="P20" s="63" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="Q20" s="55" t="str">
         <f>_xlfn.TRANSLATE(P20,"pt","es")</f>
@@ -6630,22 +6704,22 @@
         <v>181</v>
       </c>
       <c r="S20" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Tema</v>
       </c>
       <c r="T20" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="U20" s="55" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="V20" s="40" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="W20" s="58" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.20</v>
       </c>
       <c r="X20" s="40" t="s">
@@ -6655,14 +6729,14 @@
         <v>181</v>
       </c>
       <c r="Z20" s="59" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="AA20" s="59" t="str">
         <f>_xlfn.TRANSLATE(P20,"pt","en")</f>
         <v>Entrepreneurs</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="51">
         <v>21</v>
       </c>
@@ -6670,16 +6744,16 @@
         <v>395</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D21" s="35" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="G21" s="38" t="s">
         <v>181</v>
@@ -6697,48 +6771,48 @@
         <v>181</v>
       </c>
       <c r="L21" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M21" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N21" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.N.RH</v>
+      </c>
+      <c r="O21" s="55" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.N.Projetista</v>
+      </c>
+      <c r="P21" s="63" t="s">
+        <v>520</v>
+      </c>
+      <c r="Q21" s="55" t="str">
+        <f t="shared" ref="Q21:Q28" si="9">_xlfn.TRANSLATE(P21,"pt","es")</f>
+        <v>Diseñadores</v>
+      </c>
+      <c r="R21" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S21" s="57" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Tema</v>
       </c>
-      <c r="M21" s="55" t="str">
+      <c r="T21" s="57" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Subtema</v>
       </c>
-      <c r="N21" s="55" t="str">
+      <c r="U21" s="55" t="str">
         <f t="shared" si="6"/>
         <v>NBR.N.RH</v>
       </c>
-      <c r="O21" s="55" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.N.Projetista</v>
-      </c>
-      <c r="P21" s="63" t="s">
-        <v>523</v>
-      </c>
-      <c r="Q21" s="55" t="str">
-        <f t="shared" ref="Q21:Q28" si="7">_xlfn.TRANSLATE(P21,"pt","es")</f>
-        <v>Diseñadores</v>
-      </c>
-      <c r="R21" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S21" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T21" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U21" s="55" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.N.RH</v>
-      </c>
       <c r="V21" s="40" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="W21" s="58" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.21</v>
       </c>
       <c r="X21" s="40" t="s">
@@ -6748,14 +6822,14 @@
         <v>181</v>
       </c>
       <c r="Z21" s="59" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="AA21" s="59" t="str">
-        <f t="shared" ref="AA21:AA28" si="8">_xlfn.TRANSLATE(P21,"pt","en")</f>
+        <f t="shared" ref="AA21:AA28" si="10">_xlfn.TRANSLATE(P21,"pt","en")</f>
         <v>Designers</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="51">
         <v>22</v>
       </c>
@@ -6763,17 +6837,17 @@
         <v>395</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E22" s="35" t="s">
+        <v>509</v>
+      </c>
+      <c r="F22" s="14" t="s">
         <v>512</v>
       </c>
-      <c r="F22" s="14" t="s">
-        <v>515</v>
-      </c>
       <c r="G22" s="38" t="s">
         <v>181</v>
       </c>
@@ -6790,48 +6864,48 @@
         <v>181</v>
       </c>
       <c r="L22" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M22" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N22" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.N.RH</v>
+      </c>
+      <c r="O22" s="55" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.N.Gestor</v>
+      </c>
+      <c r="P22" s="63" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q22" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>Entrenadores</v>
+      </c>
+      <c r="R22" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S22" s="57" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Tema</v>
       </c>
-      <c r="M22" s="55" t="str">
+      <c r="T22" s="57" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Subtema</v>
       </c>
-      <c r="N22" s="55" t="str">
+      <c r="U22" s="55" t="str">
         <f t="shared" si="6"/>
         <v>NBR.N.RH</v>
       </c>
-      <c r="O22" s="55" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.N.Gestor</v>
-      </c>
-      <c r="P22" s="63" t="s">
-        <v>524</v>
-      </c>
-      <c r="Q22" s="55" t="str">
+      <c r="V22" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W22" s="58" t="str">
         <f t="shared" si="7"/>
-        <v>Entrenadores</v>
-      </c>
-      <c r="R22" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S22" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T22" s="57" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U22" s="55" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.N.RH</v>
-      </c>
-      <c r="V22" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W22" s="58" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.22</v>
       </c>
       <c r="X22" s="40" t="s">
@@ -6841,14 +6915,14 @@
         <v>181</v>
       </c>
       <c r="Z22" s="59" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="AA22" s="59" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Managers</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="51">
         <v>23</v>
       </c>
@@ -6856,16 +6930,16 @@
         <v>395</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D23" s="35" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="G23" s="38" t="s">
         <v>181</v>
@@ -6883,48 +6957,48 @@
         <v>181</v>
       </c>
       <c r="L23" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M23" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N23" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="O23" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.N.Construtor</v>
       </c>
       <c r="P23" s="63" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="Q23" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>Constructores y contratistas</v>
+      </c>
+      <c r="R23" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S23" s="57" t="str">
+        <f t="shared" ref="S23:U28" si="11">SUBSTITUTE(C23, "_", " ")</f>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T23" s="57" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U23" s="55" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.N.RH</v>
+      </c>
+      <c r="V23" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W23" s="58" t="str">
         <f t="shared" si="7"/>
-        <v>Constructores y contratistas</v>
-      </c>
-      <c r="R23" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S23" s="57" t="str">
-        <f t="shared" ref="S23:U28" si="9">SUBSTITUTE(C23, "_", " ")</f>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T23" s="57" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U23" s="55" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.N.RH</v>
-      </c>
-      <c r="V23" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W23" s="58" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.23</v>
       </c>
       <c r="X23" s="40" t="s">
@@ -6934,14 +7008,14 @@
         <v>181</v>
       </c>
       <c r="Z23" s="59" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="AA23" s="59" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Builders and Contractors</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="51">
         <v>24</v>
       </c>
@@ -6949,16 +7023,16 @@
         <v>395</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D24" s="35" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E24" s="35" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="G24" s="38" t="s">
         <v>181</v>
@@ -6976,48 +7050,48 @@
         <v>181</v>
       </c>
       <c r="L24" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M24" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N24" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="O24" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.N.Fiscal</v>
       </c>
       <c r="P24" s="63" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="Q24" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>Inspectores de construcción</v>
+      </c>
+      <c r="R24" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S24" s="57" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T24" s="57" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U24" s="55" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.N.RH</v>
+      </c>
+      <c r="V24" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W24" s="58" t="str">
         <f t="shared" si="7"/>
-        <v>Inspectores de construcción</v>
-      </c>
-      <c r="R24" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S24" s="57" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T24" s="57" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U24" s="55" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.N.RH</v>
-      </c>
-      <c r="V24" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W24" s="58" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.24</v>
       </c>
       <c r="X24" s="40" t="s">
@@ -7027,14 +7101,14 @@
         <v>181</v>
       </c>
       <c r="Z24" s="59" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="AA24" s="59" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Construction inspectors</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="51">
         <v>25</v>
       </c>
@@ -7042,16 +7116,16 @@
         <v>395</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D25" s="35" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E25" s="35" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="G25" s="38" t="s">
         <v>181</v>
@@ -7069,48 +7143,48 @@
         <v>181</v>
       </c>
       <c r="L25" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M25" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N25" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="O25" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.N.Apoiador</v>
       </c>
       <c r="P25" s="63" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="Q25" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>Aficionados</v>
+      </c>
+      <c r="R25" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S25" s="57" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T25" s="57" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U25" s="55" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.N.RH</v>
+      </c>
+      <c r="V25" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W25" s="58" t="str">
         <f t="shared" si="7"/>
-        <v>Aficionados</v>
-      </c>
-      <c r="R25" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S25" s="57" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T25" s="57" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U25" s="55" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.N.RH</v>
-      </c>
-      <c r="V25" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W25" s="58" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.25</v>
       </c>
       <c r="X25" s="40" t="s">
@@ -7120,14 +7194,14 @@
         <v>181</v>
       </c>
       <c r="Z25" s="59" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="AA25" s="59" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Supporters</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="51">
         <v>26</v>
       </c>
@@ -7135,16 +7209,16 @@
         <v>395</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="G26" s="38" t="s">
         <v>181</v>
@@ -7162,48 +7236,48 @@
         <v>181</v>
       </c>
       <c r="L26" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M26" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N26" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="O26" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.N.Marketero</v>
       </c>
       <c r="P26" s="63" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="Q26" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>Profesionales del marketing</v>
+      </c>
+      <c r="R26" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S26" s="57" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T26" s="57" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U26" s="55" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.N.RH</v>
+      </c>
+      <c r="V26" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W26" s="58" t="str">
         <f t="shared" si="7"/>
-        <v>Profesionales del marketing</v>
-      </c>
-      <c r="R26" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S26" s="57" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T26" s="57" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U26" s="55" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.N.RH</v>
-      </c>
-      <c r="V26" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W26" s="58" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.26</v>
       </c>
       <c r="X26" s="40" t="s">
@@ -7213,14 +7287,14 @@
         <v>181</v>
       </c>
       <c r="Z26" s="59" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="AA26" s="59" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Marketers</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="51">
         <v>27</v>
       </c>
@@ -7228,16 +7302,16 @@
         <v>395</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D27" s="35" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E27" s="35" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G27" s="38" t="s">
         <v>181</v>
@@ -7255,48 +7329,48 @@
         <v>181</v>
       </c>
       <c r="L27" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M27" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N27" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="O27" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.N.Tercerizado</v>
       </c>
       <c r="P27" s="63" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="Q27" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>Subcontratado</v>
+      </c>
+      <c r="R27" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S27" s="57" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T27" s="57" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U27" s="55" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.N.RH</v>
+      </c>
+      <c r="V27" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W27" s="58" t="str">
         <f t="shared" si="7"/>
-        <v>Subcontratado</v>
-      </c>
-      <c r="R27" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S27" s="57" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T27" s="57" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U27" s="55" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.N.RH</v>
-      </c>
-      <c r="V27" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W27" s="58" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.27</v>
       </c>
       <c r="X27" s="40" t="s">
@@ -7306,14 +7380,14 @@
         <v>181</v>
       </c>
       <c r="Z27" s="59" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="AA27" s="59" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Outsourced</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" ht="5.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="51">
         <v>28</v>
       </c>
@@ -7321,16 +7395,16 @@
         <v>395</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D28" s="35" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="G28" s="38" t="s">
         <v>181</v>
@@ -7348,48 +7422,48 @@
         <v>181</v>
       </c>
       <c r="L28" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M28" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N28" s="55" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="O28" s="55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.N.Empresa</v>
       </c>
       <c r="P28" s="63" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="Q28" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>Empresas y Grupos Participantes</v>
+      </c>
+      <c r="R28" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="S28" s="57" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T28" s="57" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U28" s="55" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.N.RH</v>
+      </c>
+      <c r="V28" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="W28" s="58" t="str">
         <f t="shared" si="7"/>
-        <v>Empresas y Grupos Participantes</v>
-      </c>
-      <c r="R28" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="S28" s="57" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T28" s="57" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U28" s="55" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.N.RH</v>
-      </c>
-      <c r="V28" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="W28" s="58" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.28</v>
       </c>
       <c r="X28" s="40" t="s">
@@ -7399,27 +7473,32 @@
         <v>181</v>
       </c>
       <c r="Z28" s="59" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="AA28" s="59" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Participating Companies and Groups</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="AA1 AA7:AA28">
+    <cfRule type="cellIs" dxfId="10" priority="9" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A2:A28">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA28">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7572,7 +7651,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7617,7 +7696,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7642,7 +7721,7 @@
     <col min="10" max="10" width="4.296875" style="50" customWidth="1"/>
     <col min="11" max="11" width="14" style="50" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.5" style="50" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.19921875" style="50" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.19921875" style="50" customWidth="1"/>
     <col min="14" max="14" width="7" style="50" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="43.796875" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8.69921875" style="50" customWidth="1"/>
@@ -7757,13 +7836,13 @@
         <v>340</v>
       </c>
       <c r="K2" s="48" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="L2" s="47" t="s">
         <v>414</v>
       </c>
       <c r="M2" s="48" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="N2" s="49" t="s">
         <v>1</v>
@@ -7810,10 +7889,10 @@
         <v>344</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D3" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E3" s="62" t="s">
         <v>345</v>
@@ -7834,13 +7913,13 @@
         <v>340</v>
       </c>
       <c r="K3" s="48" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="L3" s="47" t="s">
         <v>414</v>
       </c>
       <c r="M3" s="48" t="s">
-        <v>494</v>
+        <v>540</v>
       </c>
       <c r="N3" s="49" t="s">
         <v>1</v>
@@ -7887,10 +7966,10 @@
         <v>342</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D4" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E4" s="62" t="s">
         <v>344</v>
@@ -7911,13 +7990,13 @@
         <v>340</v>
       </c>
       <c r="K4" s="48" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="L4" s="47" t="s">
         <v>414</v>
       </c>
       <c r="M4" s="48" t="s">
-        <v>494</v>
+        <v>541</v>
       </c>
       <c r="N4" s="49" t="s">
         <v>1</v>
@@ -7964,10 +8043,10 @@
         <v>188</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D5" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E5" s="62" t="s">
         <v>344</v>
@@ -7994,7 +8073,7 @@
         <v>414</v>
       </c>
       <c r="M5" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N5" s="49" t="s">
         <v>1</v>
@@ -8041,10 +8120,10 @@
         <v>189</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D6" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E6" s="62" t="s">
         <v>344</v>
@@ -8071,7 +8150,7 @@
         <v>414</v>
       </c>
       <c r="M6" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N6" s="49" t="s">
         <v>1</v>
@@ -8118,10 +8197,10 @@
         <v>190</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D7" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E7" s="62" t="s">
         <v>344</v>
@@ -8148,7 +8227,7 @@
         <v>414</v>
       </c>
       <c r="M7" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N7" s="49" t="s">
         <v>1</v>
@@ -8195,10 +8274,10 @@
         <v>191</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D8" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E8" s="62" t="s">
         <v>344</v>
@@ -8225,7 +8304,7 @@
         <v>414</v>
       </c>
       <c r="M8" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N8" s="49" t="s">
         <v>1</v>
@@ -8272,10 +8351,10 @@
         <v>192</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D9" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E9" s="62" t="s">
         <v>344</v>
@@ -8302,7 +8381,7 @@
         <v>414</v>
       </c>
       <c r="M9" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N9" s="49" t="s">
         <v>1</v>
@@ -8349,10 +8428,10 @@
         <v>193</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D10" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E10" s="62" t="s">
         <v>344</v>
@@ -8379,7 +8458,7 @@
         <v>414</v>
       </c>
       <c r="M10" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N10" s="49" t="s">
         <v>1</v>
@@ -8426,10 +8505,10 @@
         <v>194</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D11" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E11" s="62" t="s">
         <v>344</v>
@@ -8456,7 +8535,7 @@
         <v>414</v>
       </c>
       <c r="M11" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N11" s="49" t="s">
         <v>1</v>
@@ -8503,10 +8582,10 @@
         <v>195</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D12" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E12" s="62" t="s">
         <v>344</v>
@@ -8533,7 +8612,7 @@
         <v>414</v>
       </c>
       <c r="M12" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N12" s="49" t="s">
         <v>1</v>
@@ -8580,10 +8659,10 @@
         <v>196</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D13" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E13" s="62" t="s">
         <v>344</v>
@@ -8610,7 +8689,7 @@
         <v>414</v>
       </c>
       <c r="M13" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N13" s="49" t="s">
         <v>1</v>
@@ -8657,10 +8736,10 @@
         <v>197</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D14" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E14" s="62" t="s">
         <v>344</v>
@@ -8687,7 +8766,7 @@
         <v>414</v>
       </c>
       <c r="M14" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N14" s="49" t="s">
         <v>1</v>
@@ -8734,10 +8813,10 @@
         <v>198</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D15" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E15" s="62" t="s">
         <v>344</v>
@@ -8764,7 +8843,7 @@
         <v>414</v>
       </c>
       <c r="M15" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N15" s="49" t="s">
         <v>1</v>
@@ -8811,10 +8890,10 @@
         <v>199</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D16" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E16" s="62" t="s">
         <v>344</v>
@@ -8841,7 +8920,7 @@
         <v>414</v>
       </c>
       <c r="M16" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N16" s="49" t="s">
         <v>1</v>
@@ -8888,10 +8967,10 @@
         <v>200</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D17" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E17" s="62" t="s">
         <v>344</v>
@@ -8918,7 +8997,7 @@
         <v>414</v>
       </c>
       <c r="M17" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N17" s="49" t="s">
         <v>1</v>
@@ -8965,10 +9044,10 @@
         <v>201</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D18" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E18" s="62" t="s">
         <v>344</v>
@@ -8995,7 +9074,7 @@
         <v>414</v>
       </c>
       <c r="M18" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N18" s="49" t="s">
         <v>1</v>
@@ -9042,10 +9121,10 @@
         <v>202</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D19" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E19" s="62" t="s">
         <v>344</v>
@@ -9072,7 +9151,7 @@
         <v>414</v>
       </c>
       <c r="M19" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N19" s="49" t="s">
         <v>1</v>
@@ -9119,10 +9198,10 @@
         <v>203</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D20" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E20" s="62" t="s">
         <v>344</v>
@@ -9149,7 +9228,7 @@
         <v>414</v>
       </c>
       <c r="M20" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N20" s="49" t="s">
         <v>1</v>
@@ -9196,10 +9275,10 @@
         <v>204</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D21" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E21" s="62" t="s">
         <v>344</v>
@@ -9226,7 +9305,7 @@
         <v>414</v>
       </c>
       <c r="M21" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N21" s="49" t="s">
         <v>1</v>
@@ -9273,10 +9352,10 @@
         <v>205</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D22" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E22" s="62" t="s">
         <v>344</v>
@@ -9303,7 +9382,7 @@
         <v>414</v>
       </c>
       <c r="M22" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N22" s="49" t="s">
         <v>1</v>
@@ -9350,10 +9429,10 @@
         <v>206</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D23" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E23" s="62" t="s">
         <v>344</v>
@@ -9380,7 +9459,7 @@
         <v>414</v>
       </c>
       <c r="M23" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N23" s="49" t="s">
         <v>1</v>
@@ -9427,10 +9506,10 @@
         <v>207</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D24" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E24" s="62" t="s">
         <v>344</v>
@@ -9457,7 +9536,7 @@
         <v>414</v>
       </c>
       <c r="M24" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N24" s="49" t="s">
         <v>1</v>
@@ -9504,10 +9583,10 @@
         <v>208</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D25" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E25" s="62" t="s">
         <v>344</v>
@@ -9534,7 +9613,7 @@
         <v>414</v>
       </c>
       <c r="M25" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N25" s="49" t="s">
         <v>1</v>
@@ -9581,10 +9660,10 @@
         <v>209</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D26" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E26" s="62" t="s">
         <v>344</v>
@@ -9611,7 +9690,7 @@
         <v>414</v>
       </c>
       <c r="M26" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N26" s="49" t="s">
         <v>1</v>
@@ -9658,10 +9737,10 @@
         <v>210</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D27" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E27" s="62" t="s">
         <v>344</v>
@@ -9688,7 +9767,7 @@
         <v>414</v>
       </c>
       <c r="M27" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N27" s="49" t="s">
         <v>1</v>
@@ -9735,10 +9814,10 @@
         <v>211</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D28" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E28" s="62" t="s">
         <v>344</v>
@@ -9765,7 +9844,7 @@
         <v>414</v>
       </c>
       <c r="M28" s="48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N28" s="49" t="s">
         <v>1</v>
@@ -9812,10 +9891,10 @@
         <v>212</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D29" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E29" s="62" t="s">
         <v>344</v>
@@ -9842,7 +9921,7 @@
         <v>414</v>
       </c>
       <c r="M29" s="48" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N29" s="49" t="s">
         <v>1</v>
@@ -9889,10 +9968,10 @@
         <v>213</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D30" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E30" s="62" t="s">
         <v>344</v>
@@ -9919,7 +9998,7 @@
         <v>414</v>
       </c>
       <c r="M30" s="48" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N30" s="49" t="s">
         <v>1</v>
@@ -9966,10 +10045,10 @@
         <v>214</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D31" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E31" s="62" t="s">
         <v>344</v>
@@ -9996,7 +10075,7 @@
         <v>414</v>
       </c>
       <c r="M31" s="48" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N31" s="49" t="s">
         <v>1</v>
@@ -10043,10 +10122,10 @@
         <v>215</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D32" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E32" s="62" t="s">
         <v>344</v>
@@ -10073,7 +10152,7 @@
         <v>414</v>
       </c>
       <c r="M32" s="48" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N32" s="49" t="s">
         <v>1</v>
@@ -10120,10 +10199,10 @@
         <v>216</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D33" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E33" s="62" t="s">
         <v>344</v>
@@ -10150,7 +10229,7 @@
         <v>414</v>
       </c>
       <c r="M33" s="48" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N33" s="49" t="s">
         <v>1</v>
@@ -10197,10 +10276,10 @@
         <v>217</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D34" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E34" s="62" t="s">
         <v>344</v>
@@ -10227,7 +10306,7 @@
         <v>414</v>
       </c>
       <c r="M34" s="48" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N34" s="49" t="s">
         <v>1</v>
@@ -10274,10 +10353,10 @@
         <v>218</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D35" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E35" s="62" t="s">
         <v>344</v>
@@ -10304,7 +10383,7 @@
         <v>414</v>
       </c>
       <c r="M35" s="48" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N35" s="49" t="s">
         <v>1</v>
@@ -10351,10 +10430,10 @@
         <v>419</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D36" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E36" s="62" t="s">
         <v>344</v>
@@ -10381,7 +10460,7 @@
         <v>414</v>
       </c>
       <c r="M36" s="48" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N36" s="49" t="s">
         <v>1</v>
@@ -10428,10 +10507,10 @@
         <v>219</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D37" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E37" s="62" t="s">
         <v>344</v>
@@ -10458,7 +10537,7 @@
         <v>414</v>
       </c>
       <c r="M37" s="48" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N37" s="49" t="s">
         <v>1</v>
@@ -10505,10 +10584,10 @@
         <v>220</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D38" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E38" s="62" t="s">
         <v>344</v>
@@ -10535,7 +10614,7 @@
         <v>414</v>
       </c>
       <c r="M38" s="48" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N38" s="49" t="s">
         <v>1</v>
@@ -10582,10 +10661,10 @@
         <v>221</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D39" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E39" s="62" t="s">
         <v>344</v>
@@ -10612,7 +10691,7 @@
         <v>414</v>
       </c>
       <c r="M39" s="48" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N39" s="49" t="s">
         <v>1</v>
@@ -10659,10 +10738,10 @@
         <v>222</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D40" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E40" s="62" t="s">
         <v>344</v>
@@ -10689,7 +10768,7 @@
         <v>414</v>
       </c>
       <c r="M40" s="48" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N40" s="49" t="s">
         <v>1</v>
@@ -10736,10 +10815,10 @@
         <v>223</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D41" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E41" s="62" t="s">
         <v>344</v>
@@ -10766,7 +10845,7 @@
         <v>414</v>
       </c>
       <c r="M41" s="48" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N41" s="49" t="s">
         <v>1</v>
@@ -10813,10 +10892,10 @@
         <v>224</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D42" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E42" s="62" t="s">
         <v>344</v>
@@ -10843,7 +10922,7 @@
         <v>414</v>
       </c>
       <c r="M42" s="48" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N42" s="49" t="s">
         <v>1</v>
@@ -10890,10 +10969,10 @@
         <v>225</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D43" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E43" s="62" t="s">
         <v>344</v>
@@ -10920,7 +10999,7 @@
         <v>414</v>
       </c>
       <c r="M43" s="48" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N43" s="49" t="s">
         <v>1</v>
@@ -10967,10 +11046,10 @@
         <v>226</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D44" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E44" s="62" t="s">
         <v>344</v>
@@ -10997,7 +11076,7 @@
         <v>414</v>
       </c>
       <c r="M44" s="48" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N44" s="49" t="s">
         <v>1</v>
@@ -11044,10 +11123,10 @@
         <v>227</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D45" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E45" s="62" t="s">
         <v>344</v>
@@ -11074,7 +11153,7 @@
         <v>414</v>
       </c>
       <c r="M45" s="48" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N45" s="49" t="s">
         <v>1</v>
@@ -11121,10 +11200,10 @@
         <v>228</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D46" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E46" s="62" t="s">
         <v>344</v>
@@ -11151,7 +11230,7 @@
         <v>414</v>
       </c>
       <c r="M46" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N46" s="49" t="s">
         <v>1</v>
@@ -11198,10 +11277,10 @@
         <v>229</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D47" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E47" s="62" t="s">
         <v>344</v>
@@ -11228,7 +11307,7 @@
         <v>414</v>
       </c>
       <c r="M47" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N47" s="49" t="s">
         <v>1</v>
@@ -11275,10 +11354,10 @@
         <v>230</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D48" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E48" s="62" t="s">
         <v>344</v>
@@ -11305,7 +11384,7 @@
         <v>414</v>
       </c>
       <c r="M48" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N48" s="49" t="s">
         <v>1</v>
@@ -11352,10 +11431,10 @@
         <v>231</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D49" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E49" s="62" t="s">
         <v>344</v>
@@ -11382,7 +11461,7 @@
         <v>414</v>
       </c>
       <c r="M49" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N49" s="49" t="s">
         <v>1</v>
@@ -11429,10 +11508,10 @@
         <v>232</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D50" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E50" s="62" t="s">
         <v>344</v>
@@ -11459,7 +11538,7 @@
         <v>414</v>
       </c>
       <c r="M50" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N50" s="49" t="s">
         <v>1</v>
@@ -11506,10 +11585,10 @@
         <v>233</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D51" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E51" s="62" t="s">
         <v>344</v>
@@ -11536,7 +11615,7 @@
         <v>414</v>
       </c>
       <c r="M51" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N51" s="49" t="s">
         <v>1</v>
@@ -11583,10 +11662,10 @@
         <v>234</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D52" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E52" s="62" t="s">
         <v>344</v>
@@ -11613,7 +11692,7 @@
         <v>414</v>
       </c>
       <c r="M52" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N52" s="49" t="s">
         <v>1</v>
@@ -11660,10 +11739,10 @@
         <v>235</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D53" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E53" s="62" t="s">
         <v>344</v>
@@ -11690,7 +11769,7 @@
         <v>414</v>
       </c>
       <c r="M53" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N53" s="49" t="s">
         <v>1</v>
@@ -11737,10 +11816,10 @@
         <v>236</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D54" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E54" s="62" t="s">
         <v>344</v>
@@ -11767,7 +11846,7 @@
         <v>414</v>
       </c>
       <c r="M54" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N54" s="49" t="s">
         <v>1</v>
@@ -11814,10 +11893,10 @@
         <v>237</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D55" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E55" s="62" t="s">
         <v>344</v>
@@ -11844,7 +11923,7 @@
         <v>414</v>
       </c>
       <c r="M55" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N55" s="49" t="s">
         <v>1</v>
@@ -11891,10 +11970,10 @@
         <v>238</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D56" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E56" s="62" t="s">
         <v>344</v>
@@ -11921,7 +12000,7 @@
         <v>414</v>
       </c>
       <c r="M56" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N56" s="49" t="s">
         <v>1</v>
@@ -11968,10 +12047,10 @@
         <v>239</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D57" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E57" s="62" t="s">
         <v>344</v>
@@ -11998,7 +12077,7 @@
         <v>414</v>
       </c>
       <c r="M57" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N57" s="49" t="s">
         <v>1</v>
@@ -12045,10 +12124,10 @@
         <v>240</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D58" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E58" s="62" t="s">
         <v>344</v>
@@ -12075,7 +12154,7 @@
         <v>414</v>
       </c>
       <c r="M58" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N58" s="49" t="s">
         <v>1</v>
@@ -12122,10 +12201,10 @@
         <v>241</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D59" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E59" s="62" t="s">
         <v>344</v>
@@ -12152,7 +12231,7 @@
         <v>414</v>
       </c>
       <c r="M59" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N59" s="49" t="s">
         <v>1</v>
@@ -12199,10 +12278,10 @@
         <v>242</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D60" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E60" s="62" t="s">
         <v>344</v>
@@ -12229,7 +12308,7 @@
         <v>414</v>
       </c>
       <c r="M60" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N60" s="49" t="s">
         <v>1</v>
@@ -12276,10 +12355,10 @@
         <v>243</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D61" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E61" s="62" t="s">
         <v>344</v>
@@ -12306,7 +12385,7 @@
         <v>414</v>
       </c>
       <c r="M61" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N61" s="49" t="s">
         <v>1</v>
@@ -12353,10 +12432,10 @@
         <v>244</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D62" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E62" s="62" t="s">
         <v>344</v>
@@ -12383,7 +12462,7 @@
         <v>414</v>
       </c>
       <c r="M62" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N62" s="49" t="s">
         <v>1</v>
@@ -12430,10 +12509,10 @@
         <v>245</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D63" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E63" s="62" t="s">
         <v>344</v>
@@ -12460,7 +12539,7 @@
         <v>414</v>
       </c>
       <c r="M63" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N63" s="49" t="s">
         <v>1</v>
@@ -12507,10 +12586,10 @@
         <v>246</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D64" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E64" s="62" t="s">
         <v>344</v>
@@ -12537,7 +12616,7 @@
         <v>414</v>
       </c>
       <c r="M64" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N64" s="49" t="s">
         <v>1</v>
@@ -12584,10 +12663,10 @@
         <v>247</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D65" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E65" s="62" t="s">
         <v>344</v>
@@ -12614,7 +12693,7 @@
         <v>414</v>
       </c>
       <c r="M65" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N65" s="49" t="s">
         <v>1</v>
@@ -12661,10 +12740,10 @@
         <v>248</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D66" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E66" s="62" t="s">
         <v>344</v>
@@ -12691,7 +12770,7 @@
         <v>414</v>
       </c>
       <c r="M66" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N66" s="49" t="s">
         <v>1</v>
@@ -12738,10 +12817,10 @@
         <v>249</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D67" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E67" s="62" t="s">
         <v>344</v>
@@ -12768,7 +12847,7 @@
         <v>414</v>
       </c>
       <c r="M67" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N67" s="49" t="s">
         <v>1</v>
@@ -12815,10 +12894,10 @@
         <v>250</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D68" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E68" s="62" t="s">
         <v>344</v>
@@ -12845,7 +12924,7 @@
         <v>414</v>
       </c>
       <c r="M68" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N68" s="49" t="s">
         <v>1</v>
@@ -12892,10 +12971,10 @@
         <v>251</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D69" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E69" s="62" t="s">
         <v>344</v>
@@ -12922,7 +13001,7 @@
         <v>414</v>
       </c>
       <c r="M69" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N69" s="49" t="s">
         <v>1</v>
@@ -12969,10 +13048,10 @@
         <v>252</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D70" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E70" s="62" t="s">
         <v>344</v>
@@ -12999,7 +13078,7 @@
         <v>414</v>
       </c>
       <c r="M70" s="48" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N70" s="49" t="s">
         <v>1</v>
@@ -13046,10 +13125,10 @@
         <v>253</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D71" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E71" s="62" t="s">
         <v>344</v>
@@ -13076,7 +13155,7 @@
         <v>414</v>
       </c>
       <c r="M71" s="48" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N71" s="49" t="s">
         <v>1</v>
@@ -13123,10 +13202,10 @@
         <v>254</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D72" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E72" s="62" t="s">
         <v>344</v>
@@ -13153,7 +13232,7 @@
         <v>414</v>
       </c>
       <c r="M72" s="48" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N72" s="49" t="s">
         <v>1</v>
@@ -13200,10 +13279,10 @@
         <v>255</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D73" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E73" s="62" t="s">
         <v>344</v>
@@ -13230,7 +13309,7 @@
         <v>414</v>
       </c>
       <c r="M73" s="48" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N73" s="49" t="s">
         <v>1</v>
@@ -13277,10 +13356,10 @@
         <v>256</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D74" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E74" s="62" t="s">
         <v>344</v>
@@ -13307,7 +13386,7 @@
         <v>414</v>
       </c>
       <c r="M74" s="48" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N74" s="49" t="s">
         <v>1</v>
@@ -13354,10 +13433,10 @@
         <v>257</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D75" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E75" s="62" t="s">
         <v>344</v>
@@ -13384,7 +13463,7 @@
         <v>414</v>
       </c>
       <c r="M75" s="48" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N75" s="49" t="s">
         <v>1</v>
@@ -13431,10 +13510,10 @@
         <v>258</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D76" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E76" s="62" t="s">
         <v>344</v>
@@ -13461,7 +13540,7 @@
         <v>414</v>
       </c>
       <c r="M76" s="48" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N76" s="49" t="s">
         <v>1</v>
@@ -13508,10 +13587,10 @@
         <v>259</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D77" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E77" s="62" t="s">
         <v>344</v>
@@ -13538,7 +13617,7 @@
         <v>414</v>
       </c>
       <c r="M77" s="48" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N77" s="49" t="s">
         <v>1</v>
@@ -13585,10 +13664,10 @@
         <v>260</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D78" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E78" s="62" t="s">
         <v>344</v>
@@ -13615,7 +13694,7 @@
         <v>414</v>
       </c>
       <c r="M78" s="48" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N78" s="49" t="s">
         <v>1</v>
@@ -13662,10 +13741,10 @@
         <v>261</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D79" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E79" s="62" t="s">
         <v>344</v>
@@ -13692,7 +13771,7 @@
         <v>414</v>
       </c>
       <c r="M79" s="48" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N79" s="49" t="s">
         <v>1</v>
@@ -13739,10 +13818,10 @@
         <v>262</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D80" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E80" s="62" t="s">
         <v>344</v>
@@ -13769,7 +13848,7 @@
         <v>414</v>
       </c>
       <c r="M80" s="48" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N80" s="49" t="s">
         <v>1</v>
@@ -13816,10 +13895,10 @@
         <v>263</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D81" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E81" s="62" t="s">
         <v>344</v>
@@ -13846,7 +13925,7 @@
         <v>414</v>
       </c>
       <c r="M81" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N81" s="49" t="s">
         <v>1</v>
@@ -13893,10 +13972,10 @@
         <v>264</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D82" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E82" s="62" t="s">
         <v>344</v>
@@ -13923,7 +14002,7 @@
         <v>414</v>
       </c>
       <c r="M82" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N82" s="49" t="s">
         <v>1</v>
@@ -13970,10 +14049,10 @@
         <v>265</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D83" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E83" s="62" t="s">
         <v>344</v>
@@ -14000,7 +14079,7 @@
         <v>414</v>
       </c>
       <c r="M83" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N83" s="49" t="s">
         <v>1</v>
@@ -14047,10 +14126,10 @@
         <v>266</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D84" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E84" s="62" t="s">
         <v>344</v>
@@ -14077,7 +14156,7 @@
         <v>414</v>
       </c>
       <c r="M84" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N84" s="49" t="s">
         <v>1</v>
@@ -14124,10 +14203,10 @@
         <v>267</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D85" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E85" s="62" t="s">
         <v>344</v>
@@ -14154,7 +14233,7 @@
         <v>414</v>
       </c>
       <c r="M85" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N85" s="49" t="s">
         <v>1</v>
@@ -14201,10 +14280,10 @@
         <v>268</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D86" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E86" s="62" t="s">
         <v>344</v>
@@ -14231,7 +14310,7 @@
         <v>414</v>
       </c>
       <c r="M86" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N86" s="49" t="s">
         <v>1</v>
@@ -14278,10 +14357,10 @@
         <v>269</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D87" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E87" s="62" t="s">
         <v>344</v>
@@ -14308,7 +14387,7 @@
         <v>414</v>
       </c>
       <c r="M87" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N87" s="49" t="s">
         <v>1</v>
@@ -14355,10 +14434,10 @@
         <v>270</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D88" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E88" s="62" t="s">
         <v>344</v>
@@ -14385,7 +14464,7 @@
         <v>414</v>
       </c>
       <c r="M88" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N88" s="49" t="s">
         <v>1</v>
@@ -14432,10 +14511,10 @@
         <v>271</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D89" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E89" s="62" t="s">
         <v>344</v>
@@ -14462,7 +14541,7 @@
         <v>414</v>
       </c>
       <c r="M89" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N89" s="49" t="s">
         <v>1</v>
@@ -14509,10 +14588,10 @@
         <v>272</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D90" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E90" s="62" t="s">
         <v>344</v>
@@ -14539,7 +14618,7 @@
         <v>414</v>
       </c>
       <c r="M90" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N90" s="49" t="s">
         <v>1</v>
@@ -14586,10 +14665,10 @@
         <v>273</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D91" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E91" s="62" t="s">
         <v>344</v>
@@ -14616,7 +14695,7 @@
         <v>414</v>
       </c>
       <c r="M91" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N91" s="49" t="s">
         <v>1</v>
@@ -14663,10 +14742,10 @@
         <v>274</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D92" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E92" s="62" t="s">
         <v>344</v>
@@ -14693,7 +14772,7 @@
         <v>414</v>
       </c>
       <c r="M92" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N92" s="49" t="s">
         <v>1</v>
@@ -14740,10 +14819,10 @@
         <v>275</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D93" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E93" s="62" t="s">
         <v>344</v>
@@ -14770,7 +14849,7 @@
         <v>414</v>
       </c>
       <c r="M93" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N93" s="49" t="s">
         <v>1</v>
@@ -14817,10 +14896,10 @@
         <v>276</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D94" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E94" s="62" t="s">
         <v>344</v>
@@ -14847,7 +14926,7 @@
         <v>414</v>
       </c>
       <c r="M94" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N94" s="49" t="s">
         <v>1</v>
@@ -14894,10 +14973,10 @@
         <v>277</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D95" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E95" s="62" t="s">
         <v>344</v>
@@ -14924,7 +15003,7 @@
         <v>414</v>
       </c>
       <c r="M95" s="48" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N95" s="49" t="s">
         <v>1</v>
@@ -14971,10 +15050,10 @@
         <v>278</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D96" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E96" s="62" t="s">
         <v>344</v>
@@ -15001,7 +15080,7 @@
         <v>414</v>
       </c>
       <c r="M96" s="48" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N96" s="49" t="s">
         <v>1</v>
@@ -15048,10 +15127,10 @@
         <v>279</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D97" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E97" s="62" t="s">
         <v>344</v>
@@ -15078,7 +15157,7 @@
         <v>414</v>
       </c>
       <c r="M97" s="48" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N97" s="49" t="s">
         <v>1</v>
@@ -15125,10 +15204,10 @@
         <v>280</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D98" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E98" s="62" t="s">
         <v>344</v>
@@ -15155,7 +15234,7 @@
         <v>414</v>
       </c>
       <c r="M98" s="48" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N98" s="49" t="s">
         <v>1</v>
@@ -15202,10 +15281,10 @@
         <v>281</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D99" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E99" s="62" t="s">
         <v>344</v>
@@ -15232,7 +15311,7 @@
         <v>414</v>
       </c>
       <c r="M99" s="48" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N99" s="49" t="s">
         <v>1</v>
@@ -15279,10 +15358,10 @@
         <v>282</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D100" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E100" s="62" t="s">
         <v>344</v>
@@ -15309,7 +15388,7 @@
         <v>414</v>
       </c>
       <c r="M100" s="48" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N100" s="49" t="s">
         <v>1</v>
@@ -15356,10 +15435,10 @@
         <v>283</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D101" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E101" s="62" t="s">
         <v>344</v>
@@ -15386,7 +15465,7 @@
         <v>414</v>
       </c>
       <c r="M101" s="48" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N101" s="49" t="s">
         <v>1</v>
@@ -15433,10 +15512,10 @@
         <v>284</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D102" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E102" s="62" t="s">
         <v>344</v>
@@ -15463,7 +15542,7 @@
         <v>414</v>
       </c>
       <c r="M102" s="48" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N102" s="49" t="s">
         <v>1</v>
@@ -15510,10 +15589,10 @@
         <v>285</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D103" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E103" s="62" t="s">
         <v>344</v>
@@ -15540,7 +15619,7 @@
         <v>414</v>
       </c>
       <c r="M103" s="48" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N103" s="49" t="s">
         <v>1</v>
@@ -15587,10 +15666,10 @@
         <v>286</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D104" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E104" s="62" t="s">
         <v>344</v>
@@ -15617,7 +15696,7 @@
         <v>414</v>
       </c>
       <c r="M104" s="48" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N104" s="49" t="s">
         <v>1</v>
@@ -15664,10 +15743,10 @@
         <v>287</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D105" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E105" s="62" t="s">
         <v>344</v>
@@ -15694,7 +15773,7 @@
         <v>414</v>
       </c>
       <c r="M105" s="48" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N105" s="49" t="s">
         <v>1</v>
@@ -15741,10 +15820,10 @@
         <v>288</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D106" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E106" s="62" t="s">
         <v>344</v>
@@ -15771,7 +15850,7 @@
         <v>414</v>
       </c>
       <c r="M106" s="48" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N106" s="49" t="s">
         <v>1</v>
@@ -15818,10 +15897,10 @@
         <v>289</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D107" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E107" s="62" t="s">
         <v>344</v>
@@ -15848,7 +15927,7 @@
         <v>414</v>
       </c>
       <c r="M107" s="48" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N107" s="49" t="s">
         <v>1</v>
@@ -15895,10 +15974,10 @@
         <v>290</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D108" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E108" s="62" t="s">
         <v>344</v>
@@ -15925,7 +16004,7 @@
         <v>414</v>
       </c>
       <c r="M108" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N108" s="49" t="s">
         <v>1</v>
@@ -15972,10 +16051,10 @@
         <v>291</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D109" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E109" s="62" t="s">
         <v>344</v>
@@ -16002,7 +16081,7 @@
         <v>414</v>
       </c>
       <c r="M109" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N109" s="49" t="s">
         <v>1</v>
@@ -16049,10 +16128,10 @@
         <v>292</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D110" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E110" s="62" t="s">
         <v>344</v>
@@ -16079,7 +16158,7 @@
         <v>414</v>
       </c>
       <c r="M110" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N110" s="49" t="s">
         <v>1</v>
@@ -16126,10 +16205,10 @@
         <v>293</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D111" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E111" s="62" t="s">
         <v>344</v>
@@ -16156,7 +16235,7 @@
         <v>414</v>
       </c>
       <c r="M111" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N111" s="49" t="s">
         <v>1</v>
@@ -16203,10 +16282,10 @@
         <v>294</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D112" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E112" s="62" t="s">
         <v>344</v>
@@ -16233,7 +16312,7 @@
         <v>414</v>
       </c>
       <c r="M112" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N112" s="49" t="s">
         <v>1</v>
@@ -16280,10 +16359,10 @@
         <v>295</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D113" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E113" s="62" t="s">
         <v>344</v>
@@ -16310,7 +16389,7 @@
         <v>414</v>
       </c>
       <c r="M113" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N113" s="49" t="s">
         <v>1</v>
@@ -16357,10 +16436,10 @@
         <v>296</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D114" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E114" s="62" t="s">
         <v>344</v>
@@ -16387,7 +16466,7 @@
         <v>414</v>
       </c>
       <c r="M114" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N114" s="49" t="s">
         <v>1</v>
@@ -16434,10 +16513,10 @@
         <v>297</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D115" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E115" s="62" t="s">
         <v>344</v>
@@ -16464,7 +16543,7 @@
         <v>414</v>
       </c>
       <c r="M115" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N115" s="49" t="s">
         <v>1</v>
@@ -16511,10 +16590,10 @@
         <v>298</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D116" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E116" s="62" t="s">
         <v>344</v>
@@ -16541,7 +16620,7 @@
         <v>414</v>
       </c>
       <c r="M116" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N116" s="49" t="s">
         <v>1</v>
@@ -16588,10 +16667,10 @@
         <v>299</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D117" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E117" s="62" t="s">
         <v>344</v>
@@ -16618,7 +16697,7 @@
         <v>414</v>
       </c>
       <c r="M117" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N117" s="49" t="s">
         <v>1</v>
@@ -16665,10 +16744,10 @@
         <v>300</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D118" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E118" s="62" t="s">
         <v>344</v>
@@ -16695,7 +16774,7 @@
         <v>414</v>
       </c>
       <c r="M118" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N118" s="49" t="s">
         <v>1</v>
@@ -16742,10 +16821,10 @@
         <v>301</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D119" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E119" s="62" t="s">
         <v>344</v>
@@ -16772,7 +16851,7 @@
         <v>414</v>
       </c>
       <c r="M119" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N119" s="49" t="s">
         <v>1</v>
@@ -16819,10 +16898,10 @@
         <v>302</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D120" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E120" s="62" t="s">
         <v>344</v>
@@ -16849,7 +16928,7 @@
         <v>414</v>
       </c>
       <c r="M120" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N120" s="49" t="s">
         <v>1</v>
@@ -16896,10 +16975,10 @@
         <v>303</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D121" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E121" s="62" t="s">
         <v>344</v>
@@ -16926,7 +17005,7 @@
         <v>414</v>
       </c>
       <c r="M121" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N121" s="49" t="s">
         <v>1</v>
@@ -16973,10 +17052,10 @@
         <v>304</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D122" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E122" s="62" t="s">
         <v>344</v>
@@ -17003,7 +17082,7 @@
         <v>414</v>
       </c>
       <c r="M122" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N122" s="49" t="s">
         <v>1</v>
@@ -17050,10 +17129,10 @@
         <v>305</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D123" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E123" s="62" t="s">
         <v>344</v>
@@ -17080,7 +17159,7 @@
         <v>414</v>
       </c>
       <c r="M123" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N123" s="49" t="s">
         <v>1</v>
@@ -17127,10 +17206,10 @@
         <v>306</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D124" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E124" s="62" t="s">
         <v>344</v>
@@ -17157,7 +17236,7 @@
         <v>414</v>
       </c>
       <c r="M124" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N124" s="49" t="s">
         <v>1</v>
@@ -17204,10 +17283,10 @@
         <v>307</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D125" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E125" s="62" t="s">
         <v>344</v>
@@ -17234,7 +17313,7 @@
         <v>414</v>
       </c>
       <c r="M125" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N125" s="49" t="s">
         <v>1</v>
@@ -17281,10 +17360,10 @@
         <v>308</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D126" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E126" s="62" t="s">
         <v>344</v>
@@ -17311,7 +17390,7 @@
         <v>414</v>
       </c>
       <c r="M126" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N126" s="49" t="s">
         <v>1</v>
@@ -17358,10 +17437,10 @@
         <v>309</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D127" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E127" s="62" t="s">
         <v>344</v>
@@ -17388,7 +17467,7 @@
         <v>414</v>
       </c>
       <c r="M127" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N127" s="49" t="s">
         <v>1</v>
@@ -17435,10 +17514,10 @@
         <v>310</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D128" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E128" s="62" t="s">
         <v>344</v>
@@ -17465,7 +17544,7 @@
         <v>414</v>
       </c>
       <c r="M128" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N128" s="49" t="s">
         <v>1</v>
@@ -17512,10 +17591,10 @@
         <v>311</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D129" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E129" s="62" t="s">
         <v>344</v>
@@ -17542,7 +17621,7 @@
         <v>414</v>
       </c>
       <c r="M129" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N129" s="49" t="s">
         <v>1</v>
@@ -17589,10 +17668,10 @@
         <v>312</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D130" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E130" s="62" t="s">
         <v>344</v>
@@ -17619,7 +17698,7 @@
         <v>414</v>
       </c>
       <c r="M130" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N130" s="49" t="s">
         <v>1</v>
@@ -17666,10 +17745,10 @@
         <v>313</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D131" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E131" s="62" t="s">
         <v>344</v>
@@ -17696,7 +17775,7 @@
         <v>414</v>
       </c>
       <c r="M131" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N131" s="49" t="s">
         <v>1</v>
@@ -17743,10 +17822,10 @@
         <v>314</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D132" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E132" s="62" t="s">
         <v>344</v>
@@ -17773,7 +17852,7 @@
         <v>414</v>
       </c>
       <c r="M132" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N132" s="49" t="s">
         <v>1</v>
@@ -17820,10 +17899,10 @@
         <v>315</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D133" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E133" s="62" t="s">
         <v>344</v>
@@ -17850,7 +17929,7 @@
         <v>414</v>
       </c>
       <c r="M133" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N133" s="49" t="s">
         <v>1</v>
@@ -17897,10 +17976,10 @@
         <v>316</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D134" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E134" s="62" t="s">
         <v>344</v>
@@ -17927,7 +18006,7 @@
         <v>414</v>
       </c>
       <c r="M134" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N134" s="49" t="s">
         <v>1</v>
@@ -17974,10 +18053,10 @@
         <v>317</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D135" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E135" s="62" t="s">
         <v>344</v>
@@ -18004,7 +18083,7 @@
         <v>414</v>
       </c>
       <c r="M135" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N135" s="49" t="s">
         <v>1</v>
@@ -18051,10 +18130,10 @@
         <v>318</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D136" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E136" s="62" t="s">
         <v>344</v>
@@ -18081,7 +18160,7 @@
         <v>414</v>
       </c>
       <c r="M136" s="48" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N136" s="49" t="s">
         <v>1</v>
@@ -18128,10 +18207,10 @@
         <v>319</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D137" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E137" s="62" t="s">
         <v>344</v>
@@ -18158,7 +18237,7 @@
         <v>414</v>
       </c>
       <c r="M137" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N137" s="49" t="s">
         <v>1</v>
@@ -18205,10 +18284,10 @@
         <v>320</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D138" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E138" s="62" t="s">
         <v>344</v>
@@ -18235,7 +18314,7 @@
         <v>414</v>
       </c>
       <c r="M138" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N138" s="49" t="s">
         <v>1</v>
@@ -18282,10 +18361,10 @@
         <v>321</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D139" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E139" s="62" t="s">
         <v>344</v>
@@ -18312,7 +18391,7 @@
         <v>414</v>
       </c>
       <c r="M139" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N139" s="49" t="s">
         <v>1</v>
@@ -18359,10 +18438,10 @@
         <v>322</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D140" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E140" s="62" t="s">
         <v>344</v>
@@ -18389,7 +18468,7 @@
         <v>414</v>
       </c>
       <c r="M140" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N140" s="49" t="s">
         <v>1</v>
@@ -18436,10 +18515,10 @@
         <v>323</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D141" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E141" s="62" t="s">
         <v>344</v>
@@ -18466,7 +18545,7 @@
         <v>414</v>
       </c>
       <c r="M141" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N141" s="49" t="s">
         <v>1</v>
@@ -18513,10 +18592,10 @@
         <v>324</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D142" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E142" s="62" t="s">
         <v>344</v>
@@ -18543,7 +18622,7 @@
         <v>414</v>
       </c>
       <c r="M142" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N142" s="49" t="s">
         <v>1</v>
@@ -18590,10 +18669,10 @@
         <v>325</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D143" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E143" s="62" t="s">
         <v>344</v>
@@ -18620,7 +18699,7 @@
         <v>414</v>
       </c>
       <c r="M143" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N143" s="49" t="s">
         <v>1</v>
@@ -18667,10 +18746,10 @@
         <v>420</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D144" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E144" s="62" t="s">
         <v>344</v>
@@ -18697,7 +18776,7 @@
         <v>414</v>
       </c>
       <c r="M144" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N144" s="49" t="s">
         <v>1</v>
@@ -18744,10 +18823,10 @@
         <v>326</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D145" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E145" s="62" t="s">
         <v>344</v>
@@ -18774,7 +18853,7 @@
         <v>414</v>
       </c>
       <c r="M145" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N145" s="49" t="s">
         <v>1</v>
@@ -18821,10 +18900,10 @@
         <v>327</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D146" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E146" s="62" t="s">
         <v>344</v>
@@ -18851,7 +18930,7 @@
         <v>414</v>
       </c>
       <c r="M146" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N146" s="49" t="s">
         <v>1</v>
@@ -18898,10 +18977,10 @@
         <v>328</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D147" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E147" s="62" t="s">
         <v>344</v>
@@ -18928,7 +19007,7 @@
         <v>414</v>
       </c>
       <c r="M147" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N147" s="49" t="s">
         <v>1</v>
@@ -18975,10 +19054,10 @@
         <v>329</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D148" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E148" s="62" t="s">
         <v>344</v>
@@ -19005,7 +19084,7 @@
         <v>414</v>
       </c>
       <c r="M148" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N148" s="49" t="s">
         <v>1</v>
@@ -19052,10 +19131,10 @@
         <v>330</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D149" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E149" s="62" t="s">
         <v>344</v>
@@ -19082,7 +19161,7 @@
         <v>414</v>
       </c>
       <c r="M149" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N149" s="49" t="s">
         <v>1</v>
@@ -19129,10 +19208,10 @@
         <v>331</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D150" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E150" s="62" t="s">
         <v>344</v>
@@ -19159,7 +19238,7 @@
         <v>414</v>
       </c>
       <c r="M150" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N150" s="49" t="s">
         <v>1</v>
@@ -19206,10 +19285,10 @@
         <v>332</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D151" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E151" s="62" t="s">
         <v>344</v>
@@ -19236,7 +19315,7 @@
         <v>414</v>
       </c>
       <c r="M151" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N151" s="49" t="s">
         <v>1</v>
@@ -19283,10 +19362,10 @@
         <v>333</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D152" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E152" s="62" t="s">
         <v>344</v>
@@ -19313,7 +19392,7 @@
         <v>414</v>
       </c>
       <c r="M152" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N152" s="49" t="s">
         <v>1</v>
@@ -19360,10 +19439,10 @@
         <v>334</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D153" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E153" s="62" t="s">
         <v>344</v>
@@ -19390,7 +19469,7 @@
         <v>414</v>
       </c>
       <c r="M153" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N153" s="49" t="s">
         <v>1</v>
@@ -19437,10 +19516,10 @@
         <v>335</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D154" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E154" s="62" t="s">
         <v>344</v>
@@ -19467,7 +19546,7 @@
         <v>414</v>
       </c>
       <c r="M154" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N154" s="49" t="s">
         <v>1</v>
@@ -19514,10 +19593,10 @@
         <v>336</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D155" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E155" s="62" t="s">
         <v>344</v>
@@ -19544,7 +19623,7 @@
         <v>414</v>
       </c>
       <c r="M155" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N155" s="49" t="s">
         <v>1</v>
@@ -19591,10 +19670,10 @@
         <v>337</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D156" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E156" s="62" t="s">
         <v>344</v>
@@ -19621,7 +19700,7 @@
         <v>414</v>
       </c>
       <c r="M156" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N156" s="49" t="s">
         <v>1</v>
@@ -19668,10 +19747,10 @@
         <v>338</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D157" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E157" s="62" t="s">
         <v>344</v>
@@ -19698,7 +19777,7 @@
         <v>414</v>
       </c>
       <c r="M157" s="48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N157" s="49" t="s">
         <v>1</v>
@@ -19740,10 +19819,10 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2N.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47B14F7-2B68-41A0-8387-3A70D10B0E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -2290,63 +2290,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A0D90F96-026A-4EEB-BDCF-93327D239D7A}"/>
   </cellStyles>
-  <dxfs count="71">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="65">
     <dxf>
       <font>
         <b val="0"/>
@@ -4239,33 +4183,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" tableBorderDxfId="67" totalsRowBorderDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="64" dataDxfId="62" headerRowBorderDxfId="63" tableBorderDxfId="61" totalsRowBorderDxfId="60">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="65" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="61" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="13" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="11" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4793,7 +4737,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46167.41566712963</v>
+        <v>46214.346850462964</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>406</v>
@@ -5495,7 +5439,7 @@
         <v>181</v>
       </c>
       <c r="L7" s="55" t="str">
-        <f t="shared" ref="L2:N17" si="4">CONCATENATE("", C7)</f>
+        <f t="shared" ref="L7:N17" si="4">CONCATENATE("", C7)</f>
         <v>Norma</v>
       </c>
       <c r="M7" s="55" t="str">
@@ -5535,7 +5479,7 @@
         <v>426</v>
       </c>
       <c r="W7" s="58" t="str">
-        <f t="shared" ref="W2:W28" si="7">CONCATENATE("Key.ABNT.",A7)</f>
+        <f t="shared" ref="W7:W28" si="7">CONCATENATE("Key.ABNT.",A7)</f>
         <v>Key.ABNT.7</v>
       </c>
       <c r="X7" s="40" t="s">
@@ -7481,24 +7425,19 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AA1 AA7:AA28">
-    <cfRule type="cellIs" dxfId="10" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2:A28">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="AA1:AA28">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7651,7 +7590,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7696,7 +7635,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19819,10 +19758,10 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2N.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C623C3D0-6851-4C2A-83BD-B1AB7A5A7DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFCBDD7-E7D5-46E6-9564-8B12D63BC55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4375" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4375" uniqueCount="540">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1696,9 +1696,6 @@
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
-    <t>Arquitetura</t>
   </si>
   <si>
     <t>[ 5I ]</t>
@@ -2254,63 +2251,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A0D90F96-026A-4EEB-BDCF-93327D239D7A}"/>
   </cellStyles>
-  <dxfs count="71">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="65">
     <dxf>
       <font>
         <b val="0"/>
@@ -4203,33 +4144,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" tableBorderDxfId="67" totalsRowBorderDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="64" dataDxfId="62" headerRowBorderDxfId="63" tableBorderDxfId="61" totalsRowBorderDxfId="60">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="65" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="61" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="13" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="11" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4757,7 +4698,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46216.266798726851</v>
+        <v>46219.568960300923</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>405</v>
@@ -4862,7 +4803,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958751C2-A34E-4345-8D6A-082603A025F9}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA28"/>
-  <sheetFormatPr defaultRowHeight="5.65" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="6.83203125" style="34" customWidth="1"/>
@@ -4886,7 +4827,7 @@
     <col min="27" max="27" width="64.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="31.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="22" t="s">
         <v>349</v>
       </c>
@@ -4969,7 +4910,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="34" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="49">
         <v>2</v>
       </c>
@@ -5041,7 +4982,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="38" t="s">
-        <v>535</v>
+        <v>423</v>
       </c>
       <c r="W2" s="59" t="str">
         <f>CONCATENATE("Key-ABNT-",A2)</f>
@@ -5054,14 +4995,14 @@
         <v>181</v>
       </c>
       <c r="Z2" s="38" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AA2" s="38" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="34" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="49">
         <v>3</v>
       </c>
@@ -5112,7 +5053,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="38" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="Q3" s="38" t="s">
         <v>534</v>
@@ -5133,7 +5074,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="38" t="s">
-        <v>535</v>
+        <v>423</v>
       </c>
       <c r="W3" s="59" t="str">
         <f t="shared" ref="W3:W28" si="4">CONCATENATE("Key-ABNT-",A3)</f>
@@ -5153,7 +5094,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="34" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -5204,7 +5145,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="38" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Q4" s="38" t="s">
         <v>534</v>
@@ -5225,7 +5166,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="38" t="s">
-        <v>535</v>
+        <v>423</v>
       </c>
       <c r="W4" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5245,7 +5186,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="34" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="49">
         <v>5</v>
       </c>
@@ -5296,7 +5237,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="Q5" s="38" t="s">
         <v>534</v>
@@ -5317,7 +5258,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="38" t="s">
-        <v>535</v>
+        <v>423</v>
       </c>
       <c r="W5" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5337,7 +5278,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="34" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="49">
         <v>6</v>
       </c>
@@ -5388,7 +5329,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="Q6" s="38" t="s">
         <v>534</v>
@@ -5409,7 +5350,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="38" t="s">
-        <v>535</v>
+        <v>423</v>
       </c>
       <c r="W6" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5429,7 +5370,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="49">
         <v>7</v>
       </c>
@@ -5520,7 +5461,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="49">
         <v>8</v>
       </c>
@@ -5611,7 +5552,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="49">
         <v>9</v>
       </c>
@@ -5702,7 +5643,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="49">
         <v>10</v>
       </c>
@@ -5793,7 +5734,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="49">
         <v>11</v>
       </c>
@@ -5884,7 +5825,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="49">
         <v>12</v>
       </c>
@@ -5975,7 +5916,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="49">
         <v>13</v>
       </c>
@@ -6066,7 +6007,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="49">
         <v>14</v>
       </c>
@@ -6157,7 +6098,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="49">
         <v>15</v>
       </c>
@@ -6248,7 +6189,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="49">
         <v>16</v>
       </c>
@@ -6339,7 +6280,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="49">
         <v>17</v>
       </c>
@@ -6430,7 +6371,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="49">
         <v>18</v>
       </c>
@@ -6521,7 +6462,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="49">
         <v>19</v>
       </c>
@@ -6612,7 +6553,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="49">
         <v>20</v>
       </c>
@@ -6705,7 +6646,7 @@
         <v>Entrepreneurs</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="49">
         <v>21</v>
       </c>
@@ -6798,7 +6739,7 @@
         <v>Designers</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="49">
         <v>22</v>
       </c>
@@ -6891,7 +6832,7 @@
         <v>Managers</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="49">
         <v>23</v>
       </c>
@@ -6984,7 +6925,7 @@
         <v>Builders and Contractors</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="49">
         <v>24</v>
       </c>
@@ -7077,7 +7018,7 @@
         <v>Construction inspectors</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="49">
         <v>25</v>
       </c>
@@ -7170,7 +7111,7 @@
         <v>Supporters</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="49">
         <v>26</v>
       </c>
@@ -7263,7 +7204,7 @@
         <v>Marketers</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="49">
         <v>27</v>
       </c>
@@ -7356,7 +7297,7 @@
         <v>Outsourced</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="5.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="49">
         <v>28</v>
       </c>
@@ -7450,29 +7391,19 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A28">
-    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA28">
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B28">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B6 B7:B28">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA1:AA28">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7625,7 +7556,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7670,7 +7601,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19793,10 +19724,10 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2N.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DDCD3D-7361-402E-AEF3-5F5B6928FBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805BE79A-AF5A-4CC0-9D13-6932C2B2F11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4375" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4375" uniqueCount="546">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1374,141 +1374,42 @@
     <t>Requisito.Sistemas</t>
   </si>
   <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0M.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0M.</t>
-  </si>
-  <si>
     <t>0M</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0M.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0P.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0P.</t>
-  </si>
-  <si>
     <t>0P</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0P.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1D.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1D.</t>
-  </si>
-  <si>
     <t>1D</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1D.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1F.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1F.</t>
-  </si>
-  <si>
     <t>1F</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1F.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1S.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1S.</t>
-  </si>
-  <si>
     <t>1S</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1S.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 2C.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 2C.</t>
-  </si>
-  <si>
     <t>2C</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 2C.</t>
-  </si>
-  <si>
     <t>2Q</t>
   </si>
   <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 3E.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 3E.</t>
-  </si>
-  <si>
     <t>3E</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 3E.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 3R.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 3R.</t>
-  </si>
-  <si>
     <t>3R</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 3R.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 4A.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 4A.</t>
-  </si>
-  <si>
     <t>4A</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 4A.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 4U.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 4U.</t>
-  </si>
-  <si>
     <t>4U</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 4U.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 5I.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 5I.</t>
-  </si>
-  <si>
     <t>5I</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I.</t>
-  </si>
-  <si>
     <t>"Empreendedores"</t>
   </si>
   <si>
@@ -1708,6 +1609,126 @@
   </si>
   <si>
     <t>NBR.Temática</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0M. Códigos de Materiais.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0M. Códigos de materiales.</t>
+  </si>
+  <si>
+    <t>Interdiciplinar</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0M. Material Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0P. Códigos de Propriedades.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0P. Códigos de propiedad.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0P. Property Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1D. Códigos de Disciplinas.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1D. Códigos disciplinarios.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1D. Discipline Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1F. Códigos de Fases.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1F. Códigos de fase.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1F. Phase Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1S. Códigos de Serviços.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1S. Códigos de servicio.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1S. Service Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 2C. Códigos de Produtos construtivos.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 2C. Códigos de Productos Constructivos.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 2C. Codes of Constructive Products.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 2N. Códigos de Recursos Humanos.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 2N. Códigos de Recursos Humanos.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 2N. Human Resources Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 2Q. Códigos de Equipamentos.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 2Q. Códigos de equipo.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 2Q. Equipment Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 3E. Códigos de Elementos da construção.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 3E. Códigos de elementos de edificio.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 3E. Building Element Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 3R. Códigos de Recursos da construção.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 3R. Códigos de recursos de construcción.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 3R. Building Resource Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 4A. Códigos de Ambientes.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 4A. Códigos de medio ambiente.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 4A. Environment Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 4U. Códigos de Unidades funcionais.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 4U. Códigos de unidad funcional.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 4U. Functional Unit Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 5I. Códigos de Informação da construção.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 5I. Códigos de información de edificación.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I. Building Information Codes.</t>
   </si>
 </sst>
 </file>
@@ -2248,7 +2269,59 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A0D90F96-026A-4EEB-BDCF-93327D239D7A}"/>
   </cellStyles>
-  <dxfs count="65">
+  <dxfs count="71">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4141,33 +4214,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="64" dataDxfId="62" headerRowBorderDxfId="63" tableBorderDxfId="61" totalsRowBorderDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" tableBorderDxfId="67" totalsRowBorderDxfId="66">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="17" dataDxfId="16"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="15" dataDxfId="14"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="13" dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="11" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="17" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4695,7 +4768,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46228.455256250003</v>
+        <v>46232.780858680555</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>404</v>
@@ -4912,7 +4985,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C2" s="50" t="s">
         <v>419</v>
@@ -4921,7 +4994,7 @@
         <v>421</v>
       </c>
       <c r="E2" s="51" t="s">
-        <v>529</v>
+        <v>496</v>
       </c>
       <c r="F2" s="51" t="s">
         <v>420</v>
@@ -4942,7 +5015,7 @@
         <v>181</v>
       </c>
       <c r="L2" s="52" t="str">
-        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
+        <f t="shared" ref="L2:N17" si="0">CONCATENATE("", C2)</f>
         <v>Gestão</v>
       </c>
       <c r="M2" s="52" t="str">
@@ -4958,10 +5031,10 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="38" t="s">
-        <v>530</v>
+        <v>497</v>
       </c>
       <c r="Q2" s="38" t="s">
-        <v>531</v>
+        <v>498</v>
       </c>
       <c r="R2" s="38" t="s">
         <v>181</v>
@@ -4992,7 +5065,7 @@
         <v>181</v>
       </c>
       <c r="Z2" s="38" t="s">
-        <v>532</v>
+        <v>499</v>
       </c>
       <c r="AA2" s="38" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
@@ -5004,7 +5077,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C3" s="50" t="s">
         <v>419</v>
@@ -5013,7 +5086,7 @@
         <v>421</v>
       </c>
       <c r="E3" s="51" t="s">
-        <v>529</v>
+        <v>496</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>423</v>
@@ -5050,10 +5123,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="38" t="s">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="Q3" s="38" t="s">
-        <v>531</v>
+        <v>498</v>
       </c>
       <c r="R3" s="38" t="s">
         <v>181</v>
@@ -5096,7 +5169,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C4" s="50" t="s">
         <v>419</v>
@@ -5105,7 +5178,7 @@
         <v>421</v>
       </c>
       <c r="E4" s="51" t="s">
-        <v>529</v>
+        <v>496</v>
       </c>
       <c r="F4" s="51" t="s">
         <v>424</v>
@@ -5142,10 +5215,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="38" t="s">
-        <v>534</v>
+        <v>501</v>
       </c>
       <c r="Q4" s="38" t="s">
-        <v>531</v>
+        <v>498</v>
       </c>
       <c r="R4" s="38" t="s">
         <v>181</v>
@@ -5188,7 +5261,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C5" s="50" t="s">
         <v>419</v>
@@ -5197,7 +5270,7 @@
         <v>421</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>529</v>
+        <v>496</v>
       </c>
       <c r="F5" s="51" t="s">
         <v>425</v>
@@ -5234,10 +5307,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="Q5" s="38" t="s">
-        <v>531</v>
+        <v>498</v>
       </c>
       <c r="R5" s="38" t="s">
         <v>181</v>
@@ -5280,7 +5353,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>419</v>
@@ -5289,7 +5362,7 @@
         <v>421</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>529</v>
+        <v>496</v>
       </c>
       <c r="F6" s="51" t="s">
         <v>426</v>
@@ -5326,10 +5399,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="Q6" s="38" t="s">
-        <v>531</v>
+        <v>498</v>
       </c>
       <c r="R6" s="38" t="s">
         <v>181</v>
@@ -5372,19 +5445,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D7" s="33" t="s">
         <v>372</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="G7" s="36" t="s">
         <v>181</v>
@@ -5402,44 +5475,44 @@
         <v>181</v>
       </c>
       <c r="L7" s="52" t="str">
-        <f t="shared" ref="L7:N17" si="5">CONCATENATE("", C7)</f>
+        <f t="shared" si="0"/>
         <v>Normativo</v>
       </c>
       <c r="M7" s="52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>ABNT</v>
       </c>
       <c r="N7" s="52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O7" s="52" t="str">
-        <f t="shared" ref="O7:O28" si="6">F7</f>
+        <f t="shared" ref="O7:O19" si="5">F7</f>
         <v>NBR.0M</v>
       </c>
       <c r="P7" s="52" t="s">
-        <v>427</v>
+        <v>506</v>
       </c>
       <c r="Q7" s="52" t="s">
-        <v>428</v>
+        <v>507</v>
       </c>
       <c r="R7" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S7" s="53" t="str">
-        <f t="shared" ref="S7:U22" si="7">SUBSTITUTE(C7, "_", " ")</f>
+        <f t="shared" ref="S7:U19" si="6">SUBSTITUTE(C7, "_", " ")</f>
         <v>Normativo</v>
       </c>
       <c r="T7" s="53" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U7" s="52" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V7" s="38" t="s">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="W7" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5452,10 +5525,10 @@
         <v>181</v>
       </c>
       <c r="Z7" s="38" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AA7" s="54" t="s">
-        <v>430</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5463,19 +5536,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D8" s="33" t="s">
         <v>372</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>486</v>
+        <v>453</v>
       </c>
       <c r="G8" s="36" t="s">
         <v>181</v>
@@ -5493,44 +5566,44 @@
         <v>181</v>
       </c>
       <c r="L8" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M8" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N8" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O8" s="52" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.0P</v>
+      </c>
+      <c r="P8" s="52" t="s">
+        <v>510</v>
+      </c>
+      <c r="Q8" s="52" t="s">
+        <v>511</v>
+      </c>
+      <c r="R8" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="S8" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M8" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="T8" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N8" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="U8" s="52" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O8" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.0P</v>
-      </c>
-      <c r="P8" s="52" t="s">
-        <v>431</v>
-      </c>
-      <c r="Q8" s="52" t="s">
-        <v>432</v>
-      </c>
-      <c r="R8" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S8" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T8" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U8" s="52" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V8" s="38" t="s">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="W8" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5543,10 +5616,10 @@
         <v>181</v>
       </c>
       <c r="Z8" s="38" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="AA8" s="54" t="s">
-        <v>434</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5554,19 +5627,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D9" s="33" t="s">
         <v>372</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>487</v>
+        <v>454</v>
       </c>
       <c r="G9" s="36" t="s">
         <v>181</v>
@@ -5584,44 +5657,44 @@
         <v>181</v>
       </c>
       <c r="L9" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M9" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N9" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O9" s="52" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.1D</v>
+      </c>
+      <c r="P9" s="52" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q9" s="52" t="s">
+        <v>514</v>
+      </c>
+      <c r="R9" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="S9" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M9" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="T9" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N9" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="U9" s="52" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O9" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.1D</v>
-      </c>
-      <c r="P9" s="52" t="s">
-        <v>435</v>
-      </c>
-      <c r="Q9" s="52" t="s">
-        <v>436</v>
-      </c>
-      <c r="R9" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S9" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T9" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U9" s="52" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V9" s="38" t="s">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="W9" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5634,10 +5707,10 @@
         <v>181</v>
       </c>
       <c r="Z9" s="38" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="AA9" s="54" t="s">
-        <v>438</v>
+        <v>515</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5645,19 +5718,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D10" s="33" t="s">
         <v>372</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>488</v>
+        <v>455</v>
       </c>
       <c r="G10" s="36" t="s">
         <v>181</v>
@@ -5675,44 +5748,44 @@
         <v>181</v>
       </c>
       <c r="L10" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M10" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N10" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O10" s="52" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.1F</v>
+      </c>
+      <c r="P10" s="52" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q10" s="52" t="s">
+        <v>517</v>
+      </c>
+      <c r="R10" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="S10" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M10" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="T10" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N10" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="U10" s="52" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O10" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.1F</v>
-      </c>
-      <c r="P10" s="52" t="s">
-        <v>439</v>
-      </c>
-      <c r="Q10" s="52" t="s">
-        <v>440</v>
-      </c>
-      <c r="R10" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S10" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T10" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U10" s="52" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V10" s="38" t="s">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="W10" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5725,10 +5798,10 @@
         <v>181</v>
       </c>
       <c r="Z10" s="38" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="AA10" s="54" t="s">
-        <v>442</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5736,19 +5809,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D11" s="33" t="s">
         <v>372</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="G11" s="36" t="s">
         <v>181</v>
@@ -5766,44 +5839,44 @@
         <v>181</v>
       </c>
       <c r="L11" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M11" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N11" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O11" s="52" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.1S</v>
+      </c>
+      <c r="P11" s="52" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q11" s="52" t="s">
+        <v>520</v>
+      </c>
+      <c r="R11" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="S11" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M11" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="T11" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N11" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="U11" s="52" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O11" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.1S</v>
-      </c>
-      <c r="P11" s="52" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q11" s="52" t="s">
-        <v>444</v>
-      </c>
-      <c r="R11" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S11" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T11" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U11" s="52" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V11" s="38" t="s">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="W11" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5816,10 +5889,10 @@
         <v>181</v>
       </c>
       <c r="Z11" s="38" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="AA11" s="54" t="s">
-        <v>446</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5827,19 +5900,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D12" s="33" t="s">
         <v>372</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="G12" s="36" t="s">
         <v>181</v>
@@ -5857,44 +5930,44 @@
         <v>181</v>
       </c>
       <c r="L12" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M12" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N12" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O12" s="52" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.2C</v>
+      </c>
+      <c r="P12" s="52" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q12" s="52" t="s">
+        <v>523</v>
+      </c>
+      <c r="R12" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="S12" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M12" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="T12" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N12" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="U12" s="52" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O12" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.2C</v>
-      </c>
-      <c r="P12" s="52" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q12" s="52" t="s">
-        <v>448</v>
-      </c>
-      <c r="R12" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S12" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T12" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U12" s="52" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V12" s="38" t="s">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="W12" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5907,10 +5980,10 @@
         <v>181</v>
       </c>
       <c r="Z12" s="38" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="AA12" s="54" t="s">
-        <v>450</v>
+        <v>524</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5918,19 +5991,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D13" s="33" t="s">
         <v>372</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>491</v>
+        <v>458</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>181</v>
@@ -5948,44 +6021,44 @@
         <v>181</v>
       </c>
       <c r="L13" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M13" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N13" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O13" s="52" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.2N</v>
+      </c>
+      <c r="P13" s="52" t="s">
+        <v>525</v>
+      </c>
+      <c r="Q13" s="52" t="s">
+        <v>526</v>
+      </c>
+      <c r="R13" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="S13" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M13" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="T13" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N13" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="U13" s="52" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O13" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.2N</v>
-      </c>
-      <c r="P13" s="52" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q13" s="52" t="s">
-        <v>448</v>
-      </c>
-      <c r="R13" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S13" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T13" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U13" s="52" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V13" s="38" t="s">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="W13" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6001,7 +6074,7 @@
         <v>342</v>
       </c>
       <c r="AA13" s="54" t="s">
-        <v>450</v>
+        <v>527</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6009,19 +6082,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D14" s="33" t="s">
         <v>372</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>492</v>
+        <v>459</v>
       </c>
       <c r="G14" s="36" t="s">
         <v>181</v>
@@ -6039,44 +6112,44 @@
         <v>181</v>
       </c>
       <c r="L14" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M14" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N14" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O14" s="52" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.2Q</v>
+      </c>
+      <c r="P14" s="52" t="s">
+        <v>528</v>
+      </c>
+      <c r="Q14" s="52" t="s">
+        <v>529</v>
+      </c>
+      <c r="R14" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="S14" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M14" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="T14" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N14" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="U14" s="52" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O14" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.2Q</v>
-      </c>
-      <c r="P14" s="52" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q14" s="52" t="s">
-        <v>448</v>
-      </c>
-      <c r="R14" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S14" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T14" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U14" s="52" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V14" s="38" t="s">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="W14" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6089,10 +6162,10 @@
         <v>181</v>
       </c>
       <c r="Z14" s="38" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="AA14" s="54" t="s">
-        <v>450</v>
+        <v>530</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6100,19 +6173,19 @@
         <v>15</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D15" s="33" t="s">
         <v>372</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>493</v>
+        <v>460</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>181</v>
@@ -6130,44 +6203,44 @@
         <v>181</v>
       </c>
       <c r="L15" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M15" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N15" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O15" s="52" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.3E</v>
+      </c>
+      <c r="P15" s="52" t="s">
+        <v>531</v>
+      </c>
+      <c r="Q15" s="52" t="s">
+        <v>532</v>
+      </c>
+      <c r="R15" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="S15" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M15" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="T15" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N15" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="U15" s="52" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O15" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.3E</v>
-      </c>
-      <c r="P15" s="52" t="s">
-        <v>452</v>
-      </c>
-      <c r="Q15" s="52" t="s">
-        <v>453</v>
-      </c>
-      <c r="R15" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S15" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T15" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U15" s="52" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V15" s="38" t="s">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="W15" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6180,10 +6253,10 @@
         <v>181</v>
       </c>
       <c r="Z15" s="38" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="AA15" s="54" t="s">
-        <v>455</v>
+        <v>533</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6191,19 +6264,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D16" s="33" t="s">
         <v>372</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>494</v>
+        <v>461</v>
       </c>
       <c r="G16" s="36" t="s">
         <v>181</v>
@@ -6221,44 +6294,44 @@
         <v>181</v>
       </c>
       <c r="L16" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M16" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N16" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O16" s="52" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.3R</v>
+      </c>
+      <c r="P16" s="52" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q16" s="52" t="s">
+        <v>535</v>
+      </c>
+      <c r="R16" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="S16" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M16" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="T16" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N16" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="U16" s="52" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O16" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.3R</v>
-      </c>
-      <c r="P16" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="Q16" s="52" t="s">
-        <v>457</v>
-      </c>
-      <c r="R16" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S16" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T16" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U16" s="52" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V16" s="38" t="s">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="W16" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6271,10 +6344,10 @@
         <v>181</v>
       </c>
       <c r="Z16" s="38" t="s">
-        <v>458</v>
+        <v>435</v>
       </c>
       <c r="AA16" s="54" t="s">
-        <v>459</v>
+        <v>536</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6282,19 +6355,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D17" s="33" t="s">
         <v>372</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>495</v>
+        <v>462</v>
       </c>
       <c r="G17" s="36" t="s">
         <v>181</v>
@@ -6312,44 +6385,44 @@
         <v>181</v>
       </c>
       <c r="L17" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M17" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N17" s="52" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O17" s="52" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.4A</v>
+      </c>
+      <c r="P17" s="52" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q17" s="52" t="s">
+        <v>538</v>
+      </c>
+      <c r="R17" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="S17" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M17" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="T17" s="53" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N17" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="U17" s="52" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O17" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.4A</v>
-      </c>
-      <c r="P17" s="52" t="s">
-        <v>460</v>
-      </c>
-      <c r="Q17" s="52" t="s">
-        <v>461</v>
-      </c>
-      <c r="R17" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S17" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T17" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U17" s="52" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V17" s="38" t="s">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="W17" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6362,10 +6435,10 @@
         <v>181</v>
       </c>
       <c r="Z17" s="38" t="s">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="AA17" s="54" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6373,19 +6446,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D18" s="33" t="s">
         <v>372</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="G18" s="36" t="s">
         <v>181</v>
@@ -6403,44 +6476,44 @@
         <v>181</v>
       </c>
       <c r="L18" s="52" t="str">
-        <f t="shared" ref="L18:N28" si="8">CONCATENATE("", C18)</f>
+        <f t="shared" ref="L18:N19" si="7">CONCATENATE("", C18)</f>
         <v>Normativo</v>
       </c>
       <c r="M18" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>ABNT</v>
-      </c>
-      <c r="N18" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="O18" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.4U</v>
-      </c>
-      <c r="P18" s="52" t="s">
-        <v>464</v>
-      </c>
-      <c r="Q18" s="52" t="s">
-        <v>465</v>
-      </c>
-      <c r="R18" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S18" s="53" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T18" s="53" t="str">
         <f t="shared" si="7"/>
         <v>ABNT</v>
       </c>
-      <c r="U18" s="52" t="str">
+      <c r="N18" s="52" t="str">
         <f t="shared" si="7"/>
         <v>NBR.Parte</v>
       </c>
+      <c r="O18" s="52" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.4U</v>
+      </c>
+      <c r="P18" s="52" t="s">
+        <v>540</v>
+      </c>
+      <c r="Q18" s="52" t="s">
+        <v>541</v>
+      </c>
+      <c r="R18" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="S18" s="53" t="str">
+        <f t="shared" si="6"/>
+        <v>Normativo</v>
+      </c>
+      <c r="T18" s="53" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U18" s="52" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
       <c r="V18" s="38" t="s">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="W18" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6453,10 +6526,10 @@
         <v>181</v>
       </c>
       <c r="Z18" s="38" t="s">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="AA18" s="54" t="s">
-        <v>467</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6464,19 +6537,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>372</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>497</v>
+        <v>464</v>
       </c>
       <c r="G19" s="36" t="s">
         <v>181</v>
@@ -6494,44 +6567,44 @@
         <v>181</v>
       </c>
       <c r="L19" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>Normativo</v>
-      </c>
-      <c r="M19" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>ABNT</v>
-      </c>
-      <c r="N19" s="52" t="str">
-        <f t="shared" si="8"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="O19" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.5I</v>
-      </c>
-      <c r="P19" s="52" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q19" s="52" t="s">
-        <v>469</v>
-      </c>
-      <c r="R19" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S19" s="53" t="str">
         <f t="shared" si="7"/>
         <v>Normativo</v>
       </c>
-      <c r="T19" s="53" t="str">
+      <c r="M19" s="52" t="str">
         <f t="shared" si="7"/>
         <v>ABNT</v>
       </c>
-      <c r="U19" s="52" t="str">
+      <c r="N19" s="52" t="str">
         <f t="shared" si="7"/>
         <v>NBR.Parte</v>
       </c>
+      <c r="O19" s="52" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.5I</v>
+      </c>
+      <c r="P19" s="52" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q19" s="52" t="s">
+        <v>544</v>
+      </c>
+      <c r="R19" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="S19" s="53" t="str">
+        <f t="shared" si="6"/>
+        <v>Normativo</v>
+      </c>
+      <c r="T19" s="53" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U19" s="52" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
       <c r="V19" s="38" t="s">
-        <v>422</v>
+        <v>508</v>
       </c>
       <c r="W19" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6544,10 +6617,10 @@
         <v>181</v>
       </c>
       <c r="Z19" s="38" t="s">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="AA19" s="54" t="s">
-        <v>471</v>
+        <v>545</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6555,19 +6628,19 @@
         <v>20</v>
       </c>
       <c r="B20" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>538</v>
+        <v>505</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="G20" s="36" t="s">
         <v>181</v>
@@ -6585,7 +6658,7 @@
         <v>181</v>
       </c>
       <c r="L20" s="52" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="L18:N28" si="8">CONCATENATE("", C20)</f>
         <v>Normativo</v>
       </c>
       <c r="M20" s="52" t="str">
@@ -6597,11 +6670,11 @@
         <v>NBR.N.RH</v>
       </c>
       <c r="O20" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="O7:O28" si="9">F20</f>
         <v>NBR.N.Empreendedor</v>
       </c>
       <c r="P20" s="58" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="Q20" s="52" t="str">
         <f>_xlfn.TRANSLATE(P20,"pt","es")</f>
@@ -6611,15 +6684,15 @@
         <v>181</v>
       </c>
       <c r="S20" s="53" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="S7:U22" si="10">SUBSTITUTE(C20, "_", " ")</f>
         <v>Normativo</v>
       </c>
       <c r="T20" s="53" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U20" s="52" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="V20" s="38" t="s">
@@ -6636,7 +6709,7 @@
         <v>181</v>
       </c>
       <c r="Z20" s="54" t="s">
-        <v>517</v>
+        <v>484</v>
       </c>
       <c r="AA20" s="54" t="str">
         <f>_xlfn.TRANSLATE(P20,"pt","en")</f>
@@ -6648,19 +6721,19 @@
         <v>21</v>
       </c>
       <c r="B21" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>538</v>
+        <v>505</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="G21" s="36" t="s">
         <v>181</v>
@@ -6690,29 +6763,29 @@
         <v>NBR.N.RH</v>
       </c>
       <c r="O21" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.N.Projetista</v>
       </c>
       <c r="P21" s="58" t="s">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="Q21" s="52" t="str">
-        <f t="shared" ref="Q21:Q28" si="9">_xlfn.TRANSLATE(P21,"pt","es")</f>
+        <f t="shared" ref="Q21:Q28" si="11">_xlfn.TRANSLATE(P21,"pt","es")</f>
         <v>Diseñadores</v>
       </c>
       <c r="R21" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S21" s="53" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>Normativo</v>
       </c>
       <c r="T21" s="53" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U21" s="52" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="V21" s="38" t="s">
@@ -6729,10 +6802,10 @@
         <v>181</v>
       </c>
       <c r="Z21" s="54" t="s">
-        <v>518</v>
+        <v>485</v>
       </c>
       <c r="AA21" s="54" t="str">
-        <f t="shared" ref="AA21:AA28" si="10">_xlfn.TRANSLATE(P21,"pt","en")</f>
+        <f t="shared" ref="AA21:AA28" si="12">_xlfn.TRANSLATE(P21,"pt","en")</f>
         <v>Designers</v>
       </c>
     </row>
@@ -6741,19 +6814,19 @@
         <v>22</v>
       </c>
       <c r="B22" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>538</v>
+        <v>505</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="G22" s="36" t="s">
         <v>181</v>
@@ -6783,29 +6856,29 @@
         <v>NBR.N.RH</v>
       </c>
       <c r="O22" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.N.Gestor</v>
       </c>
       <c r="P22" s="58" t="s">
-        <v>510</v>
+        <v>477</v>
       </c>
       <c r="Q22" s="52" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Entrenadores</v>
       </c>
       <c r="R22" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S22" s="53" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>Normativo</v>
       </c>
       <c r="T22" s="53" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U22" s="52" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="V22" s="38" t="s">
@@ -6822,10 +6895,10 @@
         <v>181</v>
       </c>
       <c r="Z22" s="54" t="s">
-        <v>519</v>
+        <v>486</v>
       </c>
       <c r="AA22" s="54" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Managers</v>
       </c>
     </row>
@@ -6834,19 +6907,19 @@
         <v>23</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>538</v>
+        <v>505</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="G23" s="36" t="s">
         <v>181</v>
@@ -6876,29 +6949,29 @@
         <v>NBR.N.RH</v>
       </c>
       <c r="O23" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.N.Construtor</v>
       </c>
       <c r="P23" s="58" t="s">
-        <v>511</v>
+        <v>478</v>
       </c>
       <c r="Q23" s="52" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Constructores y contratistas</v>
       </c>
       <c r="R23" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S23" s="53" t="str">
-        <f t="shared" ref="S23:U28" si="11">SUBSTITUTE(C23, "_", " ")</f>
+        <f t="shared" ref="S23:U28" si="13">SUBSTITUTE(C23, "_", " ")</f>
         <v>Normativo</v>
       </c>
       <c r="T23" s="53" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U23" s="52" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="V23" s="38" t="s">
@@ -6915,10 +6988,10 @@
         <v>181</v>
       </c>
       <c r="Z23" s="54" t="s">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="AA23" s="54" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Builders and Contractors</v>
       </c>
     </row>
@@ -6927,19 +7000,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>538</v>
+        <v>505</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="G24" s="36" t="s">
         <v>181</v>
@@ -6969,29 +7042,29 @@
         <v>NBR.N.RH</v>
       </c>
       <c r="O24" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.N.Fiscal</v>
       </c>
       <c r="P24" s="58" t="s">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="Q24" s="52" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Inspectores de construcción</v>
       </c>
       <c r="R24" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S24" s="53" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T24" s="53" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U24" s="52" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="V24" s="38" t="s">
@@ -7008,10 +7081,10 @@
         <v>181</v>
       </c>
       <c r="Z24" s="54" t="s">
-        <v>521</v>
+        <v>488</v>
       </c>
       <c r="AA24" s="54" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Construction inspectors</v>
       </c>
     </row>
@@ -7020,19 +7093,19 @@
         <v>25</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>538</v>
+        <v>505</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="G25" s="36" t="s">
         <v>181</v>
@@ -7062,29 +7135,29 @@
         <v>NBR.N.RH</v>
       </c>
       <c r="O25" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.N.Apoiador</v>
       </c>
       <c r="P25" s="58" t="s">
-        <v>513</v>
+        <v>480</v>
       </c>
       <c r="Q25" s="52" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Aficionados</v>
       </c>
       <c r="R25" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S25" s="53" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T25" s="53" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U25" s="52" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="V25" s="38" t="s">
@@ -7101,10 +7174,10 @@
         <v>181</v>
       </c>
       <c r="Z25" s="54" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="AA25" s="54" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Supporters</v>
       </c>
     </row>
@@ -7113,19 +7186,19 @@
         <v>26</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>538</v>
+        <v>505</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="G26" s="36" t="s">
         <v>181</v>
@@ -7155,29 +7228,29 @@
         <v>NBR.N.RH</v>
       </c>
       <c r="O26" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.N.Marketero</v>
       </c>
       <c r="P26" s="58" t="s">
-        <v>514</v>
+        <v>481</v>
       </c>
       <c r="Q26" s="52" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Profesionales del marketing</v>
       </c>
       <c r="R26" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S26" s="53" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T26" s="53" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U26" s="52" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="V26" s="38" t="s">
@@ -7194,10 +7267,10 @@
         <v>181</v>
       </c>
       <c r="Z26" s="54" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="AA26" s="54" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Marketers</v>
       </c>
     </row>
@@ -7206,19 +7279,19 @@
         <v>27</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>538</v>
+        <v>505</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="G27" s="36" t="s">
         <v>181</v>
@@ -7248,29 +7321,29 @@
         <v>NBR.N.RH</v>
       </c>
       <c r="O27" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.N.Tercerizado</v>
       </c>
       <c r="P27" s="58" t="s">
-        <v>515</v>
+        <v>482</v>
       </c>
       <c r="Q27" s="52" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Subcontratado</v>
       </c>
       <c r="R27" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S27" s="53" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T27" s="53" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U27" s="52" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="V27" s="38" t="s">
@@ -7287,10 +7360,10 @@
         <v>181</v>
       </c>
       <c r="Z27" s="54" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="AA27" s="54" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Outsourced</v>
       </c>
     </row>
@@ -7299,19 +7372,19 @@
         <v>28</v>
       </c>
       <c r="B28" s="50" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>538</v>
+        <v>505</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="G28" s="36" t="s">
         <v>181</v>
@@ -7341,29 +7414,29 @@
         <v>NBR.N.RH</v>
       </c>
       <c r="O28" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.N.Empresa</v>
       </c>
       <c r="P28" s="58" t="s">
-        <v>516</v>
+        <v>483</v>
       </c>
       <c r="Q28" s="52" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Empresas y Grupos Participantes</v>
       </c>
       <c r="R28" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S28" s="53" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T28" s="53" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U28" s="52" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.N.RH</v>
       </c>
       <c r="V28" s="38" t="s">
@@ -7380,27 +7453,40 @@
         <v>181</v>
       </c>
       <c r="Z28" s="54" t="s">
-        <v>525</v>
+        <v>492</v>
       </c>
       <c r="AA28" s="54" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Participating Companies and Groups</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B28">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B6 A20:B28">
+    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA28">
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
+  <conditionalFormatting sqref="AA1:AA6 AA20:AA28">
+    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:B19">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F19">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA19">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7553,7 +7639,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7598,7 +7684,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7714,7 +7800,7 @@
         <v>345</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>181</v>
@@ -7738,13 +7824,13 @@
         <v>340</v>
       </c>
       <c r="K2" s="46" t="s">
-        <v>481</v>
+        <v>448</v>
       </c>
       <c r="L2" s="45" t="s">
         <v>412</v>
       </c>
       <c r="M2" s="46" t="s">
-        <v>482</v>
+        <v>449</v>
       </c>
       <c r="N2" s="47" t="s">
         <v>1</v>
@@ -7791,10 +7877,10 @@
         <v>344</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E3" s="57" t="s">
         <v>345</v>
@@ -7815,13 +7901,13 @@
         <v>340</v>
       </c>
       <c r="K3" s="46" t="s">
-        <v>481</v>
+        <v>448</v>
       </c>
       <c r="L3" s="45" t="s">
         <v>412</v>
       </c>
       <c r="M3" s="46" t="s">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="N3" s="47" t="s">
         <v>1</v>
@@ -7868,10 +7954,10 @@
         <v>342</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>491</v>
+        <v>458</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E4" s="57" t="s">
         <v>344</v>
@@ -7892,13 +7978,13 @@
         <v>340</v>
       </c>
       <c r="K4" s="46" t="s">
-        <v>481</v>
+        <v>448</v>
       </c>
       <c r="L4" s="45" t="s">
         <v>412</v>
       </c>
       <c r="M4" s="46" t="s">
-        <v>527</v>
+        <v>494</v>
       </c>
       <c r="N4" s="47" t="s">
         <v>1</v>
@@ -7945,10 +8031,10 @@
         <v>188</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E5" s="57" t="s">
         <v>344</v>
@@ -7975,7 +8061,7 @@
         <v>412</v>
       </c>
       <c r="M5" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N5" s="47" t="s">
         <v>1</v>
@@ -8022,10 +8108,10 @@
         <v>189</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E6" s="57" t="s">
         <v>344</v>
@@ -8052,7 +8138,7 @@
         <v>412</v>
       </c>
       <c r="M6" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N6" s="47" t="s">
         <v>1</v>
@@ -8099,10 +8185,10 @@
         <v>190</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E7" s="57" t="s">
         <v>344</v>
@@ -8129,7 +8215,7 @@
         <v>412</v>
       </c>
       <c r="M7" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N7" s="47" t="s">
         <v>1</v>
@@ -8176,10 +8262,10 @@
         <v>191</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E8" s="57" t="s">
         <v>344</v>
@@ -8206,7 +8292,7 @@
         <v>412</v>
       </c>
       <c r="M8" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N8" s="47" t="s">
         <v>1</v>
@@ -8253,10 +8339,10 @@
         <v>192</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E9" s="57" t="s">
         <v>344</v>
@@ -8283,7 +8369,7 @@
         <v>412</v>
       </c>
       <c r="M9" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N9" s="47" t="s">
         <v>1</v>
@@ -8330,10 +8416,10 @@
         <v>193</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E10" s="57" t="s">
         <v>344</v>
@@ -8360,7 +8446,7 @@
         <v>412</v>
       </c>
       <c r="M10" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N10" s="47" t="s">
         <v>1</v>
@@ -8407,10 +8493,10 @@
         <v>194</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E11" s="57" t="s">
         <v>344</v>
@@ -8437,7 +8523,7 @@
         <v>412</v>
       </c>
       <c r="M11" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N11" s="47" t="s">
         <v>1</v>
@@ -8484,10 +8570,10 @@
         <v>195</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E12" s="57" t="s">
         <v>344</v>
@@ -8514,7 +8600,7 @@
         <v>412</v>
       </c>
       <c r="M12" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N12" s="47" t="s">
         <v>1</v>
@@ -8561,10 +8647,10 @@
         <v>196</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E13" s="57" t="s">
         <v>344</v>
@@ -8591,7 +8677,7 @@
         <v>412</v>
       </c>
       <c r="M13" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N13" s="47" t="s">
         <v>1</v>
@@ -8638,10 +8724,10 @@
         <v>197</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E14" s="57" t="s">
         <v>344</v>
@@ -8668,7 +8754,7 @@
         <v>412</v>
       </c>
       <c r="M14" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N14" s="47" t="s">
         <v>1</v>
@@ -8715,10 +8801,10 @@
         <v>198</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D15" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E15" s="57" t="s">
         <v>344</v>
@@ -8745,7 +8831,7 @@
         <v>412</v>
       </c>
       <c r="M15" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N15" s="47" t="s">
         <v>1</v>
@@ -8792,10 +8878,10 @@
         <v>199</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D16" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E16" s="57" t="s">
         <v>344</v>
@@ -8822,7 +8908,7 @@
         <v>412</v>
       </c>
       <c r="M16" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N16" s="47" t="s">
         <v>1</v>
@@ -8869,10 +8955,10 @@
         <v>200</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D17" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E17" s="57" t="s">
         <v>344</v>
@@ -8899,7 +8985,7 @@
         <v>412</v>
       </c>
       <c r="M17" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N17" s="47" t="s">
         <v>1</v>
@@ -8946,10 +9032,10 @@
         <v>201</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E18" s="57" t="s">
         <v>344</v>
@@ -8976,7 +9062,7 @@
         <v>412</v>
       </c>
       <c r="M18" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N18" s="47" t="s">
         <v>1</v>
@@ -9023,10 +9109,10 @@
         <v>202</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E19" s="57" t="s">
         <v>344</v>
@@ -9053,7 +9139,7 @@
         <v>412</v>
       </c>
       <c r="M19" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N19" s="47" t="s">
         <v>1</v>
@@ -9100,10 +9186,10 @@
         <v>203</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E20" s="57" t="s">
         <v>344</v>
@@ -9130,7 +9216,7 @@
         <v>412</v>
       </c>
       <c r="M20" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N20" s="47" t="s">
         <v>1</v>
@@ -9177,10 +9263,10 @@
         <v>204</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D21" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E21" s="57" t="s">
         <v>344</v>
@@ -9207,7 +9293,7 @@
         <v>412</v>
       </c>
       <c r="M21" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N21" s="47" t="s">
         <v>1</v>
@@ -9254,10 +9340,10 @@
         <v>205</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E22" s="57" t="s">
         <v>344</v>
@@ -9284,7 +9370,7 @@
         <v>412</v>
       </c>
       <c r="M22" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N22" s="47" t="s">
         <v>1</v>
@@ -9331,10 +9417,10 @@
         <v>206</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D23" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E23" s="57" t="s">
         <v>344</v>
@@ -9361,7 +9447,7 @@
         <v>412</v>
       </c>
       <c r="M23" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N23" s="47" t="s">
         <v>1</v>
@@ -9408,10 +9494,10 @@
         <v>207</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E24" s="57" t="s">
         <v>344</v>
@@ -9438,7 +9524,7 @@
         <v>412</v>
       </c>
       <c r="M24" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N24" s="47" t="s">
         <v>1</v>
@@ -9485,10 +9571,10 @@
         <v>208</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E25" s="57" t="s">
         <v>344</v>
@@ -9515,7 +9601,7 @@
         <v>412</v>
       </c>
       <c r="M25" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N25" s="47" t="s">
         <v>1</v>
@@ -9562,10 +9648,10 @@
         <v>209</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D26" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E26" s="57" t="s">
         <v>344</v>
@@ -9592,7 +9678,7 @@
         <v>412</v>
       </c>
       <c r="M26" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N26" s="47" t="s">
         <v>1</v>
@@ -9639,10 +9725,10 @@
         <v>210</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D27" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E27" s="57" t="s">
         <v>344</v>
@@ -9669,7 +9755,7 @@
         <v>412</v>
       </c>
       <c r="M27" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N27" s="47" t="s">
         <v>1</v>
@@ -9716,10 +9802,10 @@
         <v>211</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D28" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E28" s="57" t="s">
         <v>344</v>
@@ -9746,7 +9832,7 @@
         <v>412</v>
       </c>
       <c r="M28" s="46" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="N28" s="47" t="s">
         <v>1</v>
@@ -9793,10 +9879,10 @@
         <v>212</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="D29" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E29" s="57" t="s">
         <v>344</v>
@@ -9823,7 +9909,7 @@
         <v>412</v>
       </c>
       <c r="M29" s="46" t="s">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="N29" s="47" t="s">
         <v>1</v>
@@ -9870,10 +9956,10 @@
         <v>213</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E30" s="57" t="s">
         <v>344</v>
@@ -9900,7 +9986,7 @@
         <v>412</v>
       </c>
       <c r="M30" s="46" t="s">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="N30" s="47" t="s">
         <v>1</v>
@@ -9947,10 +10033,10 @@
         <v>214</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E31" s="57" t="s">
         <v>344</v>
@@ -9977,7 +10063,7 @@
         <v>412</v>
       </c>
       <c r="M31" s="46" t="s">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="N31" s="47" t="s">
         <v>1</v>
@@ -10024,10 +10110,10 @@
         <v>215</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="D32" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E32" s="57" t="s">
         <v>344</v>
@@ -10054,7 +10140,7 @@
         <v>412</v>
       </c>
       <c r="M32" s="46" t="s">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="N32" s="47" t="s">
         <v>1</v>
@@ -10101,10 +10187,10 @@
         <v>216</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="D33" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E33" s="57" t="s">
         <v>344</v>
@@ -10131,7 +10217,7 @@
         <v>412</v>
       </c>
       <c r="M33" s="46" t="s">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="N33" s="47" t="s">
         <v>1</v>
@@ -10178,10 +10264,10 @@
         <v>217</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="D34" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E34" s="57" t="s">
         <v>344</v>
@@ -10208,7 +10294,7 @@
         <v>412</v>
       </c>
       <c r="M34" s="46" t="s">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="N34" s="47" t="s">
         <v>1</v>
@@ -10255,10 +10341,10 @@
         <v>218</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="D35" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E35" s="57" t="s">
         <v>344</v>
@@ -10285,7 +10371,7 @@
         <v>412</v>
       </c>
       <c r="M35" s="46" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N35" s="47" t="s">
         <v>1</v>
@@ -10332,10 +10418,10 @@
         <v>417</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="D36" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E36" s="57" t="s">
         <v>344</v>
@@ -10362,7 +10448,7 @@
         <v>412</v>
       </c>
       <c r="M36" s="46" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N36" s="47" t="s">
         <v>1</v>
@@ -10409,10 +10495,10 @@
         <v>219</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="D37" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E37" s="57" t="s">
         <v>344</v>
@@ -10439,7 +10525,7 @@
         <v>412</v>
       </c>
       <c r="M37" s="46" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N37" s="47" t="s">
         <v>1</v>
@@ -10486,10 +10572,10 @@
         <v>220</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="D38" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E38" s="57" t="s">
         <v>344</v>
@@ -10516,7 +10602,7 @@
         <v>412</v>
       </c>
       <c r="M38" s="46" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N38" s="47" t="s">
         <v>1</v>
@@ -10563,10 +10649,10 @@
         <v>221</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="D39" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E39" s="57" t="s">
         <v>344</v>
@@ -10593,7 +10679,7 @@
         <v>412</v>
       </c>
       <c r="M39" s="46" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N39" s="47" t="s">
         <v>1</v>
@@ -10640,10 +10726,10 @@
         <v>222</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="D40" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E40" s="57" t="s">
         <v>344</v>
@@ -10670,7 +10756,7 @@
         <v>412</v>
       </c>
       <c r="M40" s="46" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N40" s="47" t="s">
         <v>1</v>
@@ -10717,10 +10803,10 @@
         <v>223</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="D41" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E41" s="57" t="s">
         <v>344</v>
@@ -10747,7 +10833,7 @@
         <v>412</v>
       </c>
       <c r="M41" s="46" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N41" s="47" t="s">
         <v>1</v>
@@ -10794,10 +10880,10 @@
         <v>224</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="D42" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E42" s="57" t="s">
         <v>344</v>
@@ -10824,7 +10910,7 @@
         <v>412</v>
       </c>
       <c r="M42" s="46" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N42" s="47" t="s">
         <v>1</v>
@@ -10871,10 +10957,10 @@
         <v>225</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="D43" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E43" s="57" t="s">
         <v>344</v>
@@ -10901,7 +10987,7 @@
         <v>412</v>
       </c>
       <c r="M43" s="46" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N43" s="47" t="s">
         <v>1</v>
@@ -10948,10 +11034,10 @@
         <v>226</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="D44" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E44" s="57" t="s">
         <v>344</v>
@@ -10978,7 +11064,7 @@
         <v>412</v>
       </c>
       <c r="M44" s="46" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N44" s="47" t="s">
         <v>1</v>
@@ -11025,10 +11111,10 @@
         <v>227</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="D45" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E45" s="57" t="s">
         <v>344</v>
@@ -11055,7 +11141,7 @@
         <v>412</v>
       </c>
       <c r="M45" s="46" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N45" s="47" t="s">
         <v>1</v>
@@ -11102,10 +11188,10 @@
         <v>228</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D46" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E46" s="57" t="s">
         <v>344</v>
@@ -11132,7 +11218,7 @@
         <v>412</v>
       </c>
       <c r="M46" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N46" s="47" t="s">
         <v>1</v>
@@ -11179,10 +11265,10 @@
         <v>229</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D47" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E47" s="57" t="s">
         <v>344</v>
@@ -11209,7 +11295,7 @@
         <v>412</v>
       </c>
       <c r="M47" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N47" s="47" t="s">
         <v>1</v>
@@ -11256,10 +11342,10 @@
         <v>230</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D48" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E48" s="57" t="s">
         <v>344</v>
@@ -11286,7 +11372,7 @@
         <v>412</v>
       </c>
       <c r="M48" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N48" s="47" t="s">
         <v>1</v>
@@ -11333,10 +11419,10 @@
         <v>231</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D49" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E49" s="57" t="s">
         <v>344</v>
@@ -11363,7 +11449,7 @@
         <v>412</v>
       </c>
       <c r="M49" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N49" s="47" t="s">
         <v>1</v>
@@ -11410,10 +11496,10 @@
         <v>232</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D50" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E50" s="57" t="s">
         <v>344</v>
@@ -11440,7 +11526,7 @@
         <v>412</v>
       </c>
       <c r="M50" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N50" s="47" t="s">
         <v>1</v>
@@ -11487,10 +11573,10 @@
         <v>233</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D51" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E51" s="57" t="s">
         <v>344</v>
@@ -11517,7 +11603,7 @@
         <v>412</v>
       </c>
       <c r="M51" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N51" s="47" t="s">
         <v>1</v>
@@ -11564,10 +11650,10 @@
         <v>234</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D52" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E52" s="57" t="s">
         <v>344</v>
@@ -11594,7 +11680,7 @@
         <v>412</v>
       </c>
       <c r="M52" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N52" s="47" t="s">
         <v>1</v>
@@ -11641,10 +11727,10 @@
         <v>235</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D53" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E53" s="57" t="s">
         <v>344</v>
@@ -11671,7 +11757,7 @@
         <v>412</v>
       </c>
       <c r="M53" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N53" s="47" t="s">
         <v>1</v>
@@ -11718,10 +11804,10 @@
         <v>236</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D54" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E54" s="57" t="s">
         <v>344</v>
@@ -11748,7 +11834,7 @@
         <v>412</v>
       </c>
       <c r="M54" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N54" s="47" t="s">
         <v>1</v>
@@ -11795,10 +11881,10 @@
         <v>237</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D55" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E55" s="57" t="s">
         <v>344</v>
@@ -11825,7 +11911,7 @@
         <v>412</v>
       </c>
       <c r="M55" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N55" s="47" t="s">
         <v>1</v>
@@ -11872,10 +11958,10 @@
         <v>238</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D56" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E56" s="57" t="s">
         <v>344</v>
@@ -11902,7 +11988,7 @@
         <v>412</v>
       </c>
       <c r="M56" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N56" s="47" t="s">
         <v>1</v>
@@ -11949,10 +12035,10 @@
         <v>239</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D57" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E57" s="57" t="s">
         <v>344</v>
@@ -11979,7 +12065,7 @@
         <v>412</v>
       </c>
       <c r="M57" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N57" s="47" t="s">
         <v>1</v>
@@ -12026,10 +12112,10 @@
         <v>240</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D58" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E58" s="57" t="s">
         <v>344</v>
@@ -12056,7 +12142,7 @@
         <v>412</v>
       </c>
       <c r="M58" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N58" s="47" t="s">
         <v>1</v>
@@ -12103,10 +12189,10 @@
         <v>241</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D59" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E59" s="57" t="s">
         <v>344</v>
@@ -12133,7 +12219,7 @@
         <v>412</v>
       </c>
       <c r="M59" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N59" s="47" t="s">
         <v>1</v>
@@ -12180,10 +12266,10 @@
         <v>242</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D60" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E60" s="57" t="s">
         <v>344</v>
@@ -12210,7 +12296,7 @@
         <v>412</v>
       </c>
       <c r="M60" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N60" s="47" t="s">
         <v>1</v>
@@ -12257,10 +12343,10 @@
         <v>243</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D61" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E61" s="57" t="s">
         <v>344</v>
@@ -12287,7 +12373,7 @@
         <v>412</v>
       </c>
       <c r="M61" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N61" s="47" t="s">
         <v>1</v>
@@ -12334,10 +12420,10 @@
         <v>244</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D62" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E62" s="57" t="s">
         <v>344</v>
@@ -12364,7 +12450,7 @@
         <v>412</v>
       </c>
       <c r="M62" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N62" s="47" t="s">
         <v>1</v>
@@ -12411,10 +12497,10 @@
         <v>245</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D63" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E63" s="57" t="s">
         <v>344</v>
@@ -12441,7 +12527,7 @@
         <v>412</v>
       </c>
       <c r="M63" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N63" s="47" t="s">
         <v>1</v>
@@ -12488,10 +12574,10 @@
         <v>246</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D64" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E64" s="57" t="s">
         <v>344</v>
@@ -12518,7 +12604,7 @@
         <v>412</v>
       </c>
       <c r="M64" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N64" s="47" t="s">
         <v>1</v>
@@ -12565,10 +12651,10 @@
         <v>247</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D65" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E65" s="57" t="s">
         <v>344</v>
@@ -12595,7 +12681,7 @@
         <v>412</v>
       </c>
       <c r="M65" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N65" s="47" t="s">
         <v>1</v>
@@ -12642,10 +12728,10 @@
         <v>248</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D66" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E66" s="57" t="s">
         <v>344</v>
@@ -12672,7 +12758,7 @@
         <v>412</v>
       </c>
       <c r="M66" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N66" s="47" t="s">
         <v>1</v>
@@ -12719,10 +12805,10 @@
         <v>249</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D67" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E67" s="57" t="s">
         <v>344</v>
@@ -12749,7 +12835,7 @@
         <v>412</v>
       </c>
       <c r="M67" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N67" s="47" t="s">
         <v>1</v>
@@ -12796,10 +12882,10 @@
         <v>250</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D68" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E68" s="57" t="s">
         <v>344</v>
@@ -12826,7 +12912,7 @@
         <v>412</v>
       </c>
       <c r="M68" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N68" s="47" t="s">
         <v>1</v>
@@ -12873,10 +12959,10 @@
         <v>251</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D69" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E69" s="57" t="s">
         <v>344</v>
@@ -12903,7 +12989,7 @@
         <v>412</v>
       </c>
       <c r="M69" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N69" s="47" t="s">
         <v>1</v>
@@ -12950,10 +13036,10 @@
         <v>252</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="D70" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E70" s="57" t="s">
         <v>344</v>
@@ -12980,7 +13066,7 @@
         <v>412</v>
       </c>
       <c r="M70" s="46" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="N70" s="47" t="s">
         <v>1</v>
@@ -13027,10 +13113,10 @@
         <v>253</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="D71" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E71" s="57" t="s">
         <v>344</v>
@@ -13057,7 +13143,7 @@
         <v>412</v>
       </c>
       <c r="M71" s="46" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="N71" s="47" t="s">
         <v>1</v>
@@ -13104,10 +13190,10 @@
         <v>254</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="D72" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E72" s="57" t="s">
         <v>344</v>
@@ -13134,7 +13220,7 @@
         <v>412</v>
       </c>
       <c r="M72" s="46" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="N72" s="47" t="s">
         <v>1</v>
@@ -13181,10 +13267,10 @@
         <v>255</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="D73" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E73" s="57" t="s">
         <v>344</v>
@@ -13211,7 +13297,7 @@
         <v>412</v>
       </c>
       <c r="M73" s="46" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="N73" s="47" t="s">
         <v>1</v>
@@ -13258,10 +13344,10 @@
         <v>256</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="D74" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E74" s="57" t="s">
         <v>344</v>
@@ -13288,7 +13374,7 @@
         <v>412</v>
       </c>
       <c r="M74" s="46" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="N74" s="47" t="s">
         <v>1</v>
@@ -13335,10 +13421,10 @@
         <v>257</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="D75" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E75" s="57" t="s">
         <v>344</v>
@@ -13365,7 +13451,7 @@
         <v>412</v>
       </c>
       <c r="M75" s="46" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="N75" s="47" t="s">
         <v>1</v>
@@ -13412,10 +13498,10 @@
         <v>258</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="D76" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E76" s="57" t="s">
         <v>344</v>
@@ -13442,7 +13528,7 @@
         <v>412</v>
       </c>
       <c r="M76" s="46" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="N76" s="47" t="s">
         <v>1</v>
@@ -13489,10 +13575,10 @@
         <v>259</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="D77" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E77" s="57" t="s">
         <v>344</v>
@@ -13519,7 +13605,7 @@
         <v>412</v>
       </c>
       <c r="M77" s="46" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="N77" s="47" t="s">
         <v>1</v>
@@ -13566,10 +13652,10 @@
         <v>260</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="D78" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E78" s="57" t="s">
         <v>344</v>
@@ -13596,7 +13682,7 @@
         <v>412</v>
       </c>
       <c r="M78" s="46" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="N78" s="47" t="s">
         <v>1</v>
@@ -13643,10 +13729,10 @@
         <v>261</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="D79" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E79" s="57" t="s">
         <v>344</v>
@@ -13673,7 +13759,7 @@
         <v>412</v>
       </c>
       <c r="M79" s="46" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="N79" s="47" t="s">
         <v>1</v>
@@ -13720,10 +13806,10 @@
         <v>262</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="D80" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E80" s="57" t="s">
         <v>344</v>
@@ -13750,7 +13836,7 @@
         <v>412</v>
       </c>
       <c r="M80" s="46" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="N80" s="47" t="s">
         <v>1</v>
@@ -13797,10 +13883,10 @@
         <v>263</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D81" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E81" s="57" t="s">
         <v>344</v>
@@ -13827,7 +13913,7 @@
         <v>412</v>
       </c>
       <c r="M81" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N81" s="47" t="s">
         <v>1</v>
@@ -13874,10 +13960,10 @@
         <v>264</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D82" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E82" s="57" t="s">
         <v>344</v>
@@ -13904,7 +13990,7 @@
         <v>412</v>
       </c>
       <c r="M82" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N82" s="47" t="s">
         <v>1</v>
@@ -13951,10 +14037,10 @@
         <v>265</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D83" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E83" s="57" t="s">
         <v>344</v>
@@ -13981,7 +14067,7 @@
         <v>412</v>
       </c>
       <c r="M83" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N83" s="47" t="s">
         <v>1</v>
@@ -14028,10 +14114,10 @@
         <v>266</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D84" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E84" s="57" t="s">
         <v>344</v>
@@ -14058,7 +14144,7 @@
         <v>412</v>
       </c>
       <c r="M84" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N84" s="47" t="s">
         <v>1</v>
@@ -14105,10 +14191,10 @@
         <v>267</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D85" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E85" s="57" t="s">
         <v>344</v>
@@ -14135,7 +14221,7 @@
         <v>412</v>
       </c>
       <c r="M85" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N85" s="47" t="s">
         <v>1</v>
@@ -14182,10 +14268,10 @@
         <v>268</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D86" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E86" s="57" t="s">
         <v>344</v>
@@ -14212,7 +14298,7 @@
         <v>412</v>
       </c>
       <c r="M86" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N86" s="47" t="s">
         <v>1</v>
@@ -14259,10 +14345,10 @@
         <v>269</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D87" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E87" s="57" t="s">
         <v>344</v>
@@ -14289,7 +14375,7 @@
         <v>412</v>
       </c>
       <c r="M87" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N87" s="47" t="s">
         <v>1</v>
@@ -14336,10 +14422,10 @@
         <v>270</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D88" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E88" s="57" t="s">
         <v>344</v>
@@ -14366,7 +14452,7 @@
         <v>412</v>
       </c>
       <c r="M88" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N88" s="47" t="s">
         <v>1</v>
@@ -14413,10 +14499,10 @@
         <v>271</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D89" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E89" s="57" t="s">
         <v>344</v>
@@ -14443,7 +14529,7 @@
         <v>412</v>
       </c>
       <c r="M89" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N89" s="47" t="s">
         <v>1</v>
@@ -14490,10 +14576,10 @@
         <v>272</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D90" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E90" s="57" t="s">
         <v>344</v>
@@ -14520,7 +14606,7 @@
         <v>412</v>
       </c>
       <c r="M90" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N90" s="47" t="s">
         <v>1</v>
@@ -14567,10 +14653,10 @@
         <v>273</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D91" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E91" s="57" t="s">
         <v>344</v>
@@ -14597,7 +14683,7 @@
         <v>412</v>
       </c>
       <c r="M91" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N91" s="47" t="s">
         <v>1</v>
@@ -14644,10 +14730,10 @@
         <v>274</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D92" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E92" s="57" t="s">
         <v>344</v>
@@ -14674,7 +14760,7 @@
         <v>412</v>
       </c>
       <c r="M92" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N92" s="47" t="s">
         <v>1</v>
@@ -14721,10 +14807,10 @@
         <v>275</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D93" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E93" s="57" t="s">
         <v>344</v>
@@ -14751,7 +14837,7 @@
         <v>412</v>
       </c>
       <c r="M93" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N93" s="47" t="s">
         <v>1</v>
@@ -14798,10 +14884,10 @@
         <v>276</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D94" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E94" s="57" t="s">
         <v>344</v>
@@ -14828,7 +14914,7 @@
         <v>412</v>
       </c>
       <c r="M94" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N94" s="47" t="s">
         <v>1</v>
@@ -14875,10 +14961,10 @@
         <v>277</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="D95" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E95" s="57" t="s">
         <v>344</v>
@@ -14905,7 +14991,7 @@
         <v>412</v>
       </c>
       <c r="M95" s="46" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="N95" s="47" t="s">
         <v>1</v>
@@ -14952,10 +15038,10 @@
         <v>278</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="D96" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E96" s="57" t="s">
         <v>344</v>
@@ -14982,7 +15068,7 @@
         <v>412</v>
       </c>
       <c r="M96" s="46" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="N96" s="47" t="s">
         <v>1</v>
@@ -15029,10 +15115,10 @@
         <v>279</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="D97" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E97" s="57" t="s">
         <v>344</v>
@@ -15059,7 +15145,7 @@
         <v>412</v>
       </c>
       <c r="M97" s="46" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="N97" s="47" t="s">
         <v>1</v>
@@ -15106,10 +15192,10 @@
         <v>280</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="D98" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E98" s="57" t="s">
         <v>344</v>
@@ -15136,7 +15222,7 @@
         <v>412</v>
       </c>
       <c r="M98" s="46" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="N98" s="47" t="s">
         <v>1</v>
@@ -15183,10 +15269,10 @@
         <v>281</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="D99" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E99" s="57" t="s">
         <v>344</v>
@@ -15213,7 +15299,7 @@
         <v>412</v>
       </c>
       <c r="M99" s="46" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="N99" s="47" t="s">
         <v>1</v>
@@ -15260,10 +15346,10 @@
         <v>282</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="D100" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E100" s="57" t="s">
         <v>344</v>
@@ -15290,7 +15376,7 @@
         <v>412</v>
       </c>
       <c r="M100" s="46" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="N100" s="47" t="s">
         <v>1</v>
@@ -15337,10 +15423,10 @@
         <v>283</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="D101" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E101" s="57" t="s">
         <v>344</v>
@@ -15367,7 +15453,7 @@
         <v>412</v>
       </c>
       <c r="M101" s="46" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="N101" s="47" t="s">
         <v>1</v>
@@ -15414,10 +15500,10 @@
         <v>284</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="D102" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E102" s="57" t="s">
         <v>344</v>
@@ -15444,7 +15530,7 @@
         <v>412</v>
       </c>
       <c r="M102" s="46" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="N102" s="47" t="s">
         <v>1</v>
@@ -15491,10 +15577,10 @@
         <v>285</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="D103" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E103" s="57" t="s">
         <v>344</v>
@@ -15521,7 +15607,7 @@
         <v>412</v>
       </c>
       <c r="M103" s="46" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="N103" s="47" t="s">
         <v>1</v>
@@ -15568,10 +15654,10 @@
         <v>286</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="D104" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E104" s="57" t="s">
         <v>344</v>
@@ -15598,7 +15684,7 @@
         <v>412</v>
       </c>
       <c r="M104" s="46" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="N104" s="47" t="s">
         <v>1</v>
@@ -15645,10 +15731,10 @@
         <v>287</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="D105" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E105" s="57" t="s">
         <v>344</v>
@@ -15675,7 +15761,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="46" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="N105" s="47" t="s">
         <v>1</v>
@@ -15722,10 +15808,10 @@
         <v>288</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="D106" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E106" s="57" t="s">
         <v>344</v>
@@ -15752,7 +15838,7 @@
         <v>412</v>
       </c>
       <c r="M106" s="46" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="N106" s="47" t="s">
         <v>1</v>
@@ -15799,10 +15885,10 @@
         <v>289</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="D107" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E107" s="57" t="s">
         <v>344</v>
@@ -15829,7 +15915,7 @@
         <v>412</v>
       </c>
       <c r="M107" s="46" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="N107" s="47" t="s">
         <v>1</v>
@@ -15876,10 +15962,10 @@
         <v>290</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D108" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E108" s="57" t="s">
         <v>344</v>
@@ -15906,7 +15992,7 @@
         <v>412</v>
       </c>
       <c r="M108" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N108" s="47" t="s">
         <v>1</v>
@@ -15953,10 +16039,10 @@
         <v>291</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D109" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E109" s="57" t="s">
         <v>344</v>
@@ -15983,7 +16069,7 @@
         <v>412</v>
       </c>
       <c r="M109" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N109" s="47" t="s">
         <v>1</v>
@@ -16030,10 +16116,10 @@
         <v>292</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D110" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E110" s="57" t="s">
         <v>344</v>
@@ -16060,7 +16146,7 @@
         <v>412</v>
       </c>
       <c r="M110" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N110" s="47" t="s">
         <v>1</v>
@@ -16107,10 +16193,10 @@
         <v>293</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D111" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E111" s="57" t="s">
         <v>344</v>
@@ -16137,7 +16223,7 @@
         <v>412</v>
       </c>
       <c r="M111" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N111" s="47" t="s">
         <v>1</v>
@@ -16184,10 +16270,10 @@
         <v>294</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D112" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E112" s="57" t="s">
         <v>344</v>
@@ -16214,7 +16300,7 @@
         <v>412</v>
       </c>
       <c r="M112" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N112" s="47" t="s">
         <v>1</v>
@@ -16261,10 +16347,10 @@
         <v>295</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D113" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E113" s="57" t="s">
         <v>344</v>
@@ -16291,7 +16377,7 @@
         <v>412</v>
       </c>
       <c r="M113" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N113" s="47" t="s">
         <v>1</v>
@@ -16338,10 +16424,10 @@
         <v>296</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D114" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E114" s="57" t="s">
         <v>344</v>
@@ -16368,7 +16454,7 @@
         <v>412</v>
       </c>
       <c r="M114" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N114" s="47" t="s">
         <v>1</v>
@@ -16415,10 +16501,10 @@
         <v>297</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D115" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E115" s="57" t="s">
         <v>344</v>
@@ -16445,7 +16531,7 @@
         <v>412</v>
       </c>
       <c r="M115" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N115" s="47" t="s">
         <v>1</v>
@@ -16492,10 +16578,10 @@
         <v>298</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D116" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E116" s="57" t="s">
         <v>344</v>
@@ -16522,7 +16608,7 @@
         <v>412</v>
       </c>
       <c r="M116" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N116" s="47" t="s">
         <v>1</v>
@@ -16569,10 +16655,10 @@
         <v>299</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D117" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E117" s="57" t="s">
         <v>344</v>
@@ -16599,7 +16685,7 @@
         <v>412</v>
       </c>
       <c r="M117" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N117" s="47" t="s">
         <v>1</v>
@@ -16646,10 +16732,10 @@
         <v>300</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D118" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E118" s="57" t="s">
         <v>344</v>
@@ -16676,7 +16762,7 @@
         <v>412</v>
       </c>
       <c r="M118" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N118" s="47" t="s">
         <v>1</v>
@@ -16723,10 +16809,10 @@
         <v>301</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D119" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E119" s="57" t="s">
         <v>344</v>
@@ -16753,7 +16839,7 @@
         <v>412</v>
       </c>
       <c r="M119" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N119" s="47" t="s">
         <v>1</v>
@@ -16800,10 +16886,10 @@
         <v>302</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D120" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E120" s="57" t="s">
         <v>344</v>
@@ -16830,7 +16916,7 @@
         <v>412</v>
       </c>
       <c r="M120" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N120" s="47" t="s">
         <v>1</v>
@@ -16877,10 +16963,10 @@
         <v>303</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D121" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E121" s="57" t="s">
         <v>344</v>
@@ -16907,7 +16993,7 @@
         <v>412</v>
       </c>
       <c r="M121" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N121" s="47" t="s">
         <v>1</v>
@@ -16954,10 +17040,10 @@
         <v>304</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D122" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E122" s="57" t="s">
         <v>344</v>
@@ -16984,7 +17070,7 @@
         <v>412</v>
       </c>
       <c r="M122" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N122" s="47" t="s">
         <v>1</v>
@@ -17031,10 +17117,10 @@
         <v>305</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D123" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E123" s="57" t="s">
         <v>344</v>
@@ -17061,7 +17147,7 @@
         <v>412</v>
       </c>
       <c r="M123" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N123" s="47" t="s">
         <v>1</v>
@@ -17108,10 +17194,10 @@
         <v>306</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D124" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E124" s="57" t="s">
         <v>344</v>
@@ -17138,7 +17224,7 @@
         <v>412</v>
       </c>
       <c r="M124" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N124" s="47" t="s">
         <v>1</v>
@@ -17185,10 +17271,10 @@
         <v>307</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D125" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E125" s="57" t="s">
         <v>344</v>
@@ -17215,7 +17301,7 @@
         <v>412</v>
       </c>
       <c r="M125" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N125" s="47" t="s">
         <v>1</v>
@@ -17262,10 +17348,10 @@
         <v>308</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D126" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E126" s="57" t="s">
         <v>344</v>
@@ -17292,7 +17378,7 @@
         <v>412</v>
       </c>
       <c r="M126" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N126" s="47" t="s">
         <v>1</v>
@@ -17339,10 +17425,10 @@
         <v>309</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D127" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E127" s="57" t="s">
         <v>344</v>
@@ -17369,7 +17455,7 @@
         <v>412</v>
       </c>
       <c r="M127" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N127" s="47" t="s">
         <v>1</v>
@@ -17416,10 +17502,10 @@
         <v>310</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D128" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E128" s="57" t="s">
         <v>344</v>
@@ -17446,7 +17532,7 @@
         <v>412</v>
       </c>
       <c r="M128" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N128" s="47" t="s">
         <v>1</v>
@@ -17493,10 +17579,10 @@
         <v>311</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D129" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E129" s="57" t="s">
         <v>344</v>
@@ -17523,7 +17609,7 @@
         <v>412</v>
       </c>
       <c r="M129" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N129" s="47" t="s">
         <v>1</v>
@@ -17570,10 +17656,10 @@
         <v>312</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D130" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E130" s="57" t="s">
         <v>344</v>
@@ -17600,7 +17686,7 @@
         <v>412</v>
       </c>
       <c r="M130" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N130" s="47" t="s">
         <v>1</v>
@@ -17647,10 +17733,10 @@
         <v>313</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D131" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E131" s="57" t="s">
         <v>344</v>
@@ -17677,7 +17763,7 @@
         <v>412</v>
       </c>
       <c r="M131" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N131" s="47" t="s">
         <v>1</v>
@@ -17724,10 +17810,10 @@
         <v>314</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D132" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E132" s="57" t="s">
         <v>344</v>
@@ -17754,7 +17840,7 @@
         <v>412</v>
       </c>
       <c r="M132" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N132" s="47" t="s">
         <v>1</v>
@@ -17801,10 +17887,10 @@
         <v>315</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D133" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E133" s="57" t="s">
         <v>344</v>
@@ -17831,7 +17917,7 @@
         <v>412</v>
       </c>
       <c r="M133" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N133" s="47" t="s">
         <v>1</v>
@@ -17878,10 +17964,10 @@
         <v>316</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D134" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E134" s="57" t="s">
         <v>344</v>
@@ -17908,7 +17994,7 @@
         <v>412</v>
       </c>
       <c r="M134" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N134" s="47" t="s">
         <v>1</v>
@@ -17955,10 +18041,10 @@
         <v>317</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D135" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E135" s="57" t="s">
         <v>344</v>
@@ -17985,7 +18071,7 @@
         <v>412</v>
       </c>
       <c r="M135" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N135" s="47" t="s">
         <v>1</v>
@@ -18032,10 +18118,10 @@
         <v>318</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="D136" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E136" s="57" t="s">
         <v>344</v>
@@ -18062,7 +18148,7 @@
         <v>412</v>
       </c>
       <c r="M136" s="46" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="N136" s="47" t="s">
         <v>1</v>
@@ -18109,10 +18195,10 @@
         <v>319</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D137" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E137" s="57" t="s">
         <v>344</v>
@@ -18139,7 +18225,7 @@
         <v>412</v>
       </c>
       <c r="M137" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N137" s="47" t="s">
         <v>1</v>
@@ -18186,10 +18272,10 @@
         <v>320</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D138" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E138" s="57" t="s">
         <v>344</v>
@@ -18216,7 +18302,7 @@
         <v>412</v>
       </c>
       <c r="M138" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N138" s="47" t="s">
         <v>1</v>
@@ -18263,10 +18349,10 @@
         <v>321</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D139" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E139" s="57" t="s">
         <v>344</v>
@@ -18293,7 +18379,7 @@
         <v>412</v>
       </c>
       <c r="M139" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N139" s="47" t="s">
         <v>1</v>
@@ -18340,10 +18426,10 @@
         <v>322</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D140" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E140" s="57" t="s">
         <v>344</v>
@@ -18370,7 +18456,7 @@
         <v>412</v>
       </c>
       <c r="M140" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N140" s="47" t="s">
         <v>1</v>
@@ -18417,10 +18503,10 @@
         <v>323</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D141" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E141" s="57" t="s">
         <v>344</v>
@@ -18447,7 +18533,7 @@
         <v>412</v>
       </c>
       <c r="M141" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N141" s="47" t="s">
         <v>1</v>
@@ -18494,10 +18580,10 @@
         <v>324</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D142" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E142" s="57" t="s">
         <v>344</v>
@@ -18524,7 +18610,7 @@
         <v>412</v>
       </c>
       <c r="M142" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N142" s="47" t="s">
         <v>1</v>
@@ -18571,10 +18657,10 @@
         <v>325</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D143" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E143" s="57" t="s">
         <v>344</v>
@@ -18601,7 +18687,7 @@
         <v>412</v>
       </c>
       <c r="M143" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N143" s="47" t="s">
         <v>1</v>
@@ -18648,10 +18734,10 @@
         <v>418</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D144" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E144" s="57" t="s">
         <v>344</v>
@@ -18678,7 +18764,7 @@
         <v>412</v>
       </c>
       <c r="M144" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N144" s="47" t="s">
         <v>1</v>
@@ -18725,10 +18811,10 @@
         <v>326</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D145" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E145" s="57" t="s">
         <v>344</v>
@@ -18755,7 +18841,7 @@
         <v>412</v>
       </c>
       <c r="M145" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N145" s="47" t="s">
         <v>1</v>
@@ -18802,10 +18888,10 @@
         <v>327</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D146" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E146" s="57" t="s">
         <v>344</v>
@@ -18832,7 +18918,7 @@
         <v>412</v>
       </c>
       <c r="M146" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N146" s="47" t="s">
         <v>1</v>
@@ -18879,10 +18965,10 @@
         <v>328</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D147" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E147" s="57" t="s">
         <v>344</v>
@@ -18909,7 +18995,7 @@
         <v>412</v>
       </c>
       <c r="M147" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N147" s="47" t="s">
         <v>1</v>
@@ -18956,10 +19042,10 @@
         <v>329</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D148" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E148" s="57" t="s">
         <v>344</v>
@@ -18986,7 +19072,7 @@
         <v>412</v>
       </c>
       <c r="M148" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N148" s="47" t="s">
         <v>1</v>
@@ -19033,10 +19119,10 @@
         <v>330</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D149" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E149" s="57" t="s">
         <v>344</v>
@@ -19063,7 +19149,7 @@
         <v>412</v>
       </c>
       <c r="M149" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N149" s="47" t="s">
         <v>1</v>
@@ -19110,10 +19196,10 @@
         <v>331</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D150" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E150" s="57" t="s">
         <v>344</v>
@@ -19140,7 +19226,7 @@
         <v>412</v>
       </c>
       <c r="M150" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N150" s="47" t="s">
         <v>1</v>
@@ -19187,10 +19273,10 @@
         <v>332</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D151" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E151" s="57" t="s">
         <v>344</v>
@@ -19217,7 +19303,7 @@
         <v>412</v>
       </c>
       <c r="M151" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N151" s="47" t="s">
         <v>1</v>
@@ -19264,10 +19350,10 @@
         <v>333</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D152" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E152" s="57" t="s">
         <v>344</v>
@@ -19294,7 +19380,7 @@
         <v>412</v>
       </c>
       <c r="M152" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N152" s="47" t="s">
         <v>1</v>
@@ -19341,10 +19427,10 @@
         <v>334</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D153" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E153" s="57" t="s">
         <v>344</v>
@@ -19371,7 +19457,7 @@
         <v>412</v>
       </c>
       <c r="M153" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N153" s="47" t="s">
         <v>1</v>
@@ -19418,10 +19504,10 @@
         <v>335</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D154" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E154" s="57" t="s">
         <v>344</v>
@@ -19448,7 +19534,7 @@
         <v>412</v>
       </c>
       <c r="M154" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N154" s="47" t="s">
         <v>1</v>
@@ -19495,10 +19581,10 @@
         <v>336</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D155" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E155" s="57" t="s">
         <v>344</v>
@@ -19525,7 +19611,7 @@
         <v>412</v>
       </c>
       <c r="M155" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N155" s="47" t="s">
         <v>1</v>
@@ -19572,10 +19658,10 @@
         <v>337</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D156" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E156" s="57" t="s">
         <v>344</v>
@@ -19602,7 +19688,7 @@
         <v>412</v>
       </c>
       <c r="M156" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N156" s="47" t="s">
         <v>1</v>
@@ -19649,10 +19735,10 @@
         <v>338</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="D157" s="56" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E157" s="57" t="s">
         <v>344</v>
@@ -19679,7 +19765,7 @@
         <v>412</v>
       </c>
       <c r="M157" s="46" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="N157" s="47" t="s">
         <v>1</v>
@@ -19721,10 +19807,10 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2N.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805BE79A-AF5A-4CC0-9D13-6932C2B2F11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE972FD-88CF-4046-B00D-00B01CF9CFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4375" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4414" uniqueCount="572">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1729,13 +1729,91 @@
   </si>
   <si>
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I. Building Information Codes.</t>
+  </si>
+  <si>
+    <t>Fonte1</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>Fonte2</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>Fonte3</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>FonteVegetação1</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>FonteVegetação2</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>FonteVegetação3</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação4</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>FonteVegetação5</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>FonteVegetação6</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação7</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>FonteVegetação8</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>FonteTSB</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>FonteSINAPI</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color theme="1"/>
@@ -1817,8 +1895,34 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="32">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2005,6 +2109,12 @@
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -2080,11 +2190,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2264,64 +2375,31 @@
     <xf numFmtId="0" fontId="3" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="16" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A0D90F96-026A-4EEB-BDCF-93327D239D7A}"/>
   </cellStyles>
-  <dxfs count="71">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="66">
     <dxf>
       <font>
         <b val="0"/>
@@ -2363,6 +2441,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4214,33 +4302,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" tableBorderDxfId="67" totalsRowBorderDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="65" dataDxfId="63" headerRowBorderDxfId="64" tableBorderDxfId="62" totalsRowBorderDxfId="61">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="65" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="61" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="60" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="58" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="46" dataDxfId="45"/>
+    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="44" dataDxfId="43"/>
+    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="34" dataDxfId="33"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="32" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="30" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="28" dataDxfId="27"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="26" dataDxfId="25"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="24" dataDxfId="23"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="22" dataDxfId="21"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="20" dataDxfId="19"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="18" dataDxfId="17"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="16" dataDxfId="15"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="14" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="12" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4564,7 +4652,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03763A90-6A45-4DA0-A35B-2601294A84FF}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="43" bestFit="1" customWidth="1"/>
@@ -4768,7 +4856,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46232.780858680555</v>
+        <v>46233.48056585648</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>404</v>
@@ -4864,7 +4952,157 @@
         <v>406</v>
       </c>
     </row>
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="39" t="s">
+        <v>546</v>
+      </c>
+      <c r="B27" s="61" t="s">
+        <v>547</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="39" t="s">
+        <v>548</v>
+      </c>
+      <c r="B28" s="62" t="s">
+        <v>549</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="39" t="s">
+        <v>550</v>
+      </c>
+      <c r="B29" s="62" t="s">
+        <v>551</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="39" t="s">
+        <v>552</v>
+      </c>
+      <c r="B30" s="63" t="s">
+        <v>553</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="39" t="s">
+        <v>554</v>
+      </c>
+      <c r="B31" s="63" t="s">
+        <v>555</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="39" t="s">
+        <v>556</v>
+      </c>
+      <c r="B32" s="63" t="s">
+        <v>557</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="39" t="s">
+        <v>558</v>
+      </c>
+      <c r="B33" s="65" t="s">
+        <v>559</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="39" t="s">
+        <v>560</v>
+      </c>
+      <c r="B34" s="65" t="s">
+        <v>561</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="39" t="s">
+        <v>562</v>
+      </c>
+      <c r="B35" s="63" t="s">
+        <v>563</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="39" t="s">
+        <v>564</v>
+      </c>
+      <c r="B36" s="65" t="s">
+        <v>565</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="39" t="s">
+        <v>566</v>
+      </c>
+      <c r="B37" s="63" t="s">
+        <v>567</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="B38" s="66" t="s">
+        <v>569</v>
+      </c>
+      <c r="C38" s="42" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="68" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="39" t="s">
+        <v>570</v>
+      </c>
+      <c r="B39" s="67" t="s">
+        <v>571</v>
+      </c>
+      <c r="C39" s="42" t="s">
+        <v>404</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{8A5D18B3-7F96-45D1-B931-84005A871D3C}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{6313AC66-DA8D-46A3-BE6D-24E456B9012E}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{13321976-FDCB-4882-8BBB-8D741D5C0A86}"/>
+    <hyperlink ref="B38" r:id="rId4" xr:uid="{B73B185B-7DEF-459D-9A08-E57FCDBEE1B8}"/>
+    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{D60280FD-2068-480B-8AAE-82CC00C5AD18}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -6658,7 +6896,7 @@
         <v>181</v>
       </c>
       <c r="L20" s="52" t="str">
-        <f t="shared" ref="L18:N28" si="8">CONCATENATE("", C20)</f>
+        <f t="shared" ref="L20:N28" si="8">CONCATENATE("", C20)</f>
         <v>Normativo</v>
       </c>
       <c r="M20" s="52" t="str">
@@ -6670,7 +6908,7 @@
         <v>NBR.N.RH</v>
       </c>
       <c r="O20" s="52" t="str">
-        <f t="shared" ref="O7:O28" si="9">F20</f>
+        <f t="shared" ref="O20:O28" si="9">F20</f>
         <v>NBR.N.Empreendedor</v>
       </c>
       <c r="P20" s="58" t="s">
@@ -6684,7 +6922,7 @@
         <v>181</v>
       </c>
       <c r="S20" s="53" t="str">
-        <f t="shared" ref="S7:U22" si="10">SUBSTITUTE(C20, "_", " ")</f>
+        <f t="shared" ref="S20:U22" si="10">SUBSTITUTE(C20, "_", " ")</f>
         <v>Normativo</v>
       </c>
       <c r="T20" s="53" t="str">
@@ -7461,32 +7699,22 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B6 A20:B28">
-    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B28">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA6 AA20:AA28">
-    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B19">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F19">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA19">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="AA1:AA28">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7639,7 +7867,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7684,7 +7912,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19807,10 +20035,10 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2N.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE972FD-88CF-4046-B00D-00B01CF9CFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CAD6BB-BEF4-4F5F-AEB7-AA25F04A1B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4414" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4414" uniqueCount="571">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1578,9 +1578,6 @@
     <t>"Recursos Humanos relacionados com a Construção"</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
@@ -1605,21 +1602,12 @@
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
   </si>
   <si>
-    <t>Normativo</t>
-  </si>
-  <si>
-    <t>NBR.Temática</t>
-  </si>
-  <si>
     <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0M. Códigos de Materiais.</t>
   </si>
   <si>
     <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0M. Códigos de materiales.</t>
   </si>
   <si>
-    <t>Interdiciplinar</t>
-  </si>
-  <si>
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0M. Material Codes.</t>
   </si>
   <si>
@@ -1807,6 +1795,15 @@
   </si>
   <si>
     <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>Normativos</t>
+  </si>
+  <si>
+    <t>NBR.Temáticas</t>
   </si>
 </sst>
 </file>
@@ -4856,7 +4853,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46233.48056585648</v>
+        <v>46243.559887268515</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>404</v>
@@ -4954,10 +4951,10 @@
     </row>
     <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="39" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B27" s="61" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C27" s="42" t="s">
         <v>404</v>
@@ -4965,10 +4962,10 @@
     </row>
     <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="39" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B28" s="62" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C28" s="42" t="s">
         <v>404</v>
@@ -4976,10 +4973,10 @@
     </row>
     <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="39" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B29" s="62" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C29" s="42" t="s">
         <v>404</v>
@@ -4987,10 +4984,10 @@
     </row>
     <row r="30" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="39" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B30" s="63" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C30" s="42" t="s">
         <v>404</v>
@@ -4998,10 +4995,10 @@
     </row>
     <row r="31" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="39" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B31" s="63" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C31" s="42" t="s">
         <v>404</v>
@@ -5009,10 +5006,10 @@
     </row>
     <row r="32" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="39" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B32" s="63" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C32" s="42" t="s">
         <v>404</v>
@@ -5020,10 +5017,10 @@
     </row>
     <row r="33" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="39" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B33" s="65" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C33" s="42" t="s">
         <v>404</v>
@@ -5031,10 +5028,10 @@
     </row>
     <row r="34" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="39" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B34" s="65" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C34" s="42" t="s">
         <v>404</v>
@@ -5042,10 +5039,10 @@
     </row>
     <row r="35" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="39" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B35" s="63" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C35" s="42" t="s">
         <v>404</v>
@@ -5053,10 +5050,10 @@
     </row>
     <row r="36" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="39" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B36" s="65" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C36" s="42" t="s">
         <v>404</v>
@@ -5064,10 +5061,10 @@
     </row>
     <row r="37" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="39" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B37" s="63" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C37" s="42" t="s">
         <v>404</v>
@@ -5075,10 +5072,10 @@
     </row>
     <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="B38" s="66" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C38" s="42" t="s">
         <v>404</v>
@@ -5086,10 +5083,10 @@
     </row>
     <row r="39" spans="1:3" s="68" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="39" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B39" s="67" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C39" s="42" t="s">
         <v>404</v>
@@ -5116,7 +5113,7 @@
     <col min="1" max="1" width="2.296875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="6.796875" style="34" customWidth="1"/>
     <col min="4" max="4" width="8.69921875" style="34" customWidth="1"/>
-    <col min="5" max="5" width="5.796875" style="34" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.59765625" style="34" customWidth="1"/>
     <col min="6" max="6" width="14" style="34" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8.69921875" style="34" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" customWidth="1"/>
@@ -5129,7 +5126,7 @@
     <col min="19" max="19" width="7" customWidth="1"/>
     <col min="20" max="20" width="9.19921875" customWidth="1"/>
     <col min="21" max="21" width="8" customWidth="1"/>
-    <col min="22" max="22" width="8.19921875" customWidth="1"/>
+    <col min="22" max="22" width="9.19921875" customWidth="1"/>
     <col min="23" max="23" width="8.69921875" style="34" customWidth="1"/>
     <col min="26" max="26" width="7.296875" customWidth="1"/>
     <col min="27" max="27" width="64.5" bestFit="1" customWidth="1"/>
@@ -5223,7 +5220,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C2" s="50" t="s">
         <v>419</v>
@@ -5232,7 +5229,7 @@
         <v>421</v>
       </c>
       <c r="E2" s="51" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F2" s="51" t="s">
         <v>420</v>
@@ -5269,10 +5266,10 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="38" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q2" s="38" t="s">
         <v>497</v>
-      </c>
-      <c r="Q2" s="38" t="s">
-        <v>498</v>
       </c>
       <c r="R2" s="38" t="s">
         <v>181</v>
@@ -5303,7 +5300,7 @@
         <v>181</v>
       </c>
       <c r="Z2" s="38" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AA2" s="38" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
@@ -5315,7 +5312,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C3" s="50" t="s">
         <v>419</v>
@@ -5324,7 +5321,7 @@
         <v>421</v>
       </c>
       <c r="E3" s="51" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F3" s="51" t="s">
         <v>423</v>
@@ -5361,10 +5358,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="38" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q3" s="38" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="R3" s="38" t="s">
         <v>181</v>
@@ -5407,7 +5404,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C4" s="50" t="s">
         <v>419</v>
@@ -5416,7 +5413,7 @@
         <v>421</v>
       </c>
       <c r="E4" s="51" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F4" s="51" t="s">
         <v>424</v>
@@ -5453,10 +5450,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="38" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="Q4" s="38" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="R4" s="38" t="s">
         <v>181</v>
@@ -5499,7 +5496,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C5" s="50" t="s">
         <v>419</v>
@@ -5508,7 +5505,7 @@
         <v>421</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F5" s="51" t="s">
         <v>425</v>
@@ -5545,10 +5542,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q5" s="38" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="R5" s="38" t="s">
         <v>181</v>
@@ -5591,7 +5588,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>419</v>
@@ -5600,7 +5597,7 @@
         <v>421</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F6" s="51" t="s">
         <v>426</v>
@@ -5637,10 +5634,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="Q6" s="38" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="R6" s="38" t="s">
         <v>181</v>
@@ -5683,10 +5680,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D7" s="33" t="s">
         <v>372</v>
@@ -5714,7 +5711,7 @@
       </c>
       <c r="L7" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M7" s="52" t="str">
         <f t="shared" si="0"/>
@@ -5729,17 +5726,17 @@
         <v>NBR.0M</v>
       </c>
       <c r="P7" s="52" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="Q7" s="52" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="R7" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S7" s="53" t="str">
         <f t="shared" ref="S7:U19" si="6">SUBSTITUTE(C7, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T7" s="53" t="str">
         <f t="shared" si="6"/>
@@ -5750,7 +5747,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V7" s="38" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="W7" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5766,7 +5763,7 @@
         <v>427</v>
       </c>
       <c r="AA7" s="54" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5774,10 +5771,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D8" s="33" t="s">
         <v>372</v>
@@ -5805,7 +5802,7 @@
       </c>
       <c r="L8" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M8" s="52" t="str">
         <f t="shared" si="0"/>
@@ -5820,17 +5817,17 @@
         <v>NBR.0P</v>
       </c>
       <c r="P8" s="52" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="Q8" s="52" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="R8" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S8" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T8" s="53" t="str">
         <f t="shared" si="6"/>
@@ -5841,7 +5838,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V8" s="38" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="W8" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5857,7 +5854,7 @@
         <v>428</v>
       </c>
       <c r="AA8" s="54" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5865,10 +5862,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D9" s="33" t="s">
         <v>372</v>
@@ -5896,7 +5893,7 @@
       </c>
       <c r="L9" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M9" s="52" t="str">
         <f t="shared" si="0"/>
@@ -5911,17 +5908,17 @@
         <v>NBR.1D</v>
       </c>
       <c r="P9" s="52" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="Q9" s="52" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="R9" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S9" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T9" s="53" t="str">
         <f t="shared" si="6"/>
@@ -5932,7 +5929,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V9" s="38" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="W9" s="59" t="str">
         <f t="shared" si="4"/>
@@ -5948,7 +5945,7 @@
         <v>429</v>
       </c>
       <c r="AA9" s="54" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5956,10 +5953,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D10" s="33" t="s">
         <v>372</v>
@@ -5987,7 +5984,7 @@
       </c>
       <c r="L10" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M10" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6002,17 +5999,17 @@
         <v>NBR.1F</v>
       </c>
       <c r="P10" s="52" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="Q10" s="52" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="R10" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S10" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T10" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6023,7 +6020,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V10" s="38" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="W10" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6039,7 +6036,7 @@
         <v>430</v>
       </c>
       <c r="AA10" s="54" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6047,10 +6044,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D11" s="33" t="s">
         <v>372</v>
@@ -6078,7 +6075,7 @@
       </c>
       <c r="L11" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M11" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6093,17 +6090,17 @@
         <v>NBR.1S</v>
       </c>
       <c r="P11" s="52" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="Q11" s="52" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="R11" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S11" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T11" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6114,7 +6111,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V11" s="38" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="W11" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6130,7 +6127,7 @@
         <v>431</v>
       </c>
       <c r="AA11" s="54" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6138,10 +6135,10 @@
         <v>12</v>
       </c>
       <c r="B12" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D12" s="33" t="s">
         <v>372</v>
@@ -6169,7 +6166,7 @@
       </c>
       <c r="L12" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M12" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6184,17 +6181,17 @@
         <v>NBR.2C</v>
       </c>
       <c r="P12" s="52" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="Q12" s="52" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="R12" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S12" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T12" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6205,7 +6202,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V12" s="38" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="W12" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6221,7 +6218,7 @@
         <v>432</v>
       </c>
       <c r="AA12" s="54" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6229,10 +6226,10 @@
         <v>13</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D13" s="33" t="s">
         <v>372</v>
@@ -6260,7 +6257,7 @@
       </c>
       <c r="L13" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M13" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6275,17 +6272,17 @@
         <v>NBR.2N</v>
       </c>
       <c r="P13" s="52" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="Q13" s="52" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="R13" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S13" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T13" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6296,7 +6293,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V13" s="38" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="W13" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6312,7 +6309,7 @@
         <v>342</v>
       </c>
       <c r="AA13" s="54" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6320,10 +6317,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D14" s="33" t="s">
         <v>372</v>
@@ -6351,7 +6348,7 @@
       </c>
       <c r="L14" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M14" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6366,17 +6363,17 @@
         <v>NBR.2Q</v>
       </c>
       <c r="P14" s="52" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="Q14" s="52" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="R14" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S14" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T14" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6387,7 +6384,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V14" s="38" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="W14" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6403,7 +6400,7 @@
         <v>433</v>
       </c>
       <c r="AA14" s="54" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6411,10 +6408,10 @@
         <v>15</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D15" s="33" t="s">
         <v>372</v>
@@ -6442,7 +6439,7 @@
       </c>
       <c r="L15" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M15" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6457,17 +6454,17 @@
         <v>NBR.3E</v>
       </c>
       <c r="P15" s="52" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="Q15" s="52" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="R15" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S15" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T15" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6478,7 +6475,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V15" s="38" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="W15" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6494,7 +6491,7 @@
         <v>434</v>
       </c>
       <c r="AA15" s="54" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6502,10 +6499,10 @@
         <v>16</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D16" s="33" t="s">
         <v>372</v>
@@ -6533,7 +6530,7 @@
       </c>
       <c r="L16" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M16" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6548,17 +6545,17 @@
         <v>NBR.3R</v>
       </c>
       <c r="P16" s="52" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="Q16" s="52" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="R16" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S16" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T16" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6569,7 +6566,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V16" s="38" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="W16" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6585,7 +6582,7 @@
         <v>435</v>
       </c>
       <c r="AA16" s="54" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6593,10 +6590,10 @@
         <v>17</v>
       </c>
       <c r="B17" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D17" s="33" t="s">
         <v>372</v>
@@ -6624,7 +6621,7 @@
       </c>
       <c r="L17" s="52" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M17" s="52" t="str">
         <f t="shared" si="0"/>
@@ -6639,17 +6636,17 @@
         <v>NBR.4A</v>
       </c>
       <c r="P17" s="52" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="Q17" s="52" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="R17" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S17" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T17" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6660,7 +6657,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V17" s="38" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="W17" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6676,7 +6673,7 @@
         <v>436</v>
       </c>
       <c r="AA17" s="54" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6684,10 +6681,10 @@
         <v>18</v>
       </c>
       <c r="B18" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D18" s="33" t="s">
         <v>372</v>
@@ -6715,7 +6712,7 @@
       </c>
       <c r="L18" s="52" t="str">
         <f t="shared" ref="L18:N19" si="7">CONCATENATE("", C18)</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M18" s="52" t="str">
         <f t="shared" si="7"/>
@@ -6730,17 +6727,17 @@
         <v>NBR.4U</v>
       </c>
       <c r="P18" s="52" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="Q18" s="52" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="R18" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S18" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T18" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6751,7 +6748,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V18" s="38" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="W18" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6767,7 +6764,7 @@
         <v>437</v>
       </c>
       <c r="AA18" s="54" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6775,10 +6772,10 @@
         <v>19</v>
       </c>
       <c r="B19" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>372</v>
@@ -6806,7 +6803,7 @@
       </c>
       <c r="L19" s="52" t="str">
         <f t="shared" si="7"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M19" s="52" t="str">
         <f t="shared" si="7"/>
@@ -6821,17 +6818,17 @@
         <v>NBR.5I</v>
       </c>
       <c r="P19" s="52" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="Q19" s="52" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="R19" s="38" t="s">
         <v>181</v>
       </c>
       <c r="S19" s="53" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T19" s="53" t="str">
         <f t="shared" si="6"/>
@@ -6842,7 +6839,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V19" s="38" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="W19" s="59" t="str">
         <f t="shared" si="4"/>
@@ -6858,7 +6855,7 @@
         <v>438</v>
       </c>
       <c r="AA19" s="54" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6866,13 +6863,13 @@
         <v>20</v>
       </c>
       <c r="B20" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>505</v>
+        <v>570</v>
       </c>
       <c r="E20" s="33" t="s">
         <v>465</v>
@@ -6897,11 +6894,11 @@
       </c>
       <c r="L20" s="52" t="str">
         <f t="shared" ref="L20:N28" si="8">CONCATENATE("", C20)</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M20" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N20" s="52" t="str">
         <f t="shared" si="8"/>
@@ -6923,11 +6920,11 @@
       </c>
       <c r="S20" s="53" t="str">
         <f t="shared" ref="S20:U22" si="10">SUBSTITUTE(C20, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T20" s="53" t="str">
         <f t="shared" si="10"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U20" s="52" t="str">
         <f t="shared" si="10"/>
@@ -6959,13 +6956,13 @@
         <v>21</v>
       </c>
       <c r="B21" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>505</v>
+        <v>570</v>
       </c>
       <c r="E21" s="33" t="s">
         <v>465</v>
@@ -6990,11 +6987,11 @@
       </c>
       <c r="L21" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M21" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N21" s="52" t="str">
         <f t="shared" si="8"/>
@@ -7016,11 +7013,11 @@
       </c>
       <c r="S21" s="53" t="str">
         <f t="shared" si="10"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T21" s="53" t="str">
         <f t="shared" si="10"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U21" s="52" t="str">
         <f t="shared" si="10"/>
@@ -7052,13 +7049,13 @@
         <v>22</v>
       </c>
       <c r="B22" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>505</v>
+        <v>570</v>
       </c>
       <c r="E22" s="33" t="s">
         <v>465</v>
@@ -7083,11 +7080,11 @@
       </c>
       <c r="L22" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M22" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N22" s="52" t="str">
         <f t="shared" si="8"/>
@@ -7109,11 +7106,11 @@
       </c>
       <c r="S22" s="53" t="str">
         <f t="shared" si="10"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T22" s="53" t="str">
         <f t="shared" si="10"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U22" s="52" t="str">
         <f t="shared" si="10"/>
@@ -7145,13 +7142,13 @@
         <v>23</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>505</v>
+        <v>570</v>
       </c>
       <c r="E23" s="33" t="s">
         <v>465</v>
@@ -7176,11 +7173,11 @@
       </c>
       <c r="L23" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M23" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N23" s="52" t="str">
         <f t="shared" si="8"/>
@@ -7202,11 +7199,11 @@
       </c>
       <c r="S23" s="53" t="str">
         <f t="shared" ref="S23:U28" si="13">SUBSTITUTE(C23, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T23" s="53" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U23" s="52" t="str">
         <f t="shared" si="13"/>
@@ -7238,13 +7235,13 @@
         <v>24</v>
       </c>
       <c r="B24" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>505</v>
+        <v>570</v>
       </c>
       <c r="E24" s="33" t="s">
         <v>465</v>
@@ -7269,11 +7266,11 @@
       </c>
       <c r="L24" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M24" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N24" s="52" t="str">
         <f t="shared" si="8"/>
@@ -7295,11 +7292,11 @@
       </c>
       <c r="S24" s="53" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T24" s="53" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U24" s="52" t="str">
         <f t="shared" si="13"/>
@@ -7331,13 +7328,13 @@
         <v>25</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>505</v>
+        <v>570</v>
       </c>
       <c r="E25" s="33" t="s">
         <v>465</v>
@@ -7362,11 +7359,11 @@
       </c>
       <c r="L25" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M25" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N25" s="52" t="str">
         <f t="shared" si="8"/>
@@ -7388,11 +7385,11 @@
       </c>
       <c r="S25" s="53" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T25" s="53" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U25" s="52" t="str">
         <f t="shared" si="13"/>
@@ -7424,13 +7421,13 @@
         <v>26</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>505</v>
+        <v>570</v>
       </c>
       <c r="E26" s="33" t="s">
         <v>465</v>
@@ -7455,11 +7452,11 @@
       </c>
       <c r="L26" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M26" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N26" s="52" t="str">
         <f t="shared" si="8"/>
@@ -7481,11 +7478,11 @@
       </c>
       <c r="S26" s="53" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T26" s="53" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U26" s="52" t="str">
         <f t="shared" si="13"/>
@@ -7517,13 +7514,13 @@
         <v>27</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>505</v>
+        <v>570</v>
       </c>
       <c r="E27" s="33" t="s">
         <v>465</v>
@@ -7548,11 +7545,11 @@
       </c>
       <c r="L27" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M27" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N27" s="52" t="str">
         <f t="shared" si="8"/>
@@ -7574,11 +7571,11 @@
       </c>
       <c r="S27" s="53" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T27" s="53" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U27" s="52" t="str">
         <f t="shared" si="13"/>
@@ -7610,13 +7607,13 @@
         <v>28</v>
       </c>
       <c r="B28" s="50" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>505</v>
+        <v>570</v>
       </c>
       <c r="E28" s="33" t="s">
         <v>465</v>
@@ -7641,11 +7638,11 @@
       </c>
       <c r="L28" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M28" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N28" s="52" t="str">
         <f t="shared" si="8"/>
@@ -7667,11 +7664,11 @@
       </c>
       <c r="S28" s="53" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T28" s="53" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U28" s="52" t="str">
         <f t="shared" si="13"/>
@@ -8028,7 +8025,7 @@
         <v>345</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>181</v>
